--- a/file_wisuda_4okt.xlsx
+++ b/file_wisuda_4okt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="78">
   <si>
     <t xml:space="preserve">Graduation Schedule 
 </t>
@@ -58,18 +58,24 @@
     <t>`1</t>
   </si>
   <si>
+    <t>Adi</t>
+  </si>
+  <si>
+    <t>Family B</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>dp 100</t>
+  </si>
+  <si>
     <t>Dian</t>
   </si>
   <si>
     <t>Graduation</t>
   </si>
   <si>
-    <t>IN</t>
-  </si>
-  <si>
-    <t>dp 100</t>
-  </si>
-  <si>
     <t>ALFIAN WICAKSANA</t>
   </si>
   <si>
@@ -229,7 +235,16 @@
     <t>Hanan Aldi R</t>
   </si>
   <si>
+    <t>Rendy Ilhamsyah</t>
+  </si>
+  <si>
     <t>Alif Arhansyah</t>
+  </si>
+  <si>
+    <t>Cibita</t>
+  </si>
+  <si>
+    <t>lunas</t>
   </si>
   <si>
     <t>CLOSED</t>
@@ -533,7 +548,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -605,6 +620,15 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -612,9 +636,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="10" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -625,9 +646,6 @@
     </xf>
     <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
@@ -739,7 +757,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image4.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -767,7 +785,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -795,7 +813,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -823,7 +841,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -851,7 +869,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1481,10 +1499,10 @@
       <c r="B14" s="23">
         <v>0.4166666666666667</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
       <c r="G14" s="22">
         <v>3.0</v>
       </c>
@@ -1495,16 +1513,24 @@
       <c r="J14" s="22"/>
       <c r="K14" s="22"/>
       <c r="L14" s="22"/>
-      <c r="M14" s="22">
+      <c r="M14" s="26">
         <v>3.0</v>
       </c>
-      <c r="N14" s="23">
+      <c r="N14" s="27">
         <v>0.4166666666666667</v>
       </c>
-      <c r="O14" s="22"/>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="22"/>
-      <c r="R14" s="22"/>
+      <c r="O14" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="P14" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q14" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="R14" s="26" t="s">
+        <v>16</v>
+      </c>
       <c r="S14" s="22">
         <v>3.0</v>
       </c>
@@ -1549,22 +1575,22 @@
       <c r="J15" s="22"/>
       <c r="K15" s="22"/>
       <c r="L15" s="22"/>
-      <c r="M15" s="25">
+      <c r="M15" s="28">
         <v>4.0</v>
       </c>
-      <c r="N15" s="26">
+      <c r="N15" s="29">
         <v>0.4375</v>
       </c>
-      <c r="O15" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="P15" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q15" s="27" t="s">
+      <c r="O15" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="P15" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q15" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="R15" s="27" t="s">
+      <c r="R15" s="26" t="s">
         <v>16</v>
       </c>
       <c r="S15" s="22">
@@ -1753,984 +1779,992 @@
       <c r="AF18" s="24"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="25">
+      <c r="A19" s="28">
         <v>8.0</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="29">
         <v>0.5208333333333334</v>
       </c>
-      <c r="C19" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="28" t="s">
+      <c r="C19" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="F19" s="28" t="s">
+      <c r="E19" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="29">
+      <c r="G19" s="31">
         <v>8.0</v>
       </c>
-      <c r="H19" s="30">
+      <c r="H19" s="32">
         <v>0.5208333333333334</v>
       </c>
-      <c r="I19" s="29"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
-      <c r="L19" s="31"/>
-      <c r="M19" s="27">
+      <c r="I19" s="31"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="33"/>
+      <c r="M19" s="26">
         <v>8.0</v>
       </c>
-      <c r="N19" s="32">
+      <c r="N19" s="27">
         <v>0.5208333333333334</v>
       </c>
-      <c r="O19" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="P19" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q19" s="27" t="s">
+      <c r="O19" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="P19" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q19" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="R19" s="33" t="s">
+      <c r="R19" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="S19" s="25">
+      <c r="S19" s="28">
         <v>8.0</v>
       </c>
-      <c r="T19" s="26">
+      <c r="T19" s="29">
         <v>0.5208333333333334</v>
       </c>
-      <c r="U19" s="34" t="s">
+      <c r="U19" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="V19" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="W19" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="V19" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="W19" s="34" t="s">
+      <c r="X19" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y19" s="26">
+        <v>8.0</v>
+      </c>
+      <c r="Z19" s="27">
+        <v>0.5208333333333334</v>
+      </c>
+      <c r="AA19" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB19" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="X19" s="34" t="s">
+      <c r="AC19" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD19" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="Y19" s="27">
-        <v>8.0</v>
-      </c>
-      <c r="Z19" s="32">
-        <v>0.5208333333333334</v>
-      </c>
-      <c r="AA19" s="35" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB19" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC19" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD19" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE19" s="37"/>
-      <c r="AF19" s="37"/>
+      <c r="AE19" s="38"/>
+      <c r="AF19" s="38"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="25">
+      <c r="A20" s="28">
         <v>9.0</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="29">
         <v>0.5416666666666666</v>
       </c>
-      <c r="C20" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="28" t="s">
+      <c r="C20" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="28"/>
-      <c r="G20" s="31">
+      <c r="E20" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="30"/>
+      <c r="G20" s="33">
         <v>9.0</v>
       </c>
-      <c r="H20" s="38">
+      <c r="H20" s="39">
         <v>0.5416666666666666</v>
       </c>
-      <c r="I20" s="39"/>
-      <c r="J20" s="39"/>
-      <c r="K20" s="39"/>
-      <c r="L20" s="39"/>
-      <c r="M20" s="25">
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="40"/>
+      <c r="M20" s="28">
         <v>9.0</v>
       </c>
-      <c r="N20" s="26">
+      <c r="N20" s="29">
         <v>0.5416666666666666</v>
       </c>
-      <c r="O20" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="P20" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q20" s="41" t="s">
+      <c r="O20" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="P20" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="R20" s="28" t="s">
+      <c r="Q20" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="R20" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="S20" s="25">
+      <c r="S20" s="28">
         <v>9.0</v>
       </c>
-      <c r="T20" s="26">
+      <c r="T20" s="29">
         <v>0.5416666666666666</v>
       </c>
-      <c r="U20" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="V20" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="W20" s="28" t="s">
+      <c r="U20" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="V20" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="X20" s="28" t="s">
+      <c r="W20" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="X20" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="Y20" s="27">
+      <c r="Y20" s="26">
         <v>9.0</v>
       </c>
-      <c r="Z20" s="32">
+      <c r="Z20" s="27">
         <v>0.5416666666666666</v>
       </c>
-      <c r="AA20" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB20" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC20" s="36" t="s">
+      <c r="AA20" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB20" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC20" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="AD20" s="42"/>
-      <c r="AE20" s="43"/>
-      <c r="AF20" s="43"/>
+      <c r="AD20" s="43"/>
+      <c r="AE20" s="44"/>
+      <c r="AF20" s="44"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="25">
+      <c r="A21" s="28">
         <v>10.0</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="29">
         <v>0.5555555555555556</v>
       </c>
-      <c r="C21" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="28" t="s">
+      <c r="C21" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="F21" s="28" t="s">
+      <c r="F21" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="G21" s="25">
+      <c r="G21" s="28">
         <v>10.0</v>
       </c>
-      <c r="H21" s="26">
+      <c r="H21" s="29">
         <v>0.5555555555555556</v>
       </c>
-      <c r="I21" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="J21" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="K21" s="28" t="s">
+      <c r="I21" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="J21" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="K21" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="L21" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="M21" s="28">
+        <v>10.0</v>
+      </c>
+      <c r="N21" s="29">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="O21" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="P21" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="L21" s="28" t="s">
+      <c r="Q21" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="R21" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="M21" s="25">
+      <c r="S21" s="28">
         <v>10.0</v>
       </c>
-      <c r="N21" s="26">
+      <c r="T21" s="29">
         <v>0.5555555555555556</v>
       </c>
-      <c r="O21" s="44" t="s">
-        <v>29</v>
-      </c>
-      <c r="P21" s="45" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q21" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="R21" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="S21" s="25">
+      <c r="U21" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="V21" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="W21" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="X21" s="28"/>
+      <c r="Y21" s="28">
         <v>10.0</v>
       </c>
-      <c r="T21" s="26">
+      <c r="Z21" s="29">
         <v>0.5555555555555556</v>
       </c>
-      <c r="U21" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="V21" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="W21" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="X21" s="25"/>
-      <c r="Y21" s="25">
-        <v>10.0</v>
-      </c>
-      <c r="Z21" s="26">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="AA21" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB21" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC21" s="28" t="s">
+      <c r="AA21" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB21" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="AD21" s="25"/>
+      <c r="AC21" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD21" s="28"/>
       <c r="AE21" s="24"/>
       <c r="AF21" s="24"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="25">
+      <c r="A22" s="28">
         <v>11.0</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="29">
         <v>0.5694444444444444</v>
       </c>
-      <c r="C22" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="28" t="s">
+      <c r="C22" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="33">
+        <v>11.0</v>
+      </c>
+      <c r="H22" s="39">
+        <v>0.5694444444444444</v>
+      </c>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="28">
+        <v>11.0</v>
+      </c>
+      <c r="N22" s="29">
+        <v>0.5694444444444444</v>
+      </c>
+      <c r="O22" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="P22" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="F22" s="28" t="s">
+      <c r="Q22" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="R22" s="28"/>
+      <c r="S22" s="28">
+        <v>11.0</v>
+      </c>
+      <c r="T22" s="29">
+        <v>0.5694444444444444</v>
+      </c>
+      <c r="U22" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="V22" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="W22" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="X22" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="G22" s="31">
+      <c r="Y22" s="28">
         <v>11.0</v>
       </c>
-      <c r="H22" s="38">
+      <c r="Z22" s="29">
         <v>0.5694444444444444</v>
       </c>
-      <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="31"/>
-      <c r="L22" s="31"/>
-      <c r="M22" s="25">
-        <v>11.0</v>
-      </c>
-      <c r="N22" s="26">
-        <v>0.5694444444444444</v>
-      </c>
-      <c r="O22" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="P22" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q22" s="28" t="s">
+      <c r="AA22" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB22" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="R22" s="25"/>
-      <c r="S22" s="25">
-        <v>11.0</v>
-      </c>
-      <c r="T22" s="26">
-        <v>0.5694444444444444</v>
-      </c>
-      <c r="U22" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="V22" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="W22" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="X22" s="28" t="s">
+      <c r="AC22" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD22" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="Y22" s="25">
-        <v>11.0</v>
-      </c>
-      <c r="Z22" s="26">
-        <v>0.5694444444444444</v>
-      </c>
-      <c r="AA22" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB22" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC22" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD22" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE22" s="46"/>
-      <c r="AF22" s="46"/>
+      <c r="AE22" s="47"/>
+      <c r="AF22" s="47"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="27">
+      <c r="A23" s="26">
         <v>13.0</v>
       </c>
-      <c r="B23" s="26">
+      <c r="B23" s="29">
         <v>0.5833333333333334</v>
       </c>
-      <c r="C23" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="27" t="s">
+      <c r="C23" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="27" t="s">
+      <c r="E23" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="G23" s="31">
+      <c r="G23" s="33">
         <v>12.0</v>
       </c>
-      <c r="H23" s="38">
+      <c r="H23" s="39">
         <v>0.5833333333333334</v>
       </c>
-      <c r="I23" s="31"/>
-      <c r="J23" s="47"/>
-      <c r="K23" s="31"/>
-      <c r="L23" s="31"/>
-      <c r="M23" s="25">
+      <c r="I23" s="33"/>
+      <c r="J23" s="48"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="28">
         <v>12.0</v>
       </c>
-      <c r="N23" s="26">
+      <c r="N23" s="29">
         <v>0.5833333333333334</v>
       </c>
-      <c r="O23" s="48" t="s">
-        <v>38</v>
-      </c>
-      <c r="P23" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q23" s="27" t="s">
+      <c r="O23" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="P23" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q23" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="R23" s="27" t="s">
+      <c r="R23" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="S23" s="25">
+      <c r="S23" s="28">
         <v>12.0</v>
       </c>
-      <c r="T23" s="26">
+      <c r="T23" s="29">
         <v>0.5833333333333334</v>
       </c>
-      <c r="U23" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="V23" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="W23" s="28" t="s">
+      <c r="U23" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="V23" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="W23" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="X23" s="28" t="s">
+      <c r="X23" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="Y23" s="25">
+      <c r="Y23" s="28">
         <v>12.0</v>
       </c>
-      <c r="Z23" s="26">
+      <c r="Z23" s="29">
         <v>0.5833333333333334</v>
       </c>
-      <c r="AA23" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB23" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC23" s="27" t="s">
+      <c r="AA23" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB23" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="AD23" s="44"/>
+      <c r="AC23" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD23" s="45"/>
       <c r="AE23" s="24"/>
       <c r="AF23" s="24"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="28">
+      <c r="A24" s="30">
         <v>14.0</v>
       </c>
-      <c r="B24" s="26">
+      <c r="B24" s="29">
         <v>0.5972222222222222</v>
       </c>
-      <c r="C24" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="28" t="s">
+      <c r="C24" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="F24" s="28" t="s">
+      <c r="E24" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="25">
+      <c r="G24" s="28">
         <v>13.0</v>
       </c>
-      <c r="H24" s="26">
+      <c r="H24" s="29">
         <v>0.5972222222222222</v>
       </c>
-      <c r="I24" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="J24" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="K24" s="28" t="s">
+      <c r="I24" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="J24" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="L24" s="28" t="s">
+      <c r="K24" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="L24" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="M24" s="25">
+      <c r="M24" s="28">
         <v>13.0</v>
       </c>
-      <c r="N24" s="26">
+      <c r="N24" s="29">
         <v>0.5972222222222222</v>
       </c>
-      <c r="O24" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="P24" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q24" s="27" t="s">
+      <c r="O24" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="P24" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q24" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="R24" s="27" t="s">
+      <c r="R24" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="S24" s="25">
+      <c r="S24" s="28">
         <v>13.0</v>
       </c>
-      <c r="T24" s="26">
+      <c r="T24" s="29">
         <v>0.5972222222222222</v>
       </c>
-      <c r="U24" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="V24" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="W24" s="28" t="s">
+      <c r="U24" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="V24" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="X24" s="28" t="s">
+      <c r="W24" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="X24" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="Y24" s="31">
+      <c r="Y24" s="33">
         <v>13.0</v>
       </c>
-      <c r="Z24" s="38">
+      <c r="Z24" s="39">
         <v>0.5972222222222222</v>
       </c>
-      <c r="AA24" s="31"/>
-      <c r="AB24" s="31"/>
-      <c r="AC24" s="31"/>
-      <c r="AD24" s="31"/>
+      <c r="AA24" s="33"/>
+      <c r="AB24" s="33"/>
+      <c r="AC24" s="33"/>
+      <c r="AD24" s="33"/>
       <c r="AE24" s="24"/>
       <c r="AF24" s="24"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="31">
+      <c r="A25" s="33">
         <v>14.0</v>
       </c>
-      <c r="B25" s="38">
+      <c r="B25" s="39">
         <v>0.6111111111111112</v>
       </c>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="25">
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="28">
         <v>14.0</v>
       </c>
-      <c r="H25" s="26">
+      <c r="H25" s="29">
         <v>0.6111111111111112</v>
       </c>
-      <c r="I25" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="J25" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="K25" s="28" t="s">
+      <c r="I25" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="J25" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="L25" s="25"/>
-      <c r="M25" s="25">
+      <c r="K25" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="L25" s="28"/>
+      <c r="M25" s="28">
         <v>14.0</v>
       </c>
-      <c r="N25" s="26">
+      <c r="N25" s="29">
         <v>0.6111111111111112</v>
       </c>
-      <c r="O25" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="P25" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q25" s="28" t="s">
+      <c r="O25" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="P25" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q25" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="R25" s="25"/>
-      <c r="S25" s="25">
+      <c r="R25" s="28"/>
+      <c r="S25" s="28">
         <v>14.0</v>
       </c>
-      <c r="T25" s="26">
+      <c r="T25" s="29">
         <v>0.6111111111111112</v>
       </c>
-      <c r="U25" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="V25" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="W25" s="28" t="s">
+      <c r="U25" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="V25" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="W25" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="X25" s="28" t="s">
+      <c r="X25" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="Y25" s="25">
+      <c r="Y25" s="28">
         <v>14.0</v>
       </c>
-      <c r="Z25" s="26">
+      <c r="Z25" s="29">
         <v>0.6111111111111112</v>
       </c>
-      <c r="AA25" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB25" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC25" s="28" t="s">
+      <c r="AA25" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB25" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="AD25" s="28" t="s">
+      <c r="AC25" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD25" s="30" t="s">
         <v>16</v>
       </c>
       <c r="AE25" s="24"/>
       <c r="AF25" s="24"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="31">
+      <c r="A26" s="33">
         <v>15.0</v>
       </c>
-      <c r="B26" s="38">
+      <c r="B26" s="39">
         <v>0.625</v>
       </c>
-      <c r="C26" s="39"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="25">
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="28">
         <v>15.0</v>
       </c>
-      <c r="H26" s="26">
+      <c r="H26" s="29">
         <v>0.625</v>
       </c>
-      <c r="I26" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="J26" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="K26" s="28" t="s">
+      <c r="I26" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="J26" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="L26" s="28" t="s">
+      <c r="K26" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="L26" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="M26" s="25">
+      <c r="M26" s="28">
         <v>15.0</v>
       </c>
-      <c r="N26" s="26">
+      <c r="N26" s="29">
         <v>0.625</v>
       </c>
-      <c r="O26" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="P26" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q26" s="28" t="s">
+      <c r="O26" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="P26" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q26" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="R26" s="25"/>
-      <c r="S26" s="25">
+      <c r="R26" s="28"/>
+      <c r="S26" s="28">
         <v>15.0</v>
       </c>
-      <c r="T26" s="26">
+      <c r="T26" s="29">
         <v>0.625</v>
       </c>
-      <c r="U26" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="V26" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="W26" s="28" t="s">
+      <c r="U26" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="V26" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="X26" s="28" t="s">
+      <c r="W26" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="X26" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="Y26" s="25">
+      <c r="Y26" s="28">
         <v>15.0</v>
       </c>
-      <c r="Z26" s="26">
+      <c r="Z26" s="29">
         <v>0.625</v>
       </c>
-      <c r="AA26" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="AB26" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC26" s="28" t="s">
+      <c r="AA26" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB26" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC26" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="AD26" s="28" t="s">
-        <v>53</v>
+      <c r="AD26" s="30" t="s">
+        <v>55</v>
       </c>
       <c r="AE26" s="24"/>
       <c r="AF26" s="24"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="25">
+      <c r="A27" s="28">
         <v>16.0</v>
       </c>
-      <c r="B27" s="26">
+      <c r="B27" s="29">
         <v>0.6388888888888888</v>
       </c>
-      <c r="C27" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="D27" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="28" t="s">
+      <c r="C27" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="F27" s="28" t="s">
+      <c r="E27" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="25">
+      <c r="G27" s="28">
         <v>16.0</v>
       </c>
-      <c r="H27" s="26">
+      <c r="H27" s="29">
         <v>0.6388888888888888</v>
       </c>
-      <c r="I27" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="J27" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="K27" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="L27" s="28" t="s">
+      <c r="I27" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="J27" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="K27" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="L27" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="M27" s="25">
+      <c r="M27" s="28">
         <v>16.0</v>
       </c>
-      <c r="N27" s="26">
+      <c r="N27" s="29">
         <v>0.6388888888888888</v>
       </c>
-      <c r="O27" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="P27" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q27" s="28" t="s">
+      <c r="O27" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="P27" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q27" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="R27" s="28" t="s">
+      <c r="R27" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="S27" s="31">
+      <c r="S27" s="33">
         <v>16.0</v>
       </c>
-      <c r="T27" s="38">
+      <c r="T27" s="39">
         <v>0.6388888888888888</v>
       </c>
-      <c r="U27" s="31"/>
-      <c r="V27" s="31"/>
-      <c r="W27" s="31"/>
-      <c r="X27" s="31"/>
-      <c r="Y27" s="25">
+      <c r="U27" s="33"/>
+      <c r="V27" s="33"/>
+      <c r="W27" s="33"/>
+      <c r="X27" s="33"/>
+      <c r="Y27" s="28">
         <v>16.0</v>
       </c>
-      <c r="Z27" s="26">
+      <c r="Z27" s="29">
         <v>0.6388888888888888</v>
       </c>
-      <c r="AA27" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB27" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC27" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD27" s="28" t="s">
+      <c r="AA27" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB27" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC27" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD27" s="30" t="s">
         <v>16</v>
       </c>
       <c r="AE27" s="24"/>
       <c r="AF27" s="24"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="25">
+      <c r="A28" s="28">
         <v>17.0</v>
       </c>
-      <c r="B28" s="26">
+      <c r="B28" s="29">
         <v>0.6527777777777778</v>
       </c>
-      <c r="C28" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="D28" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="28" t="s">
+      <c r="C28" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D28" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="F28" s="28" t="s">
+      <c r="E28" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="F28" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="G28" s="25">
+      <c r="G28" s="28">
         <v>17.0</v>
       </c>
-      <c r="H28" s="26">
+      <c r="H28" s="29">
         <v>0.6527777777777778</v>
       </c>
-      <c r="I28" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="J28" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="K28" s="28" t="s">
+      <c r="I28" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="J28" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="L28" s="28" t="s">
+      <c r="K28" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="L28" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="M28" s="25">
+      <c r="M28" s="28">
         <v>17.0</v>
       </c>
-      <c r="N28" s="26">
+      <c r="N28" s="29">
         <v>0.6527777777777778</v>
       </c>
-      <c r="O28" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="P28" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q28" s="27" t="s">
+      <c r="O28" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="P28" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q28" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="R28" s="49" t="s">
+      <c r="R28" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="S28" s="31">
+      <c r="S28" s="33">
         <v>17.0</v>
       </c>
-      <c r="T28" s="38">
+      <c r="T28" s="39">
         <v>0.6527777777777778</v>
       </c>
-      <c r="U28" s="31"/>
-      <c r="V28" s="31"/>
-      <c r="W28" s="31"/>
-      <c r="X28" s="31"/>
-      <c r="Y28" s="25">
+      <c r="U28" s="33"/>
+      <c r="V28" s="33"/>
+      <c r="W28" s="33"/>
+      <c r="X28" s="33"/>
+      <c r="Y28" s="28">
         <v>17.0</v>
       </c>
-      <c r="Z28" s="26">
+      <c r="Z28" s="29">
         <v>0.6527777777777778</v>
       </c>
-      <c r="AA28" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB28" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC28" s="28" t="s">
+      <c r="AA28" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="AB28" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC28" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="AD28" s="28" t="s">
+      <c r="AD28" s="30" t="s">
         <v>16</v>
       </c>
       <c r="AE28" s="24"/>
       <c r="AF28" s="24"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="25">
+      <c r="A29" s="28">
         <v>18.0</v>
       </c>
-      <c r="B29" s="26">
+      <c r="B29" s="29">
         <v>0.6666666666666666</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="F29" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" s="33">
+        <v>18.0</v>
+      </c>
+      <c r="H29" s="39">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="28">
+        <v>18.0</v>
+      </c>
+      <c r="N29" s="29">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="O29" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="P29" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q29" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="R29" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="S29" s="26">
+        <v>18.0</v>
+      </c>
+      <c r="T29" s="27">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="U29" s="42" t="s">
+        <v>69</v>
+      </c>
+      <c r="V29" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="28" t="s">
+      <c r="W29" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="X29" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y29" s="28">
+        <v>18.0</v>
+      </c>
+      <c r="Z29" s="29">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AA29" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB29" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F29" s="28" t="s">
+      <c r="AC29" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD29" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="G29" s="31">
-        <v>18.0</v>
-      </c>
-      <c r="H29" s="38">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31"/>
-      <c r="M29" s="25">
-        <v>18.0</v>
-      </c>
-      <c r="N29" s="26">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="O29" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="P29" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q29" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="R29" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="S29" s="27">
-        <v>18.0</v>
-      </c>
-      <c r="T29" s="32">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="U29" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="V29" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="W29" s="41" t="s">
-        <v>18</v>
-      </c>
-      <c r="X29" s="49" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y29" s="25">
-        <v>18.0</v>
-      </c>
-      <c r="Z29" s="26">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AA29" s="41" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB29" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC29" s="41" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD29" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE29" s="51"/>
-      <c r="AF29" s="52"/>
+      <c r="AE29" s="52"/>
+      <c r="AF29" s="53"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="25">
+      <c r="A30" s="28">
         <v>19.0</v>
       </c>
-      <c r="B30" s="26">
+      <c r="B30" s="29">
         <v>0.6805555555555556</v>
       </c>
-      <c r="C30" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="D30" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="28" t="s">
+      <c r="C30" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="F30" s="25"/>
-      <c r="G30" s="22">
+      <c r="F30" s="28"/>
+      <c r="G30" s="28">
         <v>19.0</v>
       </c>
-      <c r="H30" s="23">
+      <c r="H30" s="29">
         <v>0.6805555555555556</v>
       </c>
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="22"/>
-      <c r="L30" s="22"/>
-      <c r="M30" s="25">
+      <c r="I30" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="J30" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="K30" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="L30" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="M30" s="28">
         <v>19.0</v>
       </c>
-      <c r="N30" s="26">
+      <c r="N30" s="29">
         <v>0.6805555555555556</v>
       </c>
-      <c r="O30" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="P30" s="28" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q30" s="28" t="s">
+      <c r="O30" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="P30" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q30" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="R30" s="28" t="s">
+      <c r="R30" s="30" t="s">
         <v>16</v>
       </c>
       <c r="S30" s="22">
@@ -2757,16 +2791,24 @@
       <c r="AF30" s="24"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="22">
+      <c r="A31" s="28">
         <v>20.0</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B31" s="29">
         <v>0.6944444444444444</v>
       </c>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
+      <c r="C31" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="D31" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" s="30" t="s">
+        <v>75</v>
+      </c>
       <c r="G31" s="22">
         <v>20.0</v>
       </c>
@@ -2777,18 +2819,18 @@
       <c r="J31" s="22"/>
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
-      <c r="M31" s="53">
+      <c r="M31" s="54">
         <v>20.0</v>
       </c>
-      <c r="N31" s="54">
+      <c r="N31" s="55">
         <v>0.6944444444444444</v>
       </c>
-      <c r="O31" s="55" t="s">
-        <v>71</v>
-      </c>
-      <c r="P31" s="56"/>
-      <c r="Q31" s="56"/>
-      <c r="R31" s="57"/>
+      <c r="O31" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="P31" s="57"/>
+      <c r="Q31" s="57"/>
+      <c r="R31" s="58"/>
       <c r="S31" s="22">
         <v>20.0</v>
       </c>
@@ -2833,18 +2875,18 @@
       <c r="J32" s="22"/>
       <c r="K32" s="22"/>
       <c r="L32" s="22"/>
-      <c r="M32" s="53">
+      <c r="M32" s="54">
         <v>21.0</v>
       </c>
-      <c r="N32" s="54">
+      <c r="N32" s="55">
         <v>0.7083333333333334</v>
       </c>
-      <c r="O32" s="55" t="s">
-        <v>71</v>
-      </c>
-      <c r="P32" s="56"/>
-      <c r="Q32" s="56"/>
-      <c r="R32" s="57"/>
+      <c r="O32" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="P32" s="57"/>
+      <c r="Q32" s="57"/>
+      <c r="R32" s="58"/>
       <c r="S32" s="22">
         <v>21.0</v>
       </c>
@@ -2889,18 +2931,18 @@
       <c r="J33" s="22"/>
       <c r="K33" s="22"/>
       <c r="L33" s="22"/>
-      <c r="M33" s="53">
+      <c r="M33" s="54">
         <v>22.0</v>
       </c>
-      <c r="N33" s="54">
+      <c r="N33" s="55">
         <v>0.7222222222222222</v>
       </c>
-      <c r="O33" s="55" t="s">
-        <v>71</v>
-      </c>
-      <c r="P33" s="56"/>
-      <c r="Q33" s="56"/>
-      <c r="R33" s="57"/>
+      <c r="O33" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="P33" s="57"/>
+      <c r="Q33" s="57"/>
+      <c r="R33" s="58"/>
       <c r="S33" s="22">
         <v>22.0</v>
       </c>
@@ -2918,7 +2960,7 @@
         <v>0.7222222222222222</v>
       </c>
       <c r="AA33" s="22" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="AB33" s="22"/>
       <c r="AC33" s="22"/>
@@ -2947,18 +2989,18 @@
       <c r="J34" s="22"/>
       <c r="K34" s="22"/>
       <c r="L34" s="22"/>
-      <c r="M34" s="53">
+      <c r="M34" s="54">
         <v>23.0</v>
       </c>
-      <c r="N34" s="54">
+      <c r="N34" s="55">
         <v>0.7361111111111112</v>
       </c>
-      <c r="O34" s="55" t="s">
-        <v>71</v>
-      </c>
-      <c r="P34" s="56"/>
-      <c r="Q34" s="56"/>
-      <c r="R34" s="57"/>
+      <c r="O34" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="P34" s="57"/>
+      <c r="Q34" s="57"/>
+      <c r="R34" s="58"/>
       <c r="S34" s="22">
         <v>23.0</v>
       </c>
@@ -3003,18 +3045,18 @@
       <c r="J35" s="22"/>
       <c r="K35" s="22"/>
       <c r="L35" s="22"/>
-      <c r="M35" s="53">
+      <c r="M35" s="54">
         <v>24.0</v>
       </c>
-      <c r="N35" s="54">
+      <c r="N35" s="55">
         <v>0.75</v>
       </c>
-      <c r="O35" s="55" t="s">
-        <v>71</v>
-      </c>
-      <c r="P35" s="56"/>
-      <c r="Q35" s="56"/>
-      <c r="R35" s="57"/>
+      <c r="O35" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="P35" s="57"/>
+      <c r="Q35" s="57"/>
+      <c r="R35" s="58"/>
       <c r="S35" s="22">
         <v>24.0</v>
       </c>
@@ -3059,18 +3101,18 @@
       <c r="J36" s="22"/>
       <c r="K36" s="22"/>
       <c r="L36" s="22"/>
-      <c r="M36" s="53">
+      <c r="M36" s="54">
         <v>25.0</v>
       </c>
-      <c r="N36" s="54">
+      <c r="N36" s="55">
         <v>0.7638888888888888</v>
       </c>
-      <c r="O36" s="55" t="s">
-        <v>71</v>
-      </c>
-      <c r="P36" s="56"/>
-      <c r="Q36" s="56"/>
-      <c r="R36" s="57"/>
+      <c r="O36" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="P36" s="57"/>
+      <c r="Q36" s="57"/>
+      <c r="R36" s="58"/>
       <c r="S36" s="22">
         <v>25.0</v>
       </c>
@@ -3115,18 +3157,18 @@
       <c r="J37" s="22"/>
       <c r="K37" s="22"/>
       <c r="L37" s="22"/>
-      <c r="M37" s="53">
+      <c r="M37" s="54">
         <v>26.0</v>
       </c>
-      <c r="N37" s="54">
+      <c r="N37" s="55">
         <v>0.7777777777777778</v>
       </c>
-      <c r="O37" s="55" t="s">
-        <v>71</v>
-      </c>
-      <c r="P37" s="56"/>
-      <c r="Q37" s="56"/>
-      <c r="R37" s="57"/>
+      <c r="O37" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="P37" s="57"/>
+      <c r="Q37" s="57"/>
+      <c r="R37" s="58"/>
       <c r="S37" s="22">
         <v>26.0</v>
       </c>
@@ -3171,18 +3213,18 @@
       <c r="J38" s="22"/>
       <c r="K38" s="22"/>
       <c r="L38" s="22"/>
-      <c r="M38" s="53">
+      <c r="M38" s="54">
         <v>27.0</v>
       </c>
-      <c r="N38" s="54">
+      <c r="N38" s="55">
         <v>0.7916666666666666</v>
       </c>
-      <c r="O38" s="55" t="s">
-        <v>71</v>
-      </c>
-      <c r="P38" s="56"/>
-      <c r="Q38" s="56"/>
-      <c r="R38" s="57"/>
+      <c r="O38" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="P38" s="57"/>
+      <c r="Q38" s="57"/>
+      <c r="R38" s="58"/>
       <c r="S38" s="22">
         <v>27.0</v>
       </c>
@@ -3227,18 +3269,18 @@
       <c r="J39" s="22"/>
       <c r="K39" s="22"/>
       <c r="L39" s="22"/>
-      <c r="M39" s="53">
+      <c r="M39" s="54">
         <v>28.0</v>
       </c>
-      <c r="N39" s="54">
+      <c r="N39" s="55">
         <v>0.8055555555555556</v>
       </c>
-      <c r="O39" s="55" t="s">
-        <v>71</v>
-      </c>
-      <c r="P39" s="56"/>
-      <c r="Q39" s="56"/>
-      <c r="R39" s="57"/>
+      <c r="O39" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="P39" s="57"/>
+      <c r="Q39" s="57"/>
+      <c r="R39" s="58"/>
       <c r="S39" s="22">
         <v>28.0</v>
       </c>
@@ -3258,7 +3300,7 @@
       <c r="AA39" s="22"/>
       <c r="AB39" s="22"/>
       <c r="AC39" s="22"/>
-      <c r="AD39" s="58"/>
+      <c r="AD39" s="59"/>
       <c r="AE39" s="1"/>
       <c r="AF39" s="1"/>
     </row>
@@ -3283,18 +3325,18 @@
       <c r="J40" s="22"/>
       <c r="K40" s="22"/>
       <c r="L40" s="22"/>
-      <c r="M40" s="53">
+      <c r="M40" s="54">
         <v>29.0</v>
       </c>
-      <c r="N40" s="54">
+      <c r="N40" s="55">
         <v>0.8194444444444444</v>
       </c>
-      <c r="O40" s="55" t="s">
-        <v>71</v>
-      </c>
-      <c r="P40" s="56"/>
-      <c r="Q40" s="56"/>
-      <c r="R40" s="57"/>
+      <c r="O40" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="P40" s="57"/>
+      <c r="Q40" s="57"/>
+      <c r="R40" s="58"/>
       <c r="S40" s="22">
         <v>29.0</v>
       </c>
@@ -3314,7 +3356,7 @@
       <c r="AA40" s="22"/>
       <c r="AB40" s="22"/>
       <c r="AC40" s="22"/>
-      <c r="AD40" s="58"/>
+      <c r="AD40" s="59"/>
       <c r="AE40" s="1"/>
       <c r="AF40" s="1"/>
     </row>
@@ -3339,18 +3381,18 @@
       <c r="J41" s="22"/>
       <c r="K41" s="22"/>
       <c r="L41" s="22"/>
-      <c r="M41" s="53">
+      <c r="M41" s="54">
         <v>30.0</v>
       </c>
-      <c r="N41" s="54">
+      <c r="N41" s="55">
         <v>0.8333333333333334</v>
       </c>
-      <c r="O41" s="55" t="s">
-        <v>71</v>
-      </c>
-      <c r="P41" s="56"/>
-      <c r="Q41" s="56"/>
-      <c r="R41" s="57"/>
+      <c r="O41" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="P41" s="57"/>
+      <c r="Q41" s="57"/>
+      <c r="R41" s="58"/>
       <c r="S41" s="22">
         <v>30.0</v>
       </c>
@@ -3370,7 +3412,7 @@
       <c r="AA41" s="22"/>
       <c r="AB41" s="22"/>
       <c r="AC41" s="22"/>
-      <c r="AD41" s="58"/>
+      <c r="AD41" s="59"/>
       <c r="AE41" s="1"/>
       <c r="AF41" s="1"/>
     </row>
@@ -3395,18 +3437,18 @@
       <c r="J42" s="22"/>
       <c r="K42" s="22"/>
       <c r="L42" s="22"/>
-      <c r="M42" s="53">
+      <c r="M42" s="54">
         <v>31.0</v>
       </c>
-      <c r="N42" s="54">
+      <c r="N42" s="55">
         <v>0.8472222222222222</v>
       </c>
-      <c r="O42" s="55" t="s">
-        <v>71</v>
-      </c>
-      <c r="P42" s="56"/>
-      <c r="Q42" s="56"/>
-      <c r="R42" s="57"/>
+      <c r="O42" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="P42" s="57"/>
+      <c r="Q42" s="57"/>
+      <c r="R42" s="58"/>
       <c r="S42" s="22">
         <v>31.0</v>
       </c>
@@ -3426,63 +3468,63 @@
       <c r="AA42" s="22"/>
       <c r="AB42" s="22"/>
       <c r="AC42" s="22"/>
-      <c r="AD42" s="58"/>
+      <c r="AD42" s="59"/>
       <c r="AE42" s="1"/>
       <c r="AF42" s="1"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="59">
+      <c r="A43" s="60">
         <v>32.0</v>
       </c>
-      <c r="B43" s="60">
+      <c r="B43" s="61">
         <v>0.8611111111111112</v>
       </c>
-      <c r="C43" s="59"/>
-      <c r="D43" s="59"/>
-      <c r="E43" s="59"/>
-      <c r="F43" s="59"/>
-      <c r="G43" s="59">
+      <c r="C43" s="60"/>
+      <c r="D43" s="60"/>
+      <c r="E43" s="60"/>
+      <c r="F43" s="60"/>
+      <c r="G43" s="60">
         <v>32.0</v>
       </c>
-      <c r="H43" s="60">
+      <c r="H43" s="61">
         <v>0.8611111111111112</v>
       </c>
-      <c r="I43" s="59"/>
-      <c r="J43" s="59"/>
-      <c r="K43" s="59"/>
-      <c r="L43" s="59"/>
-      <c r="M43" s="61">
+      <c r="I43" s="60"/>
+      <c r="J43" s="60"/>
+      <c r="K43" s="60"/>
+      <c r="L43" s="60"/>
+      <c r="M43" s="62">
         <v>32.0</v>
       </c>
-      <c r="N43" s="62">
+      <c r="N43" s="63">
         <v>0.8611111111111112</v>
       </c>
-      <c r="O43" s="63" t="s">
-        <v>71</v>
-      </c>
-      <c r="P43" s="64"/>
-      <c r="Q43" s="64"/>
-      <c r="R43" s="65"/>
-      <c r="S43" s="59">
+      <c r="O43" s="64" t="s">
+        <v>76</v>
+      </c>
+      <c r="P43" s="65"/>
+      <c r="Q43" s="65"/>
+      <c r="R43" s="66"/>
+      <c r="S43" s="60">
         <v>32.0</v>
       </c>
-      <c r="T43" s="60">
+      <c r="T43" s="61">
         <v>0.8611111111111112</v>
       </c>
-      <c r="U43" s="59"/>
-      <c r="V43" s="59"/>
-      <c r="W43" s="59"/>
-      <c r="X43" s="59"/>
-      <c r="Y43" s="59">
+      <c r="U43" s="60"/>
+      <c r="V43" s="60"/>
+      <c r="W43" s="60"/>
+      <c r="X43" s="60"/>
+      <c r="Y43" s="60">
         <v>32.0</v>
       </c>
-      <c r="Z43" s="60">
+      <c r="Z43" s="61">
         <v>0.8611111111111112</v>
       </c>
-      <c r="AA43" s="59"/>
-      <c r="AB43" s="59"/>
-      <c r="AC43" s="59"/>
-      <c r="AD43" s="66"/>
+      <c r="AA43" s="60"/>
+      <c r="AB43" s="60"/>
+      <c r="AC43" s="60"/>
+      <c r="AD43" s="67"/>
       <c r="AE43" s="1"/>
       <c r="AF43" s="1"/>
     </row>

--- a/file_wisuda_4okt.xlsx
+++ b/file_wisuda_4okt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="78">
   <si>
     <t xml:space="preserve">Graduation Schedule 
 </t>
@@ -757,7 +757,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image2.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -785,7 +785,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -813,7 +813,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -841,7 +841,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -869,7 +869,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2316,7 +2316,9 @@
       <c r="K25" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="L25" s="28"/>
+      <c r="L25" s="30" t="s">
+        <v>16</v>
+      </c>
       <c r="M25" s="28">
         <v>14.0</v>
       </c>

--- a/file_wisuda_4okt.xlsx
+++ b/file_wisuda_4okt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="80">
   <si>
     <t xml:space="preserve">Graduation Schedule 
 </t>
@@ -58,15 +58,24 @@
     <t>`1</t>
   </si>
   <si>
+    <t>Pratama</t>
+  </si>
+  <si>
+    <t>Single</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>lunas</t>
+  </si>
+  <si>
     <t>Adi</t>
   </si>
   <si>
     <t>Family B</t>
   </si>
   <si>
-    <t>IN</t>
-  </si>
-  <si>
     <t>dp 100</t>
   </si>
   <si>
@@ -242,9 +251,6 @@
   </si>
   <si>
     <t>Cibita</t>
-  </si>
-  <si>
-    <t>lunas</t>
   </si>
   <si>
     <t>CLOSED</t>
@@ -617,6 +623,15 @@
     <xf borderId="5" fillId="0" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -628,15 +643,6 @@
     </xf>
     <xf borderId="5" fillId="9" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="10" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
@@ -757,7 +763,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -785,7 +791,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -813,7 +819,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image5.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -841,7 +847,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -869,7 +875,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -897,7 +903,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1479,18 +1485,26 @@
       <c r="V13" s="22"/>
       <c r="W13" s="22"/>
       <c r="X13" s="22"/>
-      <c r="Y13" s="22">
+      <c r="Y13" s="24">
         <v>2.0</v>
       </c>
-      <c r="Z13" s="23">
+      <c r="Z13" s="25">
         <v>0.3958333333333333</v>
       </c>
-      <c r="AA13" s="22"/>
-      <c r="AB13" s="22"/>
-      <c r="AC13" s="22"/>
-      <c r="AD13" s="22"/>
-      <c r="AE13" s="24"/>
-      <c r="AF13" s="24"/>
+      <c r="AA13" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB13" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC13" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD13" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE13" s="27"/>
+      <c r="AF13" s="27"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="22">
@@ -1499,10 +1513,10 @@
       <c r="B14" s="23">
         <v>0.4166666666666667</v>
       </c>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
       <c r="G14" s="22">
         <v>3.0</v>
       </c>
@@ -1513,23 +1527,23 @@
       <c r="J14" s="22"/>
       <c r="K14" s="22"/>
       <c r="L14" s="22"/>
-      <c r="M14" s="26">
+      <c r="M14" s="29">
         <v>3.0</v>
       </c>
-      <c r="N14" s="27">
+      <c r="N14" s="30">
         <v>0.4166666666666667</v>
       </c>
-      <c r="O14" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="P14" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q14" s="26" t="s">
+      <c r="O14" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="P14" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q14" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="R14" s="26" t="s">
-        <v>16</v>
+      <c r="R14" s="29" t="s">
+        <v>19</v>
       </c>
       <c r="S14" s="22">
         <v>3.0</v>
@@ -1551,8 +1565,8 @@
       <c r="AB14" s="22"/>
       <c r="AC14" s="22"/>
       <c r="AD14" s="22"/>
-      <c r="AE14" s="24"/>
-      <c r="AF14" s="24"/>
+      <c r="AE14" s="27"/>
+      <c r="AF14" s="27"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="22">
@@ -1575,23 +1589,23 @@
       <c r="J15" s="22"/>
       <c r="K15" s="22"/>
       <c r="L15" s="22"/>
-      <c r="M15" s="28">
+      <c r="M15" s="24">
         <v>4.0</v>
       </c>
-      <c r="N15" s="29">
+      <c r="N15" s="25">
         <v>0.4375</v>
       </c>
-      <c r="O15" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="P15" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q15" s="26" t="s">
+      <c r="O15" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="P15" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q15" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="R15" s="26" t="s">
-        <v>16</v>
+      <c r="R15" s="29" t="s">
+        <v>19</v>
       </c>
       <c r="S15" s="22">
         <v>4.0</v>
@@ -1613,8 +1627,8 @@
       <c r="AB15" s="22"/>
       <c r="AC15" s="22"/>
       <c r="AD15" s="22"/>
-      <c r="AE15" s="24"/>
-      <c r="AF15" s="24"/>
+      <c r="AE15" s="27"/>
+      <c r="AF15" s="27"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="22">
@@ -1667,8 +1681,8 @@
       <c r="AB16" s="22"/>
       <c r="AC16" s="22"/>
       <c r="AD16" s="22"/>
-      <c r="AE16" s="24"/>
-      <c r="AF16" s="24"/>
+      <c r="AE16" s="27"/>
+      <c r="AF16" s="27"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="22">
@@ -1721,8 +1735,8 @@
       <c r="AB17" s="22"/>
       <c r="AC17" s="22"/>
       <c r="AD17" s="22"/>
-      <c r="AE17" s="24"/>
-      <c r="AF17" s="24"/>
+      <c r="AE17" s="27"/>
+      <c r="AF17" s="27"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="22">
@@ -1775,27 +1789,27 @@
       <c r="AB18" s="22"/>
       <c r="AC18" s="22"/>
       <c r="AD18" s="22"/>
-      <c r="AE18" s="24"/>
-      <c r="AF18" s="24"/>
+      <c r="AE18" s="27"/>
+      <c r="AF18" s="27"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="28">
+      <c r="A19" s="24">
         <v>8.0</v>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="25">
         <v>0.5208333333333334</v>
       </c>
-      <c r="C19" s="30" t="s">
+      <c r="C19" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="26" t="s">
         <v>19</v>
-      </c>
-      <c r="D19" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" s="30" t="s">
-        <v>16</v>
       </c>
       <c r="G19" s="31">
         <v>8.0</v>
@@ -1807,80 +1821,80 @@
       <c r="J19" s="33"/>
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
-      <c r="M19" s="26">
+      <c r="M19" s="29">
         <v>8.0</v>
       </c>
-      <c r="N19" s="27">
+      <c r="N19" s="30">
         <v>0.5208333333333334</v>
       </c>
       <c r="O19" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="P19" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="P19" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q19" s="26" t="s">
+      <c r="Q19" s="29" t="s">
         <v>15</v>
       </c>
       <c r="R19" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="S19" s="28">
+        <v>19</v>
+      </c>
+      <c r="S19" s="24">
         <v>8.0</v>
       </c>
-      <c r="T19" s="29">
+      <c r="T19" s="25">
         <v>0.5208333333333334</v>
       </c>
       <c r="U19" s="35" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="V19" s="35" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="W19" s="35" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="X19" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y19" s="26">
+        <v>19</v>
+      </c>
+      <c r="Y19" s="29">
         <v>8.0</v>
       </c>
-      <c r="Z19" s="27">
+      <c r="Z19" s="30">
         <v>0.5208333333333334</v>
       </c>
       <c r="AA19" s="36" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AB19" s="37" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AC19" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="AD19" s="26" t="s">
-        <v>16</v>
+      <c r="AD19" s="29" t="s">
+        <v>19</v>
       </c>
       <c r="AE19" s="38"/>
       <c r="AF19" s="38"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="28">
+      <c r="A20" s="24">
         <v>9.0</v>
       </c>
-      <c r="B20" s="29">
+      <c r="B20" s="25">
         <v>0.5416666666666666</v>
       </c>
-      <c r="C20" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="F20" s="30"/>
+      <c r="C20" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" s="26"/>
       <c r="G20" s="33">
         <v>9.0</v>
       </c>
@@ -1891,53 +1905,53 @@
       <c r="J20" s="40"/>
       <c r="K20" s="40"/>
       <c r="L20" s="40"/>
-      <c r="M20" s="28">
+      <c r="M20" s="24">
         <v>9.0</v>
       </c>
-      <c r="N20" s="29">
+      <c r="N20" s="25">
         <v>0.5416666666666666</v>
       </c>
       <c r="O20" s="41" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P20" s="42" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q20" s="42" t="s">
-        <v>20</v>
-      </c>
-      <c r="R20" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="S20" s="28">
+        <v>23</v>
+      </c>
+      <c r="R20" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="S20" s="24">
         <v>9.0</v>
       </c>
-      <c r="T20" s="29">
+      <c r="T20" s="25">
         <v>0.5416666666666666</v>
       </c>
-      <c r="U20" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="V20" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="W20" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="X20" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y20" s="26">
+      <c r="U20" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="V20" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="W20" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="X20" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y20" s="29">
         <v>9.0</v>
       </c>
-      <c r="Z20" s="27">
+      <c r="Z20" s="30">
         <v>0.5416666666666666</v>
       </c>
       <c r="AA20" s="36" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AB20" s="37" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AC20" s="37" t="s">
         <v>15</v>
@@ -1947,113 +1961,113 @@
       <c r="AF20" s="44"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="28">
+      <c r="A21" s="24">
         <v>10.0</v>
       </c>
-      <c r="B21" s="29">
+      <c r="B21" s="25">
         <v>0.5555555555555556</v>
       </c>
-      <c r="C21" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="30" t="s">
+      <c r="C21" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="F21" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" s="28">
+      <c r="F21" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="24">
         <v>10.0</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="25">
         <v>0.5555555555555556</v>
       </c>
-      <c r="I21" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="J21" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="K21" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="L21" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="M21" s="28">
+      <c r="I21" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="J21" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="K21" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M21" s="24">
         <v>10.0</v>
       </c>
-      <c r="N21" s="29">
+      <c r="N21" s="25">
         <v>0.5555555555555556</v>
       </c>
       <c r="O21" s="45" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="P21" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q21" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="R21" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="S21" s="28">
+        <v>21</v>
+      </c>
+      <c r="Q21" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="R21" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="S21" s="24">
         <v>10.0</v>
       </c>
-      <c r="T21" s="29">
+      <c r="T21" s="25">
         <v>0.5555555555555556</v>
       </c>
-      <c r="U21" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="V21" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="W21" s="30" t="s">
+      <c r="U21" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="V21" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="W21" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="X21" s="28"/>
-      <c r="Y21" s="28">
+      <c r="X21" s="24"/>
+      <c r="Y21" s="24">
         <v>10.0</v>
       </c>
-      <c r="Z21" s="29">
+      <c r="Z21" s="25">
         <v>0.5555555555555556</v>
       </c>
-      <c r="AA21" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB21" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC21" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD21" s="28"/>
-      <c r="AE21" s="24"/>
-      <c r="AF21" s="24"/>
+      <c r="AA21" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB21" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC21" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD21" s="24"/>
+      <c r="AE21" s="27"/>
+      <c r="AF21" s="27"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="28">
+      <c r="A22" s="24">
         <v>11.0</v>
       </c>
-      <c r="B22" s="29">
+      <c r="B22" s="25">
         <v>0.5694444444444444</v>
       </c>
-      <c r="C22" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="F22" s="30" t="s">
-        <v>16</v>
+      <c r="C22" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>19</v>
       </c>
       <c r="G22" s="33">
         <v>11.0</v>
@@ -2065,79 +2079,79 @@
       <c r="J22" s="33"/>
       <c r="K22" s="33"/>
       <c r="L22" s="33"/>
-      <c r="M22" s="28">
+      <c r="M22" s="24">
         <v>11.0</v>
       </c>
-      <c r="N22" s="29">
+      <c r="N22" s="25">
         <v>0.5694444444444444</v>
       </c>
       <c r="O22" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="P22" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q22" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="R22" s="28"/>
-      <c r="S22" s="28">
+        <v>39</v>
+      </c>
+      <c r="P22" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q22" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="R22" s="24"/>
+      <c r="S22" s="24">
         <v>11.0</v>
       </c>
-      <c r="T22" s="29">
+      <c r="T22" s="25">
         <v>0.5694444444444444</v>
       </c>
-      <c r="U22" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="V22" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="W22" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="X22" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y22" s="28">
+      <c r="U22" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="V22" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="W22" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="X22" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y22" s="24">
         <v>11.0</v>
       </c>
-      <c r="Z22" s="29">
+      <c r="Z22" s="25">
         <v>0.5694444444444444</v>
       </c>
-      <c r="AA22" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="AB22" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC22" s="30" t="s">
+      <c r="AA22" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB22" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC22" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="AD22" s="30" t="s">
-        <v>16</v>
+      <c r="AD22" s="26" t="s">
+        <v>19</v>
       </c>
       <c r="AE22" s="47"/>
       <c r="AF22" s="47"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="26">
+      <c r="A23" s="29">
         <v>13.0</v>
       </c>
-      <c r="B23" s="29">
+      <c r="B23" s="25">
         <v>0.5833333333333334</v>
       </c>
-      <c r="C23" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>16</v>
+      <c r="C23" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" s="29" t="s">
+        <v>19</v>
       </c>
       <c r="G23" s="33">
         <v>12.0</v>
@@ -2149,133 +2163,133 @@
       <c r="J23" s="48"/>
       <c r="K23" s="33"/>
       <c r="L23" s="33"/>
-      <c r="M23" s="28">
+      <c r="M23" s="24">
         <v>12.0</v>
       </c>
-      <c r="N23" s="29">
+      <c r="N23" s="25">
         <v>0.5833333333333334</v>
       </c>
       <c r="O23" s="49" t="s">
-        <v>40</v>
-      </c>
-      <c r="P23" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q23" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="P23" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q23" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="R23" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="S23" s="28">
+      <c r="R23" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="S23" s="24">
         <v>12.0</v>
       </c>
-      <c r="T23" s="29">
+      <c r="T23" s="25">
         <v>0.5833333333333334</v>
       </c>
-      <c r="U23" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="V23" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="W23" s="30" t="s">
+      <c r="U23" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="V23" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="W23" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="X23" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y23" s="28">
+      <c r="X23" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y23" s="24">
         <v>12.0</v>
       </c>
-      <c r="Z23" s="29">
+      <c r="Z23" s="25">
         <v>0.5833333333333334</v>
       </c>
-      <c r="AA23" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB23" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC23" s="26" t="s">
-        <v>20</v>
+      <c r="AA23" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB23" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC23" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="AD23" s="45"/>
-      <c r="AE23" s="24"/>
-      <c r="AF23" s="24"/>
+      <c r="AE23" s="27"/>
+      <c r="AF23" s="27"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="30">
+      <c r="A24" s="26">
         <v>14.0</v>
       </c>
-      <c r="B24" s="29">
+      <c r="B24" s="25">
         <v>0.5972222222222222</v>
       </c>
-      <c r="C24" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="F24" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="G24" s="28">
+      <c r="C24" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="24">
         <v>13.0</v>
       </c>
-      <c r="H24" s="29">
+      <c r="H24" s="25">
         <v>0.5972222222222222</v>
       </c>
-      <c r="I24" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="J24" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="K24" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="L24" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="M24" s="28">
+      <c r="I24" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="J24" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M24" s="24">
         <v>13.0</v>
       </c>
-      <c r="N24" s="29">
+      <c r="N24" s="25">
         <v>0.5972222222222222</v>
       </c>
-      <c r="O24" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="P24" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q24" s="26" t="s">
+      <c r="O24" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="P24" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q24" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="R24" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="S24" s="28">
+      <c r="R24" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="S24" s="24">
         <v>13.0</v>
       </c>
-      <c r="T24" s="29">
+      <c r="T24" s="25">
         <v>0.5972222222222222</v>
       </c>
-      <c r="U24" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="V24" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="W24" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="X24" s="30" t="s">
-        <v>16</v>
+      <c r="U24" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="V24" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="W24" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="X24" s="26" t="s">
+        <v>19</v>
       </c>
       <c r="Y24" s="33">
         <v>13.0</v>
@@ -2287,8 +2301,8 @@
       <c r="AB24" s="33"/>
       <c r="AC24" s="33"/>
       <c r="AD24" s="33"/>
-      <c r="AE24" s="24"/>
-      <c r="AF24" s="24"/>
+      <c r="AE24" s="27"/>
+      <c r="AF24" s="27"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="33">
@@ -2301,78 +2315,78 @@
       <c r="D25" s="33"/>
       <c r="E25" s="33"/>
       <c r="F25" s="33"/>
-      <c r="G25" s="28">
+      <c r="G25" s="24">
         <v>14.0</v>
       </c>
-      <c r="H25" s="29">
+      <c r="H25" s="25">
         <v>0.6111111111111112</v>
       </c>
-      <c r="I25" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="J25" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="K25" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="L25" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="M25" s="28">
+      <c r="I25" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="J25" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="K25" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M25" s="24">
         <v>14.0</v>
       </c>
-      <c r="N25" s="29">
+      <c r="N25" s="25">
         <v>0.6111111111111112</v>
       </c>
-      <c r="O25" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="P25" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q25" s="30" t="s">
+      <c r="O25" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="P25" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q25" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="R25" s="28"/>
-      <c r="S25" s="28">
+      <c r="R25" s="24"/>
+      <c r="S25" s="24">
         <v>14.0</v>
       </c>
-      <c r="T25" s="29">
+      <c r="T25" s="25">
         <v>0.6111111111111112</v>
       </c>
-      <c r="U25" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="V25" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="W25" s="30" t="s">
+      <c r="U25" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="V25" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="W25" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="X25" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y25" s="28">
+      <c r="X25" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y25" s="24">
         <v>14.0</v>
       </c>
-      <c r="Z25" s="29">
+      <c r="Z25" s="25">
         <v>0.6111111111111112</v>
       </c>
-      <c r="AA25" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="AB25" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC25" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD25" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE25" s="24"/>
-      <c r="AF25" s="24"/>
+      <c r="AA25" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB25" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC25" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD25" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE25" s="27"/>
+      <c r="AF25" s="27"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="33">
@@ -2385,133 +2399,133 @@
       <c r="D26" s="40"/>
       <c r="E26" s="40"/>
       <c r="F26" s="33"/>
-      <c r="G26" s="28">
+      <c r="G26" s="24">
         <v>15.0</v>
       </c>
-      <c r="H26" s="29">
+      <c r="H26" s="25">
         <v>0.625</v>
       </c>
-      <c r="I26" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="J26" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="K26" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="L26" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="M26" s="28">
+      <c r="I26" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="J26" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="K26" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M26" s="24">
         <v>15.0</v>
       </c>
-      <c r="N26" s="29">
+      <c r="N26" s="25">
         <v>0.625</v>
       </c>
-      <c r="O26" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="P26" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q26" s="30" t="s">
+      <c r="O26" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="P26" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q26" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="R26" s="28"/>
-      <c r="S26" s="28">
+      <c r="R26" s="24"/>
+      <c r="S26" s="24">
         <v>15.0</v>
       </c>
-      <c r="T26" s="29">
+      <c r="T26" s="25">
         <v>0.625</v>
       </c>
-      <c r="U26" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="V26" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="W26" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="X26" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y26" s="28">
+      <c r="U26" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="V26" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="W26" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="X26" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y26" s="24">
         <v>15.0</v>
       </c>
-      <c r="Z26" s="29">
+      <c r="Z26" s="25">
         <v>0.625</v>
       </c>
-      <c r="AA26" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB26" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC26" s="30" t="s">
+      <c r="AA26" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB26" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC26" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="AD26" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="AE26" s="24"/>
-      <c r="AF26" s="24"/>
+      <c r="AD26" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="AE26" s="27"/>
+      <c r="AF26" s="27"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="28">
+      <c r="A27" s="24">
         <v>16.0</v>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="25">
         <v>0.6388888888888888</v>
       </c>
-      <c r="C27" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="D27" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="F27" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="G27" s="28">
+      <c r="C27" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="24">
         <v>16.0</v>
       </c>
-      <c r="H27" s="29">
+      <c r="H27" s="25">
         <v>0.6388888888888888</v>
       </c>
-      <c r="I27" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="J27" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="K27" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="L27" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="M27" s="28">
+      <c r="I27" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="J27" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="K27" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="L27" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M27" s="24">
         <v>16.0</v>
       </c>
-      <c r="N27" s="29">
+      <c r="N27" s="25">
         <v>0.6388888888888888</v>
       </c>
-      <c r="O27" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="P27" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q27" s="30" t="s">
+      <c r="O27" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="P27" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q27" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="R27" s="30" t="s">
-        <v>16</v>
+      <c r="R27" s="26" t="s">
+        <v>19</v>
       </c>
       <c r="S27" s="33">
         <v>16.0</v>
@@ -2523,81 +2537,81 @@
       <c r="V27" s="33"/>
       <c r="W27" s="33"/>
       <c r="X27" s="33"/>
-      <c r="Y27" s="28">
+      <c r="Y27" s="24">
         <v>16.0</v>
       </c>
-      <c r="Z27" s="29">
+      <c r="Z27" s="25">
         <v>0.6388888888888888</v>
       </c>
-      <c r="AA27" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB27" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC27" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD27" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE27" s="24"/>
-      <c r="AF27" s="24"/>
+      <c r="AA27" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB27" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC27" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD27" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE27" s="27"/>
+      <c r="AF27" s="27"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="28">
+      <c r="A28" s="24">
         <v>17.0</v>
       </c>
-      <c r="B28" s="29">
+      <c r="B28" s="25">
         <v>0.6527777777777778</v>
       </c>
-      <c r="C28" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="D28" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E28" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="F28" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="G28" s="28">
+      <c r="C28" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="G28" s="24">
         <v>17.0</v>
       </c>
-      <c r="H28" s="29">
+      <c r="H28" s="25">
         <v>0.6527777777777778</v>
       </c>
-      <c r="I28" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="J28" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="K28" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="L28" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="M28" s="28">
+      <c r="I28" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="J28" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="K28" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M28" s="24">
         <v>17.0</v>
       </c>
-      <c r="N28" s="29">
+      <c r="N28" s="25">
         <v>0.6527777777777778</v>
       </c>
-      <c r="O28" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="P28" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q28" s="26" t="s">
+      <c r="O28" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="P28" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q28" s="29" t="s">
         <v>15</v>
       </c>
       <c r="R28" s="50" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="S28" s="33">
         <v>17.0</v>
@@ -2609,45 +2623,45 @@
       <c r="V28" s="33"/>
       <c r="W28" s="33"/>
       <c r="X28" s="33"/>
-      <c r="Y28" s="28">
+      <c r="Y28" s="24">
         <v>17.0</v>
       </c>
-      <c r="Z28" s="29">
+      <c r="Z28" s="25">
         <v>0.6527777777777778</v>
       </c>
-      <c r="AA28" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB28" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC28" s="30" t="s">
+      <c r="AA28" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB28" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC28" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="AD28" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE28" s="24"/>
-      <c r="AF28" s="24"/>
+      <c r="AD28" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE28" s="27"/>
+      <c r="AF28" s="27"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="28">
+      <c r="A29" s="24">
         <v>18.0</v>
       </c>
-      <c r="B29" s="29">
+      <c r="B29" s="25">
         <v>0.6666666666666666</v>
       </c>
-      <c r="C29" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="D29" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E29" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="F29" s="30" t="s">
-        <v>16</v>
+      <c r="C29" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="F29" s="26" t="s">
+        <v>19</v>
       </c>
       <c r="G29" s="33">
         <v>18.0</v>
@@ -2659,115 +2673,115 @@
       <c r="J29" s="33"/>
       <c r="K29" s="33"/>
       <c r="L29" s="33"/>
-      <c r="M29" s="28">
+      <c r="M29" s="24">
         <v>18.0</v>
       </c>
-      <c r="N29" s="29">
+      <c r="N29" s="25">
         <v>0.6666666666666666</v>
       </c>
-      <c r="O29" s="30" t="s">
+      <c r="O29" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="P29" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q29" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="R29" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="S29" s="29">
+        <v>18.0</v>
+      </c>
+      <c r="T29" s="30">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="U29" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="V29" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="P29" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q29" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="R29" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="S29" s="26">
+      <c r="W29" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="X29" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y29" s="24">
         <v>18.0</v>
       </c>
-      <c r="T29" s="27">
+      <c r="Z29" s="25">
         <v>0.6666666666666666</v>
       </c>
-      <c r="U29" s="42" t="s">
-        <v>69</v>
-      </c>
-      <c r="V29" s="42" t="s">
-        <v>64</v>
-      </c>
-      <c r="W29" s="42" t="s">
-        <v>20</v>
-      </c>
-      <c r="X29" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y29" s="28">
-        <v>18.0</v>
-      </c>
-      <c r="Z29" s="29">
-        <v>0.6666666666666666</v>
-      </c>
       <c r="AA29" s="42" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AB29" s="42" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AC29" s="42" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AD29" s="51" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE29" s="52"/>
       <c r="AF29" s="53"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="28">
+      <c r="A30" s="24">
         <v>19.0</v>
       </c>
-      <c r="B30" s="29">
+      <c r="B30" s="25">
         <v>0.6805555555555556</v>
       </c>
-      <c r="C30" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="D30" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" s="30" t="s">
+      <c r="C30" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28">
+      <c r="F30" s="24"/>
+      <c r="G30" s="24">
         <v>19.0</v>
       </c>
-      <c r="H30" s="29">
+      <c r="H30" s="25">
         <v>0.6805555555555556</v>
       </c>
-      <c r="I30" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="J30" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="K30" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="L30" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="M30" s="28">
+      <c r="I30" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="J30" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="K30" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="L30" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M30" s="24">
         <v>19.0</v>
       </c>
-      <c r="N30" s="29">
+      <c r="N30" s="25">
         <v>0.6805555555555556</v>
       </c>
-      <c r="O30" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="P30" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q30" s="30" t="s">
+      <c r="O30" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="P30" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="R30" s="30" t="s">
-        <v>16</v>
+      <c r="R30" s="26" t="s">
+        <v>19</v>
       </c>
       <c r="S30" s="22">
         <v>19.0</v>
@@ -2789,27 +2803,27 @@
       <c r="AB30" s="22"/>
       <c r="AC30" s="22"/>
       <c r="AD30" s="22"/>
-      <c r="AE30" s="24"/>
-      <c r="AF30" s="24"/>
+      <c r="AE30" s="27"/>
+      <c r="AF30" s="27"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="28">
+      <c r="A31" s="24">
         <v>20.0</v>
       </c>
-      <c r="B31" s="29">
+      <c r="B31" s="25">
         <v>0.6944444444444444</v>
       </c>
-      <c r="C31" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="D31" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" s="30" t="s">
+      <c r="C31" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="D31" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="F31" s="30" t="s">
-        <v>75</v>
+      <c r="F31" s="26" t="s">
+        <v>16</v>
       </c>
       <c r="G31" s="22">
         <v>20.0</v>
@@ -2828,7 +2842,7 @@
         <v>0.6944444444444444</v>
       </c>
       <c r="O31" s="56" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P31" s="57"/>
       <c r="Q31" s="57"/>
@@ -2853,8 +2867,8 @@
       <c r="AB31" s="22"/>
       <c r="AC31" s="22"/>
       <c r="AD31" s="22"/>
-      <c r="AE31" s="24"/>
-      <c r="AF31" s="24"/>
+      <c r="AE31" s="27"/>
+      <c r="AF31" s="27"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="22">
@@ -2884,7 +2898,7 @@
         <v>0.7083333333333334</v>
       </c>
       <c r="O32" s="56" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P32" s="57"/>
       <c r="Q32" s="57"/>
@@ -2909,8 +2923,8 @@
       <c r="AB32" s="22"/>
       <c r="AC32" s="22"/>
       <c r="AD32" s="22"/>
-      <c r="AE32" s="24"/>
-      <c r="AF32" s="24"/>
+      <c r="AE32" s="27"/>
+      <c r="AF32" s="27"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="22">
@@ -2940,7 +2954,7 @@
         <v>0.7222222222222222</v>
       </c>
       <c r="O33" s="56" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P33" s="57"/>
       <c r="Q33" s="57"/>
@@ -2962,13 +2976,13 @@
         <v>0.7222222222222222</v>
       </c>
       <c r="AA33" s="22" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AB33" s="22"/>
       <c r="AC33" s="22"/>
       <c r="AD33" s="22"/>
-      <c r="AE33" s="24"/>
-      <c r="AF33" s="24"/>
+      <c r="AE33" s="27"/>
+      <c r="AF33" s="27"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="22">
@@ -2998,7 +3012,7 @@
         <v>0.7361111111111112</v>
       </c>
       <c r="O34" s="56" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P34" s="57"/>
       <c r="Q34" s="57"/>
@@ -3023,8 +3037,8 @@
       <c r="AB34" s="22"/>
       <c r="AC34" s="22"/>
       <c r="AD34" s="22"/>
-      <c r="AE34" s="24"/>
-      <c r="AF34" s="24"/>
+      <c r="AE34" s="27"/>
+      <c r="AF34" s="27"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="22">
@@ -3054,7 +3068,7 @@
         <v>0.75</v>
       </c>
       <c r="O35" s="56" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P35" s="57"/>
       <c r="Q35" s="57"/>
@@ -3079,8 +3093,8 @@
       <c r="AB35" s="22"/>
       <c r="AC35" s="22"/>
       <c r="AD35" s="22"/>
-      <c r="AE35" s="24"/>
-      <c r="AF35" s="24"/>
+      <c r="AE35" s="27"/>
+      <c r="AF35" s="27"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="22">
@@ -3110,7 +3124,7 @@
         <v>0.7638888888888888</v>
       </c>
       <c r="O36" s="56" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P36" s="57"/>
       <c r="Q36" s="57"/>
@@ -3135,8 +3149,8 @@
       <c r="AB36" s="22"/>
       <c r="AC36" s="22"/>
       <c r="AD36" s="22"/>
-      <c r="AE36" s="24"/>
-      <c r="AF36" s="24"/>
+      <c r="AE36" s="27"/>
+      <c r="AF36" s="27"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="22">
@@ -3166,7 +3180,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="O37" s="56" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P37" s="57"/>
       <c r="Q37" s="57"/>
@@ -3191,8 +3205,8 @@
       <c r="AB37" s="22"/>
       <c r="AC37" s="22"/>
       <c r="AD37" s="22"/>
-      <c r="AE37" s="24"/>
-      <c r="AF37" s="24"/>
+      <c r="AE37" s="27"/>
+      <c r="AF37" s="27"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="22">
@@ -3222,7 +3236,7 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="O38" s="56" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P38" s="57"/>
       <c r="Q38" s="57"/>
@@ -3247,8 +3261,8 @@
       <c r="AB38" s="22"/>
       <c r="AC38" s="22"/>
       <c r="AD38" s="22"/>
-      <c r="AE38" s="24"/>
-      <c r="AF38" s="24"/>
+      <c r="AE38" s="27"/>
+      <c r="AF38" s="27"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="22">
@@ -3278,7 +3292,7 @@
         <v>0.8055555555555556</v>
       </c>
       <c r="O39" s="56" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P39" s="57"/>
       <c r="Q39" s="57"/>
@@ -3334,7 +3348,7 @@
         <v>0.8194444444444444</v>
       </c>
       <c r="O40" s="56" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P40" s="57"/>
       <c r="Q40" s="57"/>
@@ -3390,7 +3404,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="O41" s="56" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P41" s="57"/>
       <c r="Q41" s="57"/>
@@ -3446,7 +3460,7 @@
         <v>0.8472222222222222</v>
       </c>
       <c r="O42" s="56" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P42" s="57"/>
       <c r="Q42" s="57"/>
@@ -3502,7 +3516,7 @@
         <v>0.8611111111111112</v>
       </c>
       <c r="O43" s="64" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P43" s="65"/>
       <c r="Q43" s="65"/>

--- a/file_wisuda_4okt.xlsx
+++ b/file_wisuda_4okt.xlsx
@@ -85,12 +85,15 @@
     <t>Graduation</t>
   </si>
   <si>
+    <t>Nurul Indah Amalia</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
     <t>ALFIAN WICAKSANA</t>
   </si>
   <si>
-    <t>AL</t>
-  </si>
-  <si>
     <t>Bening</t>
   </si>
   <si>
@@ -194,9 +197,6 @@
   </si>
   <si>
     <t>dp 200</t>
-  </si>
-  <si>
-    <t>Nurul Indah Amalia</t>
   </si>
   <si>
     <t>Indriyani</t>
@@ -346,7 +346,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -397,6 +397,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF00FFFF"/>
+        <bgColor rgb="FF00FFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF9900"/>
+        <bgColor rgb="FFFF9900"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF00FF00"/>
         <bgColor rgb="FF00FF00"/>
       </patternFill>
@@ -405,12 +417,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor rgb="FFFF0000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF9900"/>
-        <bgColor rgb="FFFF9900"/>
       </patternFill>
     </fill>
   </fills>
@@ -554,7 +560,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="74">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -644,78 +650,96 @@
     <xf borderId="5" fillId="9" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="10" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="10" fontId="13" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="12" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="12" fontId="13" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="6" fillId="11" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="12" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="6" fillId="11" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="5" fillId="11" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="7" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="12" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="8" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="6" fillId="9" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf borderId="5" fillId="10" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="6" fillId="9" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="9" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="7" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="8" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="8" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="8" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="9" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -729,13 +753,13 @@
     <xf borderId="10" fillId="0" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="10" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="10" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="10" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="10" fillId="10" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="11" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="11" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="12" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -763,7 +787,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image2.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -791,7 +815,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -819,7 +843,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -847,7 +871,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -875,7 +899,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="0" name="image5.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -903,7 +927,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1604,7 +1628,7 @@
       <c r="Q15" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="R15" s="29" t="s">
+      <c r="R15" s="31" t="s">
         <v>19</v>
       </c>
       <c r="S15" s="22">
@@ -1739,16 +1763,24 @@
       <c r="AF17" s="27"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="22">
+      <c r="A18" s="32">
         <v>7.0</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B18" s="33">
         <v>0.5</v>
       </c>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
+      <c r="C18" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="34" t="s">
+        <v>19</v>
+      </c>
       <c r="G18" s="22">
         <v>7.0</v>
       </c>
@@ -1793,995 +1825,987 @@
       <c r="AF18" s="27"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="24">
+      <c r="A19" s="32">
         <v>8.0</v>
       </c>
-      <c r="B19" s="25">
+      <c r="B19" s="33">
         <v>0.5208333333333334</v>
       </c>
-      <c r="C19" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="26" t="s">
+      <c r="C19" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="26" t="s">
+      <c r="E19" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="26" t="s">
+      <c r="F19" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="G19" s="31">
+      <c r="G19" s="35">
         <v>8.0</v>
       </c>
-      <c r="H19" s="32">
+      <c r="H19" s="36">
         <v>0.5208333333333334</v>
       </c>
-      <c r="I19" s="31"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="33"/>
-      <c r="M19" s="29">
+      <c r="I19" s="35"/>
+      <c r="J19" s="37"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="37"/>
+      <c r="M19" s="38">
         <v>8.0</v>
       </c>
-      <c r="N19" s="30">
+      <c r="N19" s="39">
         <v>0.5208333333333334</v>
       </c>
-      <c r="O19" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="P19" s="29" t="s">
+      <c r="O19" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="P19" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="Q19" s="29" t="s">
+      <c r="Q19" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="R19" s="34" t="s">
+      <c r="R19" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="S19" s="24">
+      <c r="S19" s="32">
         <v>8.0</v>
       </c>
-      <c r="T19" s="25">
+      <c r="T19" s="33">
         <v>0.5208333333333334</v>
       </c>
-      <c r="U19" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="V19" s="35" t="s">
+      <c r="U19" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="V19" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="W19" s="35" t="s">
+      <c r="W19" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="X19" s="35" t="s">
+      <c r="X19" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="Y19" s="29">
+      <c r="Y19" s="38">
         <v>8.0</v>
       </c>
-      <c r="Z19" s="30">
+      <c r="Z19" s="39">
         <v>0.5208333333333334</v>
       </c>
-      <c r="AA19" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB19" s="37" t="s">
+      <c r="AA19" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB19" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="AC19" s="37" t="s">
+      <c r="AC19" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="AD19" s="29" t="s">
+      <c r="AD19" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="AE19" s="38"/>
-      <c r="AF19" s="38"/>
+      <c r="AE19" s="44"/>
+      <c r="AF19" s="44"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="24">
+      <c r="A20" s="32">
         <v>9.0</v>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="33">
         <v>0.5416666666666666</v>
       </c>
-      <c r="C20" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="D20" s="26" t="s">
+      <c r="C20" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="26" t="s">
+      <c r="E20" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="26"/>
-      <c r="G20" s="33">
+      <c r="F20" s="34"/>
+      <c r="G20" s="37">
         <v>9.0</v>
       </c>
-      <c r="H20" s="39">
+      <c r="H20" s="45">
         <v>0.5416666666666666</v>
       </c>
-      <c r="I20" s="40"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="40"/>
-      <c r="M20" s="24">
+      <c r="I20" s="46"/>
+      <c r="J20" s="46"/>
+      <c r="K20" s="46"/>
+      <c r="L20" s="46"/>
+      <c r="M20" s="32">
         <v>9.0</v>
       </c>
-      <c r="N20" s="25">
+      <c r="N20" s="33">
         <v>0.5416666666666666</v>
       </c>
-      <c r="O20" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="P20" s="42" t="s">
+      <c r="O20" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="P20" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="Q20" s="42" t="s">
+      <c r="Q20" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="R20" s="26" t="s">
+      <c r="R20" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="S20" s="24">
+      <c r="S20" s="32">
         <v>9.0</v>
       </c>
-      <c r="T20" s="25">
+      <c r="T20" s="33">
         <v>0.5416666666666666</v>
       </c>
-      <c r="U20" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="V20" s="26" t="s">
+      <c r="U20" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="V20" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="W20" s="26" t="s">
+      <c r="W20" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="X20" s="26" t="s">
+      <c r="X20" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="Y20" s="29">
+      <c r="Y20" s="38">
         <v>9.0</v>
       </c>
-      <c r="Z20" s="30">
+      <c r="Z20" s="39">
         <v>0.5416666666666666</v>
       </c>
-      <c r="AA20" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB20" s="37" t="s">
+      <c r="AA20" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB20" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="AC20" s="37" t="s">
+      <c r="AC20" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="AD20" s="43"/>
-      <c r="AE20" s="44"/>
-      <c r="AF20" s="44"/>
+      <c r="AD20" s="49"/>
+      <c r="AE20" s="50"/>
+      <c r="AF20" s="50"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="24">
+      <c r="A21" s="32">
         <v>10.0</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="33">
         <v>0.5555555555555556</v>
       </c>
-      <c r="C21" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="26" t="s">
+      <c r="C21" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="26" t="s">
+      <c r="E21" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="F21" s="26" t="s">
+      <c r="F21" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="G21" s="24">
+      <c r="G21" s="32">
         <v>10.0</v>
       </c>
-      <c r="H21" s="25">
+      <c r="H21" s="33">
         <v>0.5555555555555556</v>
       </c>
-      <c r="I21" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="J21" s="26" t="s">
+      <c r="I21" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="K21" s="26" t="s">
+      <c r="J21" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="K21" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="L21" s="26" t="s">
+      <c r="L21" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="M21" s="24">
+      <c r="M21" s="32">
         <v>10.0</v>
       </c>
-      <c r="N21" s="25">
+      <c r="N21" s="33">
         <v>0.5555555555555556</v>
       </c>
-      <c r="O21" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="P21" s="46" t="s">
+      <c r="O21" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="P21" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="Q21" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="R21" s="29" t="s">
+      <c r="Q21" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="R21" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="S21" s="24">
+      <c r="S21" s="32">
         <v>10.0</v>
       </c>
-      <c r="T21" s="25">
+      <c r="T21" s="33">
         <v>0.5555555555555556</v>
       </c>
-      <c r="U21" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="V21" s="26" t="s">
+      <c r="U21" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="V21" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="W21" s="26" t="s">
+      <c r="W21" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="X21" s="24"/>
-      <c r="Y21" s="24">
+      <c r="X21" s="32"/>
+      <c r="Y21" s="32">
         <v>10.0</v>
       </c>
-      <c r="Z21" s="25">
+      <c r="Z21" s="33">
         <v>0.5555555555555556</v>
       </c>
-      <c r="AA21" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="AB21" s="26" t="s">
+      <c r="AA21" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB21" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="AC21" s="26" t="s">
+      <c r="AC21" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="AD21" s="24"/>
+      <c r="AD21" s="32"/>
       <c r="AE21" s="27"/>
       <c r="AF21" s="27"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="24">
+      <c r="A22" s="32">
         <v>11.0</v>
       </c>
-      <c r="B22" s="25">
+      <c r="B22" s="33">
         <v>0.5694444444444444</v>
       </c>
-      <c r="C22" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" s="26" t="s">
+      <c r="C22" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="F22" s="26" t="s">
+      <c r="F22" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="G22" s="33">
+      <c r="G22" s="37">
         <v>11.0</v>
       </c>
-      <c r="H22" s="39">
+      <c r="H22" s="45">
         <v>0.5694444444444444</v>
       </c>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="24">
+      <c r="I22" s="37"/>
+      <c r="J22" s="37"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="37"/>
+      <c r="M22" s="32">
         <v>11.0</v>
       </c>
-      <c r="N22" s="25">
+      <c r="N22" s="33">
         <v>0.5694444444444444</v>
       </c>
-      <c r="O22" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="P22" s="26" t="s">
+      <c r="O22" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="P22" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="Q22" s="26" t="s">
+      <c r="Q22" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="R22" s="24"/>
-      <c r="S22" s="24">
+      <c r="R22" s="32"/>
+      <c r="S22" s="32">
         <v>11.0</v>
       </c>
-      <c r="T22" s="25">
+      <c r="T22" s="33">
         <v>0.5694444444444444</v>
       </c>
-      <c r="U22" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="V22" s="26" t="s">
+      <c r="U22" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="V22" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="W22" s="26" t="s">
+      <c r="W22" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="X22" s="26" t="s">
+      <c r="X22" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="Y22" s="24">
+      <c r="Y22" s="32">
         <v>11.0</v>
       </c>
-      <c r="Z22" s="25">
+      <c r="Z22" s="33">
         <v>0.5694444444444444</v>
       </c>
-      <c r="AA22" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB22" s="26" t="s">
+      <c r="AA22" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB22" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="AC22" s="26" t="s">
+      <c r="AC22" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="AD22" s="26" t="s">
+      <c r="AD22" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="AE22" s="47"/>
-      <c r="AF22" s="47"/>
+      <c r="AE22" s="53"/>
+      <c r="AF22" s="53"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="29">
+      <c r="A23" s="38">
         <v>13.0</v>
       </c>
-      <c r="B23" s="25">
+      <c r="B23" s="33">
         <v>0.5833333333333334</v>
       </c>
-      <c r="C23" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" s="29" t="s">
+      <c r="C23" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="29" t="s">
+      <c r="E23" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="F23" s="29" t="s">
+      <c r="F23" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="G23" s="33">
+      <c r="G23" s="37">
         <v>12.0</v>
       </c>
-      <c r="H23" s="39">
+      <c r="H23" s="45">
         <v>0.5833333333333334</v>
       </c>
-      <c r="I23" s="33"/>
-      <c r="J23" s="48"/>
-      <c r="K23" s="33"/>
-      <c r="L23" s="33"/>
-      <c r="M23" s="24">
+      <c r="I23" s="37"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="37"/>
+      <c r="M23" s="32">
         <v>12.0</v>
       </c>
-      <c r="N23" s="25">
+      <c r="N23" s="33">
         <v>0.5833333333333334</v>
       </c>
-      <c r="O23" s="49" t="s">
-        <v>43</v>
-      </c>
-      <c r="P23" s="29" t="s">
+      <c r="O23" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="P23" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="Q23" s="29" t="s">
+      <c r="Q23" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="R23" s="29" t="s">
+      <c r="R23" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="S23" s="24">
+      <c r="S23" s="32">
         <v>12.0</v>
       </c>
-      <c r="T23" s="25">
+      <c r="T23" s="33">
         <v>0.5833333333333334</v>
       </c>
-      <c r="U23" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="V23" s="26" t="s">
+      <c r="U23" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="V23" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="W23" s="26" t="s">
+      <c r="W23" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="X23" s="26" t="s">
+      <c r="X23" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="Y23" s="24">
+      <c r="Y23" s="32">
         <v>12.0</v>
       </c>
-      <c r="Z23" s="25">
+      <c r="Z23" s="33">
         <v>0.5833333333333334</v>
       </c>
-      <c r="AA23" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB23" s="29" t="s">
+      <c r="AA23" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB23" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="AC23" s="29" t="s">
+      <c r="AC23" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="AD23" s="45"/>
+      <c r="AD23" s="51"/>
       <c r="AE23" s="27"/>
       <c r="AF23" s="27"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="26">
+      <c r="A24" s="34">
         <v>14.0</v>
       </c>
-      <c r="B24" s="25">
+      <c r="B24" s="33">
         <v>0.5972222222222222</v>
       </c>
-      <c r="C24" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="D24" s="26" t="s">
+      <c r="C24" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="26" t="s">
+      <c r="E24" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="F24" s="26" t="s">
+      <c r="F24" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="G24" s="24">
+      <c r="G24" s="32">
         <v>13.0</v>
       </c>
-      <c r="H24" s="25">
+      <c r="H24" s="33">
         <v>0.5972222222222222</v>
       </c>
-      <c r="I24" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="J24" s="26" t="s">
+      <c r="I24" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="J24" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="K24" s="26" t="s">
+      <c r="K24" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="L24" s="26" t="s">
+      <c r="L24" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="M24" s="24">
+      <c r="M24" s="32">
         <v>13.0</v>
       </c>
-      <c r="N24" s="25">
+      <c r="N24" s="33">
         <v>0.5972222222222222</v>
       </c>
-      <c r="O24" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="P24" s="29" t="s">
+      <c r="O24" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="P24" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="Q24" s="29" t="s">
+      <c r="Q24" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="R24" s="29" t="s">
+      <c r="R24" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="S24" s="24">
+      <c r="S24" s="32">
         <v>13.0</v>
       </c>
-      <c r="T24" s="25">
+      <c r="T24" s="33">
         <v>0.5972222222222222</v>
       </c>
-      <c r="U24" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="V24" s="26" t="s">
+      <c r="U24" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="V24" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="W24" s="26" t="s">
+      <c r="W24" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="X24" s="26" t="s">
+      <c r="X24" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="Y24" s="33">
+      <c r="Y24" s="37">
         <v>13.0</v>
       </c>
-      <c r="Z24" s="39">
+      <c r="Z24" s="45">
         <v>0.5972222222222222</v>
       </c>
-      <c r="AA24" s="33"/>
-      <c r="AB24" s="33"/>
-      <c r="AC24" s="33"/>
-      <c r="AD24" s="33"/>
+      <c r="AA24" s="37"/>
+      <c r="AB24" s="37"/>
+      <c r="AC24" s="37"/>
+      <c r="AD24" s="37"/>
       <c r="AE24" s="27"/>
       <c r="AF24" s="27"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="33">
+      <c r="A25" s="37">
         <v>14.0</v>
       </c>
-      <c r="B25" s="39">
+      <c r="B25" s="45">
         <v>0.6111111111111112</v>
       </c>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="24">
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="32">
         <v>14.0</v>
       </c>
-      <c r="H25" s="25">
+      <c r="H25" s="33">
         <v>0.6111111111111112</v>
       </c>
-      <c r="I25" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="J25" s="26" t="s">
+      <c r="I25" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="J25" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="K25" s="26" t="s">
+      <c r="K25" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="L25" s="26" t="s">
+      <c r="L25" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="M25" s="24">
+      <c r="M25" s="32">
         <v>14.0</v>
       </c>
-      <c r="N25" s="25">
+      <c r="N25" s="33">
         <v>0.6111111111111112</v>
       </c>
-      <c r="O25" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="P25" s="26" t="s">
+      <c r="O25" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="P25" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="Q25" s="26" t="s">
+      <c r="Q25" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="R25" s="24"/>
-      <c r="S25" s="24">
+      <c r="R25" s="32"/>
+      <c r="S25" s="32">
         <v>14.0</v>
       </c>
-      <c r="T25" s="25">
+      <c r="T25" s="33">
         <v>0.6111111111111112</v>
       </c>
-      <c r="U25" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="V25" s="26" t="s">
+      <c r="U25" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="V25" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="W25" s="26" t="s">
+      <c r="W25" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="X25" s="26" t="s">
+      <c r="X25" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="Y25" s="24">
+      <c r="Y25" s="32">
         <v>14.0</v>
       </c>
-      <c r="Z25" s="25">
+      <c r="Z25" s="33">
         <v>0.6111111111111112</v>
       </c>
-      <c r="AA25" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB25" s="26" t="s">
+      <c r="AA25" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB25" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="AC25" s="26" t="s">
+      <c r="AC25" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="AD25" s="26" t="s">
+      <c r="AD25" s="34" t="s">
         <v>19</v>
       </c>
       <c r="AE25" s="27"/>
       <c r="AF25" s="27"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="33">
+      <c r="A26" s="37">
         <v>15.0</v>
       </c>
-      <c r="B26" s="39">
+      <c r="B26" s="45">
         <v>0.625</v>
       </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="24">
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="32">
         <v>15.0</v>
       </c>
-      <c r="H26" s="25">
+      <c r="H26" s="33">
         <v>0.625</v>
       </c>
-      <c r="I26" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="J26" s="26" t="s">
+      <c r="I26" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="J26" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="K26" s="26" t="s">
+      <c r="K26" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="L26" s="26" t="s">
+      <c r="L26" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="M26" s="24">
+      <c r="M26" s="32">
         <v>15.0</v>
       </c>
-      <c r="N26" s="25">
+      <c r="N26" s="33">
         <v>0.625</v>
       </c>
-      <c r="O26" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="P26" s="26" t="s">
+      <c r="O26" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="P26" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="Q26" s="26" t="s">
+      <c r="Q26" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="R26" s="24"/>
-      <c r="S26" s="24">
+      <c r="R26" s="32"/>
+      <c r="S26" s="32">
         <v>15.0</v>
       </c>
-      <c r="T26" s="25">
+      <c r="T26" s="33">
         <v>0.625</v>
       </c>
-      <c r="U26" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="V26" s="26" t="s">
+      <c r="U26" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="V26" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="W26" s="26" t="s">
+      <c r="W26" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="X26" s="26" t="s">
+      <c r="X26" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="Y26" s="24">
+      <c r="Y26" s="32">
         <v>15.0</v>
       </c>
-      <c r="Z26" s="25">
+      <c r="Z26" s="33">
         <v>0.625</v>
       </c>
-      <c r="AA26" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="AB26" s="26" t="s">
+      <c r="AA26" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB26" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="AC26" s="26" t="s">
+      <c r="AC26" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="AD26" s="26" t="s">
-        <v>58</v>
+      <c r="AD26" s="34" t="s">
+        <v>59</v>
       </c>
       <c r="AE26" s="27"/>
       <c r="AF26" s="27"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="24">
+      <c r="A27" s="22">
         <v>16.0</v>
       </c>
-      <c r="B27" s="25">
+      <c r="B27" s="23">
         <v>0.6388888888888888</v>
       </c>
-      <c r="C27" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="D27" s="26" t="s">
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="32">
+        <v>16.0</v>
+      </c>
+      <c r="H27" s="33">
+        <v>0.6388888888888888</v>
+      </c>
+      <c r="I27" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="J27" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="E27" s="26" t="s">
+      <c r="K27" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="L27" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="M27" s="32">
+        <v>16.0</v>
+      </c>
+      <c r="N27" s="33">
+        <v>0.6388888888888888</v>
+      </c>
+      <c r="O27" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="P27" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q27" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="R27" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="S27" s="37">
+        <v>16.0</v>
+      </c>
+      <c r="T27" s="45">
+        <v>0.6388888888888888</v>
+      </c>
+      <c r="U27" s="37"/>
+      <c r="V27" s="37"/>
+      <c r="W27" s="37"/>
+      <c r="X27" s="37"/>
+      <c r="Y27" s="32">
+        <v>16.0</v>
+      </c>
+      <c r="Z27" s="33">
+        <v>0.6388888888888888</v>
+      </c>
+      <c r="AA27" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB27" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC27" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="F27" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="G27" s="24">
-        <v>16.0</v>
-      </c>
-      <c r="H27" s="25">
-        <v>0.6388888888888888</v>
-      </c>
-      <c r="I27" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="J27" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="K27" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="L27" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="M27" s="24">
-        <v>16.0</v>
-      </c>
-      <c r="N27" s="25">
-        <v>0.6388888888888888</v>
-      </c>
-      <c r="O27" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="P27" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q27" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="R27" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="S27" s="33">
-        <v>16.0</v>
-      </c>
-      <c r="T27" s="39">
-        <v>0.6388888888888888</v>
-      </c>
-      <c r="U27" s="33"/>
-      <c r="V27" s="33"/>
-      <c r="W27" s="33"/>
-      <c r="X27" s="33"/>
-      <c r="Y27" s="24">
-        <v>16.0</v>
-      </c>
-      <c r="Z27" s="25">
-        <v>0.6388888888888888</v>
-      </c>
-      <c r="AA27" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB27" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC27" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="AD27" s="26" t="s">
+      <c r="AD27" s="34" t="s">
         <v>19</v>
       </c>
       <c r="AE27" s="27"/>
       <c r="AF27" s="27"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="24">
+      <c r="A28" s="32">
         <v>17.0</v>
       </c>
-      <c r="B28" s="25">
+      <c r="B28" s="33">
         <v>0.6527777777777778</v>
       </c>
-      <c r="C28" s="26" t="s">
+      <c r="C28" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="D28" s="26" t="s">
+      <c r="D28" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="E28" s="26" t="s">
+      <c r="E28" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="F28" s="26" t="s">
+      <c r="F28" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="G28" s="24">
+      <c r="G28" s="32">
         <v>17.0</v>
       </c>
-      <c r="H28" s="25">
+      <c r="H28" s="33">
         <v>0.6527777777777778</v>
       </c>
-      <c r="I28" s="26" t="s">
+      <c r="I28" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="J28" s="26" t="s">
+      <c r="J28" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="K28" s="26" t="s">
+      <c r="K28" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="L28" s="26" t="s">
+      <c r="L28" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="M28" s="24">
+      <c r="M28" s="32">
         <v>17.0</v>
       </c>
-      <c r="N28" s="25">
+      <c r="N28" s="33">
         <v>0.6527777777777778</v>
       </c>
-      <c r="O28" s="29" t="s">
+      <c r="O28" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="P28" s="29" t="s">
+      <c r="P28" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="Q28" s="29" t="s">
+      <c r="Q28" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="R28" s="50" t="s">
+      <c r="R28" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="S28" s="33">
+      <c r="S28" s="37">
         <v>17.0</v>
       </c>
-      <c r="T28" s="39">
+      <c r="T28" s="45">
         <v>0.6527777777777778</v>
       </c>
-      <c r="U28" s="33"/>
-      <c r="V28" s="33"/>
-      <c r="W28" s="33"/>
-      <c r="X28" s="33"/>
-      <c r="Y28" s="24">
+      <c r="U28" s="37"/>
+      <c r="V28" s="37"/>
+      <c r="W28" s="37"/>
+      <c r="X28" s="37"/>
+      <c r="Y28" s="32">
         <v>17.0</v>
       </c>
-      <c r="Z28" s="25">
+      <c r="Z28" s="33">
         <v>0.6527777777777778</v>
       </c>
-      <c r="AA28" s="26" t="s">
+      <c r="AA28" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="AB28" s="26" t="s">
+      <c r="AB28" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="AC28" s="26" t="s">
+      <c r="AC28" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="AD28" s="26" t="s">
+      <c r="AD28" s="34" t="s">
         <v>19</v>
       </c>
       <c r="AE28" s="27"/>
       <c r="AF28" s="27"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="24">
+      <c r="A29" s="32">
         <v>18.0</v>
       </c>
-      <c r="B29" s="25">
+      <c r="B29" s="33">
         <v>0.6666666666666666</v>
       </c>
-      <c r="C29" s="26" t="s">
+      <c r="C29" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="D29" s="26" t="s">
+      <c r="D29" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="E29" s="26" t="s">
+      <c r="E29" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="F29" s="26" t="s">
+      <c r="F29" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="G29" s="33">
+      <c r="G29" s="37">
         <v>18.0</v>
       </c>
-      <c r="H29" s="39">
+      <c r="H29" s="45">
         <v>0.6666666666666666</v>
       </c>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="33"/>
-      <c r="L29" s="33"/>
-      <c r="M29" s="24">
+      <c r="I29" s="37"/>
+      <c r="J29" s="37"/>
+      <c r="K29" s="37"/>
+      <c r="L29" s="37"/>
+      <c r="M29" s="32">
         <v>18.0</v>
       </c>
-      <c r="N29" s="25">
+      <c r="N29" s="33">
         <v>0.6666666666666666</v>
       </c>
-      <c r="O29" s="26" t="s">
+      <c r="O29" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="P29" s="26" t="s">
+      <c r="P29" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="Q29" s="26" t="s">
+      <c r="Q29" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="R29" s="26" t="s">
+      <c r="R29" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="S29" s="29">
+      <c r="S29" s="38">
         <v>18.0</v>
       </c>
-      <c r="T29" s="30">
+      <c r="T29" s="39">
         <v>0.6666666666666666</v>
       </c>
-      <c r="U29" s="42" t="s">
+      <c r="U29" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="V29" s="42" t="s">
+      <c r="V29" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="W29" s="42" t="s">
+      <c r="W29" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="X29" s="50" t="s">
+      <c r="X29" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="Y29" s="24">
+      <c r="Y29" s="32">
         <v>18.0</v>
       </c>
-      <c r="Z29" s="25">
+      <c r="Z29" s="33">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AA29" s="42" t="s">
+      <c r="AA29" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="AB29" s="42" t="s">
+      <c r="AB29" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="AC29" s="42" t="s">
+      <c r="AC29" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="AD29" s="51" t="s">
+      <c r="AD29" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="AE29" s="52"/>
-      <c r="AF29" s="53"/>
+      <c r="AE29" s="58"/>
+      <c r="AF29" s="59"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="24">
+      <c r="A30" s="32">
         <v>19.0</v>
       </c>
-      <c r="B30" s="25">
+      <c r="B30" s="33">
         <v>0.6805555555555556</v>
       </c>
-      <c r="C30" s="26" t="s">
+      <c r="C30" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="26" t="s">
+      <c r="D30" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="E30" s="26" t="s">
+      <c r="E30" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="F30" s="24"/>
-      <c r="G30" s="24">
+      <c r="F30" s="32"/>
+      <c r="G30" s="32">
         <v>19.0</v>
       </c>
-      <c r="H30" s="25">
+      <c r="H30" s="33">
         <v>0.6805555555555556</v>
       </c>
-      <c r="I30" s="26" t="s">
+      <c r="I30" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="J30" s="26" t="s">
+      <c r="J30" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="K30" s="26" t="s">
+      <c r="K30" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="L30" s="26" t="s">
+      <c r="L30" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="M30" s="24">
+      <c r="M30" s="32">
         <v>19.0</v>
       </c>
-      <c r="N30" s="25">
+      <c r="N30" s="33">
         <v>0.6805555555555556</v>
       </c>
-      <c r="O30" s="26" t="s">
+      <c r="O30" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="P30" s="26" t="s">
+      <c r="P30" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="Q30" s="26" t="s">
+      <c r="Q30" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="R30" s="26" t="s">
-        <v>19</v>
+      <c r="R30" s="34" t="s">
+        <v>59</v>
       </c>
       <c r="S30" s="22">
         <v>19.0</v>
@@ -2807,22 +2831,22 @@
       <c r="AF30" s="27"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="24">
+      <c r="A31" s="32">
         <v>20.0</v>
       </c>
-      <c r="B31" s="25">
+      <c r="B31" s="33">
         <v>0.6944444444444444</v>
       </c>
-      <c r="C31" s="26" t="s">
+      <c r="C31" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="D31" s="26" t="s">
+      <c r="D31" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="E31" s="26" t="s">
+      <c r="E31" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="F31" s="26" t="s">
+      <c r="F31" s="34" t="s">
         <v>16</v>
       </c>
       <c r="G31" s="22">
@@ -2835,18 +2859,18 @@
       <c r="J31" s="22"/>
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
-      <c r="M31" s="54">
+      <c r="M31" s="60">
         <v>20.0</v>
       </c>
-      <c r="N31" s="55">
+      <c r="N31" s="61">
         <v>0.6944444444444444</v>
       </c>
-      <c r="O31" s="56" t="s">
+      <c r="O31" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="P31" s="57"/>
-      <c r="Q31" s="57"/>
-      <c r="R31" s="58"/>
+      <c r="P31" s="63"/>
+      <c r="Q31" s="63"/>
+      <c r="R31" s="64"/>
       <c r="S31" s="22">
         <v>20.0</v>
       </c>
@@ -2891,18 +2915,18 @@
       <c r="J32" s="22"/>
       <c r="K32" s="22"/>
       <c r="L32" s="22"/>
-      <c r="M32" s="54">
+      <c r="M32" s="60">
         <v>21.0</v>
       </c>
-      <c r="N32" s="55">
+      <c r="N32" s="61">
         <v>0.7083333333333334</v>
       </c>
-      <c r="O32" s="56" t="s">
+      <c r="O32" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="P32" s="57"/>
-      <c r="Q32" s="57"/>
-      <c r="R32" s="58"/>
+      <c r="P32" s="63"/>
+      <c r="Q32" s="63"/>
+      <c r="R32" s="64"/>
       <c r="S32" s="22">
         <v>21.0</v>
       </c>
@@ -2947,18 +2971,18 @@
       <c r="J33" s="22"/>
       <c r="K33" s="22"/>
       <c r="L33" s="22"/>
-      <c r="M33" s="54">
+      <c r="M33" s="60">
         <v>22.0</v>
       </c>
-      <c r="N33" s="55">
+      <c r="N33" s="61">
         <v>0.7222222222222222</v>
       </c>
-      <c r="O33" s="56" t="s">
+      <c r="O33" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="P33" s="57"/>
-      <c r="Q33" s="57"/>
-      <c r="R33" s="58"/>
+      <c r="P33" s="63"/>
+      <c r="Q33" s="63"/>
+      <c r="R33" s="64"/>
       <c r="S33" s="22">
         <v>22.0</v>
       </c>
@@ -3005,18 +3029,18 @@
       <c r="J34" s="22"/>
       <c r="K34" s="22"/>
       <c r="L34" s="22"/>
-      <c r="M34" s="54">
+      <c r="M34" s="60">
         <v>23.0</v>
       </c>
-      <c r="N34" s="55">
+      <c r="N34" s="61">
         <v>0.7361111111111112</v>
       </c>
-      <c r="O34" s="56" t="s">
+      <c r="O34" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="P34" s="57"/>
-      <c r="Q34" s="57"/>
-      <c r="R34" s="58"/>
+      <c r="P34" s="63"/>
+      <c r="Q34" s="63"/>
+      <c r="R34" s="64"/>
       <c r="S34" s="22">
         <v>23.0</v>
       </c>
@@ -3061,18 +3085,18 @@
       <c r="J35" s="22"/>
       <c r="K35" s="22"/>
       <c r="L35" s="22"/>
-      <c r="M35" s="54">
+      <c r="M35" s="60">
         <v>24.0</v>
       </c>
-      <c r="N35" s="55">
+      <c r="N35" s="61">
         <v>0.75</v>
       </c>
-      <c r="O35" s="56" t="s">
+      <c r="O35" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="P35" s="57"/>
-      <c r="Q35" s="57"/>
-      <c r="R35" s="58"/>
+      <c r="P35" s="63"/>
+      <c r="Q35" s="63"/>
+      <c r="R35" s="64"/>
       <c r="S35" s="22">
         <v>24.0</v>
       </c>
@@ -3117,18 +3141,18 @@
       <c r="J36" s="22"/>
       <c r="K36" s="22"/>
       <c r="L36" s="22"/>
-      <c r="M36" s="54">
+      <c r="M36" s="60">
         <v>25.0</v>
       </c>
-      <c r="N36" s="55">
+      <c r="N36" s="61">
         <v>0.7638888888888888</v>
       </c>
-      <c r="O36" s="56" t="s">
+      <c r="O36" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="P36" s="57"/>
-      <c r="Q36" s="57"/>
-      <c r="R36" s="58"/>
+      <c r="P36" s="63"/>
+      <c r="Q36" s="63"/>
+      <c r="R36" s="64"/>
       <c r="S36" s="22">
         <v>25.0</v>
       </c>
@@ -3173,18 +3197,18 @@
       <c r="J37" s="22"/>
       <c r="K37" s="22"/>
       <c r="L37" s="22"/>
-      <c r="M37" s="54">
+      <c r="M37" s="60">
         <v>26.0</v>
       </c>
-      <c r="N37" s="55">
+      <c r="N37" s="61">
         <v>0.7777777777777778</v>
       </c>
-      <c r="O37" s="56" t="s">
+      <c r="O37" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="P37" s="57"/>
-      <c r="Q37" s="57"/>
-      <c r="R37" s="58"/>
+      <c r="P37" s="63"/>
+      <c r="Q37" s="63"/>
+      <c r="R37" s="64"/>
       <c r="S37" s="22">
         <v>26.0</v>
       </c>
@@ -3229,18 +3253,18 @@
       <c r="J38" s="22"/>
       <c r="K38" s="22"/>
       <c r="L38" s="22"/>
-      <c r="M38" s="54">
+      <c r="M38" s="60">
         <v>27.0</v>
       </c>
-      <c r="N38" s="55">
+      <c r="N38" s="61">
         <v>0.7916666666666666</v>
       </c>
-      <c r="O38" s="56" t="s">
+      <c r="O38" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="P38" s="57"/>
-      <c r="Q38" s="57"/>
-      <c r="R38" s="58"/>
+      <c r="P38" s="63"/>
+      <c r="Q38" s="63"/>
+      <c r="R38" s="64"/>
       <c r="S38" s="22">
         <v>27.0</v>
       </c>
@@ -3285,18 +3309,18 @@
       <c r="J39" s="22"/>
       <c r="K39" s="22"/>
       <c r="L39" s="22"/>
-      <c r="M39" s="54">
+      <c r="M39" s="60">
         <v>28.0</v>
       </c>
-      <c r="N39" s="55">
+      <c r="N39" s="61">
         <v>0.8055555555555556</v>
       </c>
-      <c r="O39" s="56" t="s">
+      <c r="O39" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="P39" s="57"/>
-      <c r="Q39" s="57"/>
-      <c r="R39" s="58"/>
+      <c r="P39" s="63"/>
+      <c r="Q39" s="63"/>
+      <c r="R39" s="64"/>
       <c r="S39" s="22">
         <v>28.0</v>
       </c>
@@ -3316,7 +3340,7 @@
       <c r="AA39" s="22"/>
       <c r="AB39" s="22"/>
       <c r="AC39" s="22"/>
-      <c r="AD39" s="59"/>
+      <c r="AD39" s="65"/>
       <c r="AE39" s="1"/>
       <c r="AF39" s="1"/>
     </row>
@@ -3341,18 +3365,18 @@
       <c r="J40" s="22"/>
       <c r="K40" s="22"/>
       <c r="L40" s="22"/>
-      <c r="M40" s="54">
+      <c r="M40" s="60">
         <v>29.0</v>
       </c>
-      <c r="N40" s="55">
+      <c r="N40" s="61">
         <v>0.8194444444444444</v>
       </c>
-      <c r="O40" s="56" t="s">
+      <c r="O40" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="P40" s="57"/>
-      <c r="Q40" s="57"/>
-      <c r="R40" s="58"/>
+      <c r="P40" s="63"/>
+      <c r="Q40" s="63"/>
+      <c r="R40" s="64"/>
       <c r="S40" s="22">
         <v>29.0</v>
       </c>
@@ -3372,7 +3396,7 @@
       <c r="AA40" s="22"/>
       <c r="AB40" s="22"/>
       <c r="AC40" s="22"/>
-      <c r="AD40" s="59"/>
+      <c r="AD40" s="65"/>
       <c r="AE40" s="1"/>
       <c r="AF40" s="1"/>
     </row>
@@ -3397,18 +3421,18 @@
       <c r="J41" s="22"/>
       <c r="K41" s="22"/>
       <c r="L41" s="22"/>
-      <c r="M41" s="54">
+      <c r="M41" s="60">
         <v>30.0</v>
       </c>
-      <c r="N41" s="55">
+      <c r="N41" s="61">
         <v>0.8333333333333334</v>
       </c>
-      <c r="O41" s="56" t="s">
+      <c r="O41" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="P41" s="57"/>
-      <c r="Q41" s="57"/>
-      <c r="R41" s="58"/>
+      <c r="P41" s="63"/>
+      <c r="Q41" s="63"/>
+      <c r="R41" s="64"/>
       <c r="S41" s="22">
         <v>30.0</v>
       </c>
@@ -3428,7 +3452,7 @@
       <c r="AA41" s="22"/>
       <c r="AB41" s="22"/>
       <c r="AC41" s="22"/>
-      <c r="AD41" s="59"/>
+      <c r="AD41" s="65"/>
       <c r="AE41" s="1"/>
       <c r="AF41" s="1"/>
     </row>
@@ -3453,18 +3477,18 @@
       <c r="J42" s="22"/>
       <c r="K42" s="22"/>
       <c r="L42" s="22"/>
-      <c r="M42" s="54">
+      <c r="M42" s="60">
         <v>31.0</v>
       </c>
-      <c r="N42" s="55">
+      <c r="N42" s="61">
         <v>0.8472222222222222</v>
       </c>
-      <c r="O42" s="56" t="s">
+      <c r="O42" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="P42" s="57"/>
-      <c r="Q42" s="57"/>
-      <c r="R42" s="58"/>
+      <c r="P42" s="63"/>
+      <c r="Q42" s="63"/>
+      <c r="R42" s="64"/>
       <c r="S42" s="22">
         <v>31.0</v>
       </c>
@@ -3484,63 +3508,63 @@
       <c r="AA42" s="22"/>
       <c r="AB42" s="22"/>
       <c r="AC42" s="22"/>
-      <c r="AD42" s="59"/>
+      <c r="AD42" s="65"/>
       <c r="AE42" s="1"/>
       <c r="AF42" s="1"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="60">
+      <c r="A43" s="66">
         <v>32.0</v>
       </c>
-      <c r="B43" s="61">
+      <c r="B43" s="67">
         <v>0.8611111111111112</v>
       </c>
-      <c r="C43" s="60"/>
-      <c r="D43" s="60"/>
-      <c r="E43" s="60"/>
-      <c r="F43" s="60"/>
-      <c r="G43" s="60">
+      <c r="C43" s="66"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66">
         <v>32.0</v>
       </c>
-      <c r="H43" s="61">
+      <c r="H43" s="67">
         <v>0.8611111111111112</v>
       </c>
-      <c r="I43" s="60"/>
-      <c r="J43" s="60"/>
-      <c r="K43" s="60"/>
-      <c r="L43" s="60"/>
-      <c r="M43" s="62">
+      <c r="I43" s="66"/>
+      <c r="J43" s="66"/>
+      <c r="K43" s="66"/>
+      <c r="L43" s="66"/>
+      <c r="M43" s="68">
         <v>32.0</v>
       </c>
-      <c r="N43" s="63">
+      <c r="N43" s="69">
         <v>0.8611111111111112</v>
       </c>
-      <c r="O43" s="64" t="s">
+      <c r="O43" s="70" t="s">
         <v>78</v>
       </c>
-      <c r="P43" s="65"/>
-      <c r="Q43" s="65"/>
-      <c r="R43" s="66"/>
-      <c r="S43" s="60">
+      <c r="P43" s="71"/>
+      <c r="Q43" s="71"/>
+      <c r="R43" s="72"/>
+      <c r="S43" s="66">
         <v>32.0</v>
       </c>
-      <c r="T43" s="61">
+      <c r="T43" s="67">
         <v>0.8611111111111112</v>
       </c>
-      <c r="U43" s="60"/>
-      <c r="V43" s="60"/>
-      <c r="W43" s="60"/>
-      <c r="X43" s="60"/>
-      <c r="Y43" s="60">
+      <c r="U43" s="66"/>
+      <c r="V43" s="66"/>
+      <c r="W43" s="66"/>
+      <c r="X43" s="66"/>
+      <c r="Y43" s="66">
         <v>32.0</v>
       </c>
-      <c r="Z43" s="61">
+      <c r="Z43" s="67">
         <v>0.8611111111111112</v>
       </c>
-      <c r="AA43" s="60"/>
-      <c r="AB43" s="60"/>
-      <c r="AC43" s="60"/>
-      <c r="AD43" s="67"/>
+      <c r="AA43" s="66"/>
+      <c r="AB43" s="66"/>
+      <c r="AC43" s="66"/>
+      <c r="AD43" s="73"/>
       <c r="AE43" s="1"/>
       <c r="AF43" s="1"/>
     </row>

--- a/file_wisuda_4okt.xlsx
+++ b/file_wisuda_4okt.xlsx
@@ -403,12 +403,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF9900"/>
-        <bgColor rgb="FFFF9900"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF00FF00"/>
         <bgColor rgb="FF00FF00"/>
       </patternFill>
@@ -417,6 +411,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF9900"/>
+        <bgColor rgb="FFFF9900"/>
       </patternFill>
     </fill>
   </fills>
@@ -560,7 +560,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="73">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -651,95 +651,92 @@
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="10" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="13" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="10" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="10" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="6" fillId="10" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="5" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="12" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="6" fillId="10" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="10" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="5" fillId="10" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="7" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="12" fontId="13" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="4" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="10" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="8" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="6" fillId="11" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf borderId="5" fillId="12" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="6" fillId="11" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="11" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="7" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="8" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="10" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="8" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="8" fillId="12" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="9" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -753,13 +750,13 @@
     <xf borderId="10" fillId="0" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="10" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="10" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="10" fillId="10" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="10" fillId="12" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="11" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="11" fillId="12" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="12" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -787,7 +784,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -815,7 +812,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -871,7 +868,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -927,7 +924,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1628,7 +1625,7 @@
       <c r="Q15" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="R15" s="31" t="s">
+      <c r="R15" s="29" t="s">
         <v>19</v>
       </c>
       <c r="S15" s="22">
@@ -1763,22 +1760,22 @@
       <c r="AF17" s="27"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="32">
+      <c r="A18" s="31">
         <v>7.0</v>
       </c>
-      <c r="B18" s="33">
+      <c r="B18" s="32">
         <v>0.5</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C18" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="34" t="s">
+      <c r="D18" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="34" t="s">
+      <c r="E18" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="F18" s="34" t="s">
+      <c r="F18" s="33" t="s">
         <v>19</v>
       </c>
       <c r="G18" s="22">
@@ -1825,680 +1822,680 @@
       <c r="AF18" s="27"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="32">
+      <c r="A19" s="31">
         <v>8.0</v>
       </c>
-      <c r="B19" s="33">
+      <c r="B19" s="32">
         <v>0.5208333333333334</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="D19" s="34" t="s">
+      <c r="D19" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="34" t="s">
+      <c r="E19" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="34" t="s">
+      <c r="F19" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="G19" s="35">
+      <c r="G19" s="34">
         <v>8.0</v>
       </c>
-      <c r="H19" s="36">
+      <c r="H19" s="35">
         <v>0.5208333333333334</v>
       </c>
-      <c r="I19" s="35"/>
-      <c r="J19" s="37"/>
-      <c r="K19" s="37"/>
-      <c r="L19" s="37"/>
-      <c r="M19" s="38">
+      <c r="I19" s="34"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="36"/>
+      <c r="L19" s="36"/>
+      <c r="M19" s="37">
         <v>8.0</v>
       </c>
-      <c r="N19" s="39">
+      <c r="N19" s="38">
         <v>0.5208333333333334</v>
       </c>
-      <c r="O19" s="40" t="s">
+      <c r="O19" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="P19" s="38" t="s">
+      <c r="P19" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="Q19" s="38" t="s">
+      <c r="Q19" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="R19" s="40" t="s">
+      <c r="R19" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="S19" s="32">
+      <c r="S19" s="31">
         <v>8.0</v>
       </c>
-      <c r="T19" s="33">
+      <c r="T19" s="32">
         <v>0.5208333333333334</v>
       </c>
-      <c r="U19" s="41" t="s">
+      <c r="U19" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="V19" s="41" t="s">
+      <c r="V19" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="W19" s="41" t="s">
+      <c r="W19" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="X19" s="41" t="s">
+      <c r="X19" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="Y19" s="38">
+      <c r="Y19" s="37">
         <v>8.0</v>
       </c>
-      <c r="Z19" s="39">
+      <c r="Z19" s="38">
         <v>0.5208333333333334</v>
       </c>
-      <c r="AA19" s="42" t="s">
+      <c r="AA19" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="AB19" s="43" t="s">
+      <c r="AB19" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="AC19" s="43" t="s">
+      <c r="AC19" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="AD19" s="38" t="s">
+      <c r="AD19" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="AE19" s="44"/>
-      <c r="AF19" s="44"/>
+      <c r="AE19" s="43"/>
+      <c r="AF19" s="43"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="32">
+      <c r="A20" s="31">
         <v>9.0</v>
       </c>
-      <c r="B20" s="33">
+      <c r="B20" s="32">
         <v>0.5416666666666666</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="34" t="s">
+      <c r="D20" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="34" t="s">
+      <c r="E20" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="34"/>
-      <c r="G20" s="37">
+      <c r="F20" s="33"/>
+      <c r="G20" s="36">
         <v>9.0</v>
       </c>
-      <c r="H20" s="45">
+      <c r="H20" s="44">
         <v>0.5416666666666666</v>
       </c>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="46"/>
-      <c r="L20" s="46"/>
-      <c r="M20" s="32">
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="45"/>
+      <c r="M20" s="31">
         <v>9.0</v>
       </c>
-      <c r="N20" s="33">
+      <c r="N20" s="32">
         <v>0.5416666666666666</v>
       </c>
-      <c r="O20" s="47" t="s">
+      <c r="O20" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="P20" s="48" t="s">
+      <c r="P20" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="Q20" s="48" t="s">
+      <c r="Q20" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="R20" s="34" t="s">
+      <c r="R20" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="S20" s="32">
+      <c r="S20" s="31">
         <v>9.0</v>
       </c>
-      <c r="T20" s="33">
+      <c r="T20" s="32">
         <v>0.5416666666666666</v>
       </c>
-      <c r="U20" s="34" t="s">
+      <c r="U20" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="V20" s="34" t="s">
+      <c r="V20" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="W20" s="34" t="s">
+      <c r="W20" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="X20" s="34" t="s">
+      <c r="X20" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="Y20" s="38">
+      <c r="Y20" s="37">
         <v>9.0</v>
       </c>
-      <c r="Z20" s="39">
+      <c r="Z20" s="38">
         <v>0.5416666666666666</v>
       </c>
-      <c r="AA20" s="42" t="s">
+      <c r="AA20" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="AB20" s="43" t="s">
+      <c r="AB20" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="AC20" s="43" t="s">
+      <c r="AC20" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="AD20" s="49"/>
-      <c r="AE20" s="50"/>
-      <c r="AF20" s="50"/>
+      <c r="AD20" s="48"/>
+      <c r="AE20" s="49"/>
+      <c r="AF20" s="49"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="32">
+      <c r="A21" s="31">
         <v>10.0</v>
       </c>
-      <c r="B21" s="33">
+      <c r="B21" s="32">
         <v>0.5555555555555556</v>
       </c>
-      <c r="C21" s="34" t="s">
+      <c r="C21" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="34" t="s">
+      <c r="D21" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="34" t="s">
+      <c r="E21" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="F21" s="34" t="s">
+      <c r="F21" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="G21" s="32">
+      <c r="G21" s="31">
         <v>10.0</v>
       </c>
-      <c r="H21" s="33">
+      <c r="H21" s="32">
         <v>0.5555555555555556</v>
       </c>
-      <c r="I21" s="34" t="s">
+      <c r="I21" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="J21" s="34" t="s">
+      <c r="J21" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="K21" s="34" t="s">
+      <c r="K21" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="L21" s="34" t="s">
+      <c r="L21" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="M21" s="32">
+      <c r="M21" s="31">
         <v>10.0</v>
       </c>
-      <c r="N21" s="33">
+      <c r="N21" s="32">
         <v>0.5555555555555556</v>
       </c>
-      <c r="O21" s="51" t="s">
+      <c r="O21" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="P21" s="52" t="s">
+      <c r="P21" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Q21" s="38" t="s">
+      <c r="Q21" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="R21" s="38" t="s">
+      <c r="R21" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="S21" s="32">
+      <c r="S21" s="31">
         <v>10.0</v>
       </c>
-      <c r="T21" s="33">
+      <c r="T21" s="32">
         <v>0.5555555555555556</v>
       </c>
-      <c r="U21" s="34" t="s">
+      <c r="U21" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="V21" s="34" t="s">
+      <c r="V21" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="W21" s="34" t="s">
+      <c r="W21" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="X21" s="32"/>
-      <c r="Y21" s="32">
+      <c r="X21" s="31"/>
+      <c r="Y21" s="31">
         <v>10.0</v>
       </c>
-      <c r="Z21" s="33">
+      <c r="Z21" s="32">
         <v>0.5555555555555556</v>
       </c>
-      <c r="AA21" s="34" t="s">
+      <c r="AA21" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="AB21" s="34" t="s">
+      <c r="AB21" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="AC21" s="34" t="s">
+      <c r="AC21" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="AD21" s="32"/>
+      <c r="AD21" s="31"/>
       <c r="AE21" s="27"/>
       <c r="AF21" s="27"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="32">
+      <c r="A22" s="31">
         <v>11.0</v>
       </c>
-      <c r="B22" s="33">
+      <c r="B22" s="32">
         <v>0.5694444444444444</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="34" t="s">
+      <c r="D22" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="E22" s="34" t="s">
+      <c r="E22" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="F22" s="34" t="s">
+      <c r="F22" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="G22" s="37">
+      <c r="G22" s="36">
         <v>11.0</v>
       </c>
-      <c r="H22" s="45">
+      <c r="H22" s="44">
         <v>0.5694444444444444</v>
       </c>
-      <c r="I22" s="37"/>
-      <c r="J22" s="37"/>
-      <c r="K22" s="37"/>
-      <c r="L22" s="37"/>
-      <c r="M22" s="32">
+      <c r="I22" s="36"/>
+      <c r="J22" s="36"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="31">
         <v>11.0</v>
       </c>
-      <c r="N22" s="33">
+      <c r="N22" s="32">
         <v>0.5694444444444444</v>
       </c>
-      <c r="O22" s="47" t="s">
+      <c r="O22" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="P22" s="34" t="s">
+      <c r="P22" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="Q22" s="34" t="s">
+      <c r="Q22" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="R22" s="32"/>
-      <c r="S22" s="32">
+      <c r="R22" s="31"/>
+      <c r="S22" s="31">
         <v>11.0</v>
       </c>
-      <c r="T22" s="33">
+      <c r="T22" s="32">
         <v>0.5694444444444444</v>
       </c>
-      <c r="U22" s="34" t="s">
+      <c r="U22" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="V22" s="34" t="s">
+      <c r="V22" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="W22" s="34" t="s">
+      <c r="W22" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="X22" s="34" t="s">
+      <c r="X22" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="Y22" s="32">
+      <c r="Y22" s="31">
         <v>11.0</v>
       </c>
-      <c r="Z22" s="33">
+      <c r="Z22" s="32">
         <v>0.5694444444444444</v>
       </c>
-      <c r="AA22" s="34" t="s">
+      <c r="AA22" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="AB22" s="34" t="s">
+      <c r="AB22" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="AC22" s="34" t="s">
+      <c r="AC22" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="AD22" s="34" t="s">
+      <c r="AD22" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="AE22" s="53"/>
-      <c r="AF22" s="53"/>
+      <c r="AE22" s="52"/>
+      <c r="AF22" s="52"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="38">
+      <c r="A23" s="37">
         <v>13.0</v>
       </c>
-      <c r="B23" s="33">
+      <c r="B23" s="32">
         <v>0.5833333333333334</v>
       </c>
-      <c r="C23" s="38" t="s">
+      <c r="C23" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="38" t="s">
+      <c r="D23" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="38" t="s">
+      <c r="E23" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="F23" s="38" t="s">
+      <c r="F23" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="G23" s="37">
+      <c r="G23" s="36">
         <v>12.0</v>
       </c>
-      <c r="H23" s="45">
+      <c r="H23" s="44">
         <v>0.5833333333333334</v>
       </c>
-      <c r="I23" s="37"/>
-      <c r="J23" s="54"/>
-      <c r="K23" s="37"/>
-      <c r="L23" s="37"/>
-      <c r="M23" s="32">
+      <c r="I23" s="36"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="36"/>
+      <c r="L23" s="36"/>
+      <c r="M23" s="31">
         <v>12.0</v>
       </c>
-      <c r="N23" s="33">
+      <c r="N23" s="32">
         <v>0.5833333333333334</v>
       </c>
-      <c r="O23" s="55" t="s">
+      <c r="O23" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="P23" s="38" t="s">
+      <c r="P23" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="Q23" s="38" t="s">
+      <c r="Q23" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="R23" s="38" t="s">
+      <c r="R23" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="S23" s="32">
+      <c r="S23" s="31">
         <v>12.0</v>
       </c>
-      <c r="T23" s="33">
+      <c r="T23" s="32">
         <v>0.5833333333333334</v>
       </c>
-      <c r="U23" s="34" t="s">
+      <c r="U23" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="V23" s="34" t="s">
+      <c r="V23" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="W23" s="34" t="s">
+      <c r="W23" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="X23" s="34" t="s">
+      <c r="X23" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="Y23" s="32">
+      <c r="Y23" s="31">
         <v>12.0</v>
       </c>
-      <c r="Z23" s="33">
+      <c r="Z23" s="32">
         <v>0.5833333333333334</v>
       </c>
-      <c r="AA23" s="38" t="s">
+      <c r="AA23" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="AB23" s="38" t="s">
+      <c r="AB23" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="AC23" s="38" t="s">
+      <c r="AC23" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="AD23" s="51"/>
+      <c r="AD23" s="50"/>
       <c r="AE23" s="27"/>
       <c r="AF23" s="27"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="34">
+      <c r="A24" s="33">
         <v>14.0</v>
       </c>
-      <c r="B24" s="33">
+      <c r="B24" s="32">
         <v>0.5972222222222222</v>
       </c>
-      <c r="C24" s="34" t="s">
+      <c r="C24" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="34" t="s">
+      <c r="D24" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="34" t="s">
+      <c r="E24" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="F24" s="34" t="s">
+      <c r="F24" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="G24" s="32">
+      <c r="G24" s="31">
         <v>13.0</v>
       </c>
-      <c r="H24" s="33">
+      <c r="H24" s="32">
         <v>0.5972222222222222</v>
       </c>
-      <c r="I24" s="34" t="s">
+      <c r="I24" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="J24" s="34" t="s">
+      <c r="J24" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="K24" s="34" t="s">
+      <c r="K24" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="L24" s="34" t="s">
+      <c r="L24" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="M24" s="32">
+      <c r="M24" s="31">
         <v>13.0</v>
       </c>
-      <c r="N24" s="33">
+      <c r="N24" s="32">
         <v>0.5972222222222222</v>
       </c>
-      <c r="O24" s="38" t="s">
+      <c r="O24" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="P24" s="38" t="s">
+      <c r="P24" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="Q24" s="38" t="s">
+      <c r="Q24" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="R24" s="38" t="s">
+      <c r="R24" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="S24" s="32">
+      <c r="S24" s="31">
         <v>13.0</v>
       </c>
-      <c r="T24" s="33">
+      <c r="T24" s="32">
         <v>0.5972222222222222</v>
       </c>
-      <c r="U24" s="34" t="s">
+      <c r="U24" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="V24" s="34" t="s">
+      <c r="V24" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="W24" s="34" t="s">
+      <c r="W24" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="X24" s="34" t="s">
+      <c r="X24" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="Y24" s="37">
+      <c r="Y24" s="36">
         <v>13.0</v>
       </c>
-      <c r="Z24" s="45">
+      <c r="Z24" s="44">
         <v>0.5972222222222222</v>
       </c>
-      <c r="AA24" s="37"/>
-      <c r="AB24" s="37"/>
-      <c r="AC24" s="37"/>
-      <c r="AD24" s="37"/>
+      <c r="AA24" s="36"/>
+      <c r="AB24" s="36"/>
+      <c r="AC24" s="36"/>
+      <c r="AD24" s="36"/>
       <c r="AE24" s="27"/>
       <c r="AF24" s="27"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="37">
+      <c r="A25" s="36">
         <v>14.0</v>
       </c>
-      <c r="B25" s="45">
+      <c r="B25" s="44">
         <v>0.6111111111111112</v>
       </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="32">
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="31">
         <v>14.0</v>
       </c>
-      <c r="H25" s="33">
+      <c r="H25" s="32">
         <v>0.6111111111111112</v>
       </c>
-      <c r="I25" s="34" t="s">
+      <c r="I25" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="J25" s="34" t="s">
+      <c r="J25" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="K25" s="34" t="s">
+      <c r="K25" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="L25" s="34" t="s">
+      <c r="L25" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="M25" s="32">
+      <c r="M25" s="31">
         <v>14.0</v>
       </c>
-      <c r="N25" s="33">
+      <c r="N25" s="32">
         <v>0.6111111111111112</v>
       </c>
-      <c r="O25" s="34" t="s">
+      <c r="O25" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="P25" s="34" t="s">
+      <c r="P25" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="Q25" s="34" t="s">
+      <c r="Q25" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="R25" s="32"/>
-      <c r="S25" s="32">
+      <c r="R25" s="31"/>
+      <c r="S25" s="31">
         <v>14.0</v>
       </c>
-      <c r="T25" s="33">
+      <c r="T25" s="32">
         <v>0.6111111111111112</v>
       </c>
-      <c r="U25" s="34" t="s">
+      <c r="U25" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="V25" s="34" t="s">
+      <c r="V25" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="W25" s="34" t="s">
+      <c r="W25" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="X25" s="34" t="s">
+      <c r="X25" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="Y25" s="32">
+      <c r="Y25" s="31">
         <v>14.0</v>
       </c>
-      <c r="Z25" s="33">
+      <c r="Z25" s="32">
         <v>0.6111111111111112</v>
       </c>
-      <c r="AA25" s="34" t="s">
+      <c r="AA25" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="AB25" s="34" t="s">
+      <c r="AB25" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="AC25" s="34" t="s">
+      <c r="AC25" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="AD25" s="34" t="s">
+      <c r="AD25" s="33" t="s">
         <v>19</v>
       </c>
       <c r="AE25" s="27"/>
       <c r="AF25" s="27"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="37">
+      <c r="A26" s="36">
         <v>15.0</v>
       </c>
-      <c r="B26" s="45">
+      <c r="B26" s="44">
         <v>0.625</v>
       </c>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="32">
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="31">
         <v>15.0</v>
       </c>
-      <c r="H26" s="33">
+      <c r="H26" s="32">
         <v>0.625</v>
       </c>
-      <c r="I26" s="34" t="s">
+      <c r="I26" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="J26" s="34" t="s">
+      <c r="J26" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="K26" s="34" t="s">
+      <c r="K26" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="L26" s="34" t="s">
+      <c r="L26" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="M26" s="32">
+      <c r="M26" s="31">
         <v>15.0</v>
       </c>
-      <c r="N26" s="33">
+      <c r="N26" s="32">
         <v>0.625</v>
       </c>
-      <c r="O26" s="34" t="s">
+      <c r="O26" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="P26" s="34" t="s">
+      <c r="P26" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="Q26" s="34" t="s">
+      <c r="Q26" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="R26" s="32"/>
-      <c r="S26" s="32">
+      <c r="R26" s="31"/>
+      <c r="S26" s="31">
         <v>15.0</v>
       </c>
-      <c r="T26" s="33">
+      <c r="T26" s="32">
         <v>0.625</v>
       </c>
-      <c r="U26" s="34" t="s">
+      <c r="U26" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="V26" s="34" t="s">
+      <c r="V26" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="W26" s="34" t="s">
+      <c r="W26" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="X26" s="34" t="s">
+      <c r="X26" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="Y26" s="32">
+      <c r="Y26" s="31">
         <v>15.0</v>
       </c>
-      <c r="Z26" s="33">
+      <c r="Z26" s="32">
         <v>0.625</v>
       </c>
-      <c r="AA26" s="34" t="s">
+      <c r="AA26" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="AB26" s="34" t="s">
+      <c r="AB26" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="AC26" s="34" t="s">
+      <c r="AC26" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="AD26" s="34" t="s">
+      <c r="AD26" s="33" t="s">
         <v>59</v>
       </c>
       <c r="AE26" s="27"/>
@@ -2515,296 +2512,296 @@
       <c r="D27" s="28"/>
       <c r="E27" s="28"/>
       <c r="F27" s="28"/>
-      <c r="G27" s="32">
+      <c r="G27" s="31">
         <v>16.0</v>
       </c>
-      <c r="H27" s="33">
+      <c r="H27" s="32">
         <v>0.6388888888888888</v>
       </c>
-      <c r="I27" s="34" t="s">
+      <c r="I27" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="J27" s="34" t="s">
+      <c r="J27" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="K27" s="34" t="s">
+      <c r="K27" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="L27" s="34" t="s">
+      <c r="L27" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="M27" s="32">
+      <c r="M27" s="31">
         <v>16.0</v>
       </c>
-      <c r="N27" s="33">
+      <c r="N27" s="32">
         <v>0.6388888888888888</v>
       </c>
-      <c r="O27" s="34" t="s">
+      <c r="O27" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="P27" s="34" t="s">
+      <c r="P27" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="Q27" s="34" t="s">
+      <c r="Q27" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="R27" s="34" t="s">
+      <c r="R27" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="S27" s="37">
+      <c r="S27" s="36">
         <v>16.0</v>
       </c>
-      <c r="T27" s="45">
+      <c r="T27" s="44">
         <v>0.6388888888888888</v>
       </c>
-      <c r="U27" s="37"/>
-      <c r="V27" s="37"/>
-      <c r="W27" s="37"/>
-      <c r="X27" s="37"/>
-      <c r="Y27" s="32">
+      <c r="U27" s="36"/>
+      <c r="V27" s="36"/>
+      <c r="W27" s="36"/>
+      <c r="X27" s="36"/>
+      <c r="Y27" s="31">
         <v>16.0</v>
       </c>
-      <c r="Z27" s="33">
+      <c r="Z27" s="32">
         <v>0.6388888888888888</v>
       </c>
-      <c r="AA27" s="34" t="s">
+      <c r="AA27" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="AB27" s="34" t="s">
+      <c r="AB27" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="AC27" s="34" t="s">
+      <c r="AC27" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="AD27" s="34" t="s">
+      <c r="AD27" s="33" t="s">
         <v>19</v>
       </c>
       <c r="AE27" s="27"/>
       <c r="AF27" s="27"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="32">
+      <c r="A28" s="31">
         <v>17.0</v>
       </c>
-      <c r="B28" s="33">
+      <c r="B28" s="32">
         <v>0.6527777777777778</v>
       </c>
-      <c r="C28" s="34" t="s">
+      <c r="C28" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="D28" s="34" t="s">
+      <c r="D28" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="E28" s="34" t="s">
+      <c r="E28" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="F28" s="34" t="s">
+      <c r="F28" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="G28" s="32">
+      <c r="G28" s="31">
         <v>17.0</v>
       </c>
-      <c r="H28" s="33">
+      <c r="H28" s="32">
         <v>0.6527777777777778</v>
       </c>
-      <c r="I28" s="34" t="s">
+      <c r="I28" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="J28" s="34" t="s">
+      <c r="J28" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="K28" s="34" t="s">
+      <c r="K28" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="L28" s="34" t="s">
+      <c r="L28" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="M28" s="32">
+      <c r="M28" s="31">
         <v>17.0</v>
       </c>
-      <c r="N28" s="33">
+      <c r="N28" s="32">
         <v>0.6527777777777778</v>
       </c>
-      <c r="O28" s="38" t="s">
+      <c r="O28" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="P28" s="38" t="s">
+      <c r="P28" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="Q28" s="38" t="s">
+      <c r="Q28" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="R28" s="56" t="s">
+      <c r="R28" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="S28" s="37">
+      <c r="S28" s="36">
         <v>17.0</v>
       </c>
-      <c r="T28" s="45">
+      <c r="T28" s="44">
         <v>0.6527777777777778</v>
       </c>
-      <c r="U28" s="37"/>
-      <c r="V28" s="37"/>
-      <c r="W28" s="37"/>
-      <c r="X28" s="37"/>
-      <c r="Y28" s="32">
+      <c r="U28" s="36"/>
+      <c r="V28" s="36"/>
+      <c r="W28" s="36"/>
+      <c r="X28" s="36"/>
+      <c r="Y28" s="31">
         <v>17.0</v>
       </c>
-      <c r="Z28" s="33">
+      <c r="Z28" s="32">
         <v>0.6527777777777778</v>
       </c>
-      <c r="AA28" s="34" t="s">
+      <c r="AA28" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="AB28" s="34" t="s">
+      <c r="AB28" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="AC28" s="34" t="s">
+      <c r="AC28" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="AD28" s="34" t="s">
+      <c r="AD28" s="33" t="s">
         <v>19</v>
       </c>
       <c r="AE28" s="27"/>
       <c r="AF28" s="27"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="32">
+      <c r="A29" s="31">
         <v>18.0</v>
       </c>
-      <c r="B29" s="33">
+      <c r="B29" s="32">
         <v>0.6666666666666666</v>
       </c>
-      <c r="C29" s="34" t="s">
+      <c r="C29" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="D29" s="34" t="s">
+      <c r="D29" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="E29" s="34" t="s">
+      <c r="E29" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="F29" s="34" t="s">
+      <c r="F29" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="G29" s="37">
+      <c r="G29" s="36">
         <v>18.0</v>
       </c>
-      <c r="H29" s="45">
+      <c r="H29" s="44">
         <v>0.6666666666666666</v>
       </c>
-      <c r="I29" s="37"/>
-      <c r="J29" s="37"/>
-      <c r="K29" s="37"/>
-      <c r="L29" s="37"/>
-      <c r="M29" s="32">
+      <c r="I29" s="36"/>
+      <c r="J29" s="36"/>
+      <c r="K29" s="36"/>
+      <c r="L29" s="36"/>
+      <c r="M29" s="31">
         <v>18.0</v>
       </c>
-      <c r="N29" s="33">
+      <c r="N29" s="32">
         <v>0.6666666666666666</v>
       </c>
-      <c r="O29" s="34" t="s">
+      <c r="O29" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="P29" s="34" t="s">
+      <c r="P29" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="Q29" s="34" t="s">
+      <c r="Q29" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="R29" s="34" t="s">
+      <c r="R29" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="S29" s="38">
+      <c r="S29" s="37">
         <v>18.0</v>
       </c>
-      <c r="T29" s="39">
+      <c r="T29" s="38">
         <v>0.6666666666666666</v>
       </c>
-      <c r="U29" s="48" t="s">
+      <c r="U29" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="V29" s="48" t="s">
+      <c r="V29" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="W29" s="48" t="s">
+      <c r="W29" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="X29" s="56" t="s">
+      <c r="X29" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="Y29" s="32">
+      <c r="Y29" s="31">
         <v>18.0</v>
       </c>
-      <c r="Z29" s="33">
+      <c r="Z29" s="32">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AA29" s="48" t="s">
+      <c r="AA29" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="AB29" s="48" t="s">
+      <c r="AB29" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="AC29" s="48" t="s">
+      <c r="AC29" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="AD29" s="57" t="s">
+      <c r="AD29" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="AE29" s="58"/>
-      <c r="AF29" s="59"/>
+      <c r="AE29" s="57"/>
+      <c r="AF29" s="58"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="32">
+      <c r="A30" s="31">
         <v>19.0</v>
       </c>
-      <c r="B30" s="33">
+      <c r="B30" s="32">
         <v>0.6805555555555556</v>
       </c>
-      <c r="C30" s="34" t="s">
+      <c r="C30" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="34" t="s">
+      <c r="D30" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="E30" s="34" t="s">
+      <c r="E30" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32">
+      <c r="F30" s="31"/>
+      <c r="G30" s="31">
         <v>19.0</v>
       </c>
-      <c r="H30" s="33">
+      <c r="H30" s="32">
         <v>0.6805555555555556</v>
       </c>
-      <c r="I30" s="34" t="s">
+      <c r="I30" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="J30" s="34" t="s">
+      <c r="J30" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="K30" s="34" t="s">
+      <c r="K30" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="L30" s="34" t="s">
+      <c r="L30" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="M30" s="32">
+      <c r="M30" s="31">
         <v>19.0</v>
       </c>
-      <c r="N30" s="33">
+      <c r="N30" s="32">
         <v>0.6805555555555556</v>
       </c>
-      <c r="O30" s="34" t="s">
+      <c r="O30" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="P30" s="34" t="s">
+      <c r="P30" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="Q30" s="34" t="s">
+      <c r="Q30" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="R30" s="34" t="s">
+      <c r="R30" s="33" t="s">
         <v>59</v>
       </c>
       <c r="S30" s="22">
@@ -2831,22 +2828,22 @@
       <c r="AF30" s="27"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="32">
+      <c r="A31" s="31">
         <v>20.0</v>
       </c>
-      <c r="B31" s="33">
+      <c r="B31" s="32">
         <v>0.6944444444444444</v>
       </c>
-      <c r="C31" s="34" t="s">
+      <c r="C31" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="D31" s="34" t="s">
+      <c r="D31" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="E31" s="34" t="s">
+      <c r="E31" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="F31" s="34" t="s">
+      <c r="F31" s="33" t="s">
         <v>16</v>
       </c>
       <c r="G31" s="22">
@@ -2859,18 +2856,18 @@
       <c r="J31" s="22"/>
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
-      <c r="M31" s="60">
+      <c r="M31" s="59">
         <v>20.0</v>
       </c>
-      <c r="N31" s="61">
+      <c r="N31" s="60">
         <v>0.6944444444444444</v>
       </c>
-      <c r="O31" s="62" t="s">
+      <c r="O31" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="P31" s="63"/>
-      <c r="Q31" s="63"/>
-      <c r="R31" s="64"/>
+      <c r="P31" s="62"/>
+      <c r="Q31" s="62"/>
+      <c r="R31" s="63"/>
       <c r="S31" s="22">
         <v>20.0</v>
       </c>
@@ -2915,18 +2912,18 @@
       <c r="J32" s="22"/>
       <c r="K32" s="22"/>
       <c r="L32" s="22"/>
-      <c r="M32" s="60">
+      <c r="M32" s="59">
         <v>21.0</v>
       </c>
-      <c r="N32" s="61">
+      <c r="N32" s="60">
         <v>0.7083333333333334</v>
       </c>
-      <c r="O32" s="62" t="s">
+      <c r="O32" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="P32" s="63"/>
-      <c r="Q32" s="63"/>
-      <c r="R32" s="64"/>
+      <c r="P32" s="62"/>
+      <c r="Q32" s="62"/>
+      <c r="R32" s="63"/>
       <c r="S32" s="22">
         <v>21.0</v>
       </c>
@@ -2971,18 +2968,18 @@
       <c r="J33" s="22"/>
       <c r="K33" s="22"/>
       <c r="L33" s="22"/>
-      <c r="M33" s="60">
+      <c r="M33" s="59">
         <v>22.0</v>
       </c>
-      <c r="N33" s="61">
+      <c r="N33" s="60">
         <v>0.7222222222222222</v>
       </c>
-      <c r="O33" s="62" t="s">
+      <c r="O33" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="P33" s="63"/>
-      <c r="Q33" s="63"/>
-      <c r="R33" s="64"/>
+      <c r="P33" s="62"/>
+      <c r="Q33" s="62"/>
+      <c r="R33" s="63"/>
       <c r="S33" s="22">
         <v>22.0</v>
       </c>
@@ -3029,18 +3026,18 @@
       <c r="J34" s="22"/>
       <c r="K34" s="22"/>
       <c r="L34" s="22"/>
-      <c r="M34" s="60">
+      <c r="M34" s="59">
         <v>23.0</v>
       </c>
-      <c r="N34" s="61">
+      <c r="N34" s="60">
         <v>0.7361111111111112</v>
       </c>
-      <c r="O34" s="62" t="s">
+      <c r="O34" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="P34" s="63"/>
-      <c r="Q34" s="63"/>
-      <c r="R34" s="64"/>
+      <c r="P34" s="62"/>
+      <c r="Q34" s="62"/>
+      <c r="R34" s="63"/>
       <c r="S34" s="22">
         <v>23.0</v>
       </c>
@@ -3085,18 +3082,18 @@
       <c r="J35" s="22"/>
       <c r="K35" s="22"/>
       <c r="L35" s="22"/>
-      <c r="M35" s="60">
+      <c r="M35" s="59">
         <v>24.0</v>
       </c>
-      <c r="N35" s="61">
+      <c r="N35" s="60">
         <v>0.75</v>
       </c>
-      <c r="O35" s="62" t="s">
+      <c r="O35" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="P35" s="63"/>
-      <c r="Q35" s="63"/>
-      <c r="R35" s="64"/>
+      <c r="P35" s="62"/>
+      <c r="Q35" s="62"/>
+      <c r="R35" s="63"/>
       <c r="S35" s="22">
         <v>24.0</v>
       </c>
@@ -3141,18 +3138,18 @@
       <c r="J36" s="22"/>
       <c r="K36" s="22"/>
       <c r="L36" s="22"/>
-      <c r="M36" s="60">
+      <c r="M36" s="59">
         <v>25.0</v>
       </c>
-      <c r="N36" s="61">
+      <c r="N36" s="60">
         <v>0.7638888888888888</v>
       </c>
-      <c r="O36" s="62" t="s">
+      <c r="O36" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="P36" s="63"/>
-      <c r="Q36" s="63"/>
-      <c r="R36" s="64"/>
+      <c r="P36" s="62"/>
+      <c r="Q36" s="62"/>
+      <c r="R36" s="63"/>
       <c r="S36" s="22">
         <v>25.0</v>
       </c>
@@ -3197,18 +3194,18 @@
       <c r="J37" s="22"/>
       <c r="K37" s="22"/>
       <c r="L37" s="22"/>
-      <c r="M37" s="60">
+      <c r="M37" s="59">
         <v>26.0</v>
       </c>
-      <c r="N37" s="61">
+      <c r="N37" s="60">
         <v>0.7777777777777778</v>
       </c>
-      <c r="O37" s="62" t="s">
+      <c r="O37" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="P37" s="63"/>
-      <c r="Q37" s="63"/>
-      <c r="R37" s="64"/>
+      <c r="P37" s="62"/>
+      <c r="Q37" s="62"/>
+      <c r="R37" s="63"/>
       <c r="S37" s="22">
         <v>26.0</v>
       </c>
@@ -3253,18 +3250,18 @@
       <c r="J38" s="22"/>
       <c r="K38" s="22"/>
       <c r="L38" s="22"/>
-      <c r="M38" s="60">
+      <c r="M38" s="59">
         <v>27.0</v>
       </c>
-      <c r="N38" s="61">
+      <c r="N38" s="60">
         <v>0.7916666666666666</v>
       </c>
-      <c r="O38" s="62" t="s">
+      <c r="O38" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="P38" s="63"/>
-      <c r="Q38" s="63"/>
-      <c r="R38" s="64"/>
+      <c r="P38" s="62"/>
+      <c r="Q38" s="62"/>
+      <c r="R38" s="63"/>
       <c r="S38" s="22">
         <v>27.0</v>
       </c>
@@ -3309,18 +3306,18 @@
       <c r="J39" s="22"/>
       <c r="K39" s="22"/>
       <c r="L39" s="22"/>
-      <c r="M39" s="60">
+      <c r="M39" s="59">
         <v>28.0</v>
       </c>
-      <c r="N39" s="61">
+      <c r="N39" s="60">
         <v>0.8055555555555556</v>
       </c>
-      <c r="O39" s="62" t="s">
+      <c r="O39" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="P39" s="63"/>
-      <c r="Q39" s="63"/>
-      <c r="R39" s="64"/>
+      <c r="P39" s="62"/>
+      <c r="Q39" s="62"/>
+      <c r="R39" s="63"/>
       <c r="S39" s="22">
         <v>28.0</v>
       </c>
@@ -3340,7 +3337,7 @@
       <c r="AA39" s="22"/>
       <c r="AB39" s="22"/>
       <c r="AC39" s="22"/>
-      <c r="AD39" s="65"/>
+      <c r="AD39" s="64"/>
       <c r="AE39" s="1"/>
       <c r="AF39" s="1"/>
     </row>
@@ -3365,18 +3362,18 @@
       <c r="J40" s="22"/>
       <c r="K40" s="22"/>
       <c r="L40" s="22"/>
-      <c r="M40" s="60">
+      <c r="M40" s="59">
         <v>29.0</v>
       </c>
-      <c r="N40" s="61">
+      <c r="N40" s="60">
         <v>0.8194444444444444</v>
       </c>
-      <c r="O40" s="62" t="s">
+      <c r="O40" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="P40" s="63"/>
-      <c r="Q40" s="63"/>
-      <c r="R40" s="64"/>
+      <c r="P40" s="62"/>
+      <c r="Q40" s="62"/>
+      <c r="R40" s="63"/>
       <c r="S40" s="22">
         <v>29.0</v>
       </c>
@@ -3396,7 +3393,7 @@
       <c r="AA40" s="22"/>
       <c r="AB40" s="22"/>
       <c r="AC40" s="22"/>
-      <c r="AD40" s="65"/>
+      <c r="AD40" s="64"/>
       <c r="AE40" s="1"/>
       <c r="AF40" s="1"/>
     </row>
@@ -3421,18 +3418,18 @@
       <c r="J41" s="22"/>
       <c r="K41" s="22"/>
       <c r="L41" s="22"/>
-      <c r="M41" s="60">
+      <c r="M41" s="59">
         <v>30.0</v>
       </c>
-      <c r="N41" s="61">
+      <c r="N41" s="60">
         <v>0.8333333333333334</v>
       </c>
-      <c r="O41" s="62" t="s">
+      <c r="O41" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="P41" s="63"/>
-      <c r="Q41" s="63"/>
-      <c r="R41" s="64"/>
+      <c r="P41" s="62"/>
+      <c r="Q41" s="62"/>
+      <c r="R41" s="63"/>
       <c r="S41" s="22">
         <v>30.0</v>
       </c>
@@ -3452,7 +3449,7 @@
       <c r="AA41" s="22"/>
       <c r="AB41" s="22"/>
       <c r="AC41" s="22"/>
-      <c r="AD41" s="65"/>
+      <c r="AD41" s="64"/>
       <c r="AE41" s="1"/>
       <c r="AF41" s="1"/>
     </row>
@@ -3477,18 +3474,18 @@
       <c r="J42" s="22"/>
       <c r="K42" s="22"/>
       <c r="L42" s="22"/>
-      <c r="M42" s="60">
+      <c r="M42" s="59">
         <v>31.0</v>
       </c>
-      <c r="N42" s="61">
+      <c r="N42" s="60">
         <v>0.8472222222222222</v>
       </c>
-      <c r="O42" s="62" t="s">
+      <c r="O42" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="P42" s="63"/>
-      <c r="Q42" s="63"/>
-      <c r="R42" s="64"/>
+      <c r="P42" s="62"/>
+      <c r="Q42" s="62"/>
+      <c r="R42" s="63"/>
       <c r="S42" s="22">
         <v>31.0</v>
       </c>
@@ -3508,63 +3505,63 @@
       <c r="AA42" s="22"/>
       <c r="AB42" s="22"/>
       <c r="AC42" s="22"/>
-      <c r="AD42" s="65"/>
+      <c r="AD42" s="64"/>
       <c r="AE42" s="1"/>
       <c r="AF42" s="1"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="66">
+      <c r="A43" s="65">
         <v>32.0</v>
       </c>
-      <c r="B43" s="67">
+      <c r="B43" s="66">
         <v>0.8611111111111112</v>
       </c>
-      <c r="C43" s="66"/>
-      <c r="D43" s="66"/>
-      <c r="E43" s="66"/>
-      <c r="F43" s="66"/>
-      <c r="G43" s="66">
+      <c r="C43" s="65"/>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65">
         <v>32.0</v>
       </c>
-      <c r="H43" s="67">
+      <c r="H43" s="66">
         <v>0.8611111111111112</v>
       </c>
-      <c r="I43" s="66"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="66"/>
-      <c r="L43" s="66"/>
-      <c r="M43" s="68">
+      <c r="I43" s="65"/>
+      <c r="J43" s="65"/>
+      <c r="K43" s="65"/>
+      <c r="L43" s="65"/>
+      <c r="M43" s="67">
         <v>32.0</v>
       </c>
-      <c r="N43" s="69">
+      <c r="N43" s="68">
         <v>0.8611111111111112</v>
       </c>
-      <c r="O43" s="70" t="s">
+      <c r="O43" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="P43" s="71"/>
-      <c r="Q43" s="71"/>
-      <c r="R43" s="72"/>
-      <c r="S43" s="66">
+      <c r="P43" s="70"/>
+      <c r="Q43" s="70"/>
+      <c r="R43" s="71"/>
+      <c r="S43" s="65">
         <v>32.0</v>
       </c>
-      <c r="T43" s="67">
+      <c r="T43" s="66">
         <v>0.8611111111111112</v>
       </c>
-      <c r="U43" s="66"/>
-      <c r="V43" s="66"/>
-      <c r="W43" s="66"/>
-      <c r="X43" s="66"/>
-      <c r="Y43" s="66">
+      <c r="U43" s="65"/>
+      <c r="V43" s="65"/>
+      <c r="W43" s="65"/>
+      <c r="X43" s="65"/>
+      <c r="Y43" s="65">
         <v>32.0</v>
       </c>
-      <c r="Z43" s="67">
+      <c r="Z43" s="66">
         <v>0.8611111111111112</v>
       </c>
-      <c r="AA43" s="66"/>
-      <c r="AB43" s="66"/>
-      <c r="AC43" s="66"/>
-      <c r="AD43" s="73"/>
+      <c r="AA43" s="65"/>
+      <c r="AB43" s="65"/>
+      <c r="AC43" s="65"/>
+      <c r="AD43" s="72"/>
       <c r="AE43" s="1"/>
       <c r="AF43" s="1"/>
     </row>

--- a/file_wisuda_4okt.xlsx
+++ b/file_wisuda_4okt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="81">
   <si>
     <t xml:space="preserve">Graduation Schedule 
 </t>
@@ -85,6 +85,9 @@
     <t>Graduation</t>
   </si>
   <si>
+    <t>Yeni A</t>
+  </si>
+  <si>
     <t>Nurul Indah Amalia</t>
   </si>
   <si>
@@ -115,7 +118,7 @@
     <t>Azhar</t>
   </si>
   <si>
-    <t>Yeni A</t>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>Fedinda Nara</t>
@@ -199,6 +202,9 @@
     <t>dp 200</t>
   </si>
   <si>
+    <t>Ridho</t>
+  </si>
+  <si>
     <t>Indriyani</t>
   </si>
   <si>
@@ -254,9 +260,6 @@
   </si>
   <si>
     <t>CLOSED</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -671,9 +674,6 @@
     <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="10" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
@@ -720,6 +720,9 @@
     </xf>
     <xf borderId="5" fillId="10" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="10" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="8" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
@@ -896,7 +899,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -924,7 +927,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image5.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1706,16 +1709,24 @@
       <c r="AF16" s="27"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="22">
+      <c r="A17" s="24">
         <v>6.0</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B17" s="25">
         <v>0.4791666666666667</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
+      <c r="C17" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="26" t="s">
+        <v>19</v>
+      </c>
       <c r="G17" s="22">
         <v>6.0</v>
       </c>
@@ -1767,13 +1778,13 @@
         <v>0.5</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D18" s="33" t="s">
         <v>21</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F18" s="33" t="s">
         <v>19</v>
@@ -1822,20 +1833,20 @@
       <c r="AF18" s="27"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="31">
+      <c r="A19" s="24">
         <v>8.0</v>
       </c>
-      <c r="B19" s="32">
+      <c r="B19" s="25">
         <v>0.5208333333333334</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D19" s="33" t="s">
         <v>21</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F19" s="33" t="s">
         <v>19</v>
@@ -1850,62 +1861,62 @@
       <c r="J19" s="36"/>
       <c r="K19" s="36"/>
       <c r="L19" s="36"/>
-      <c r="M19" s="37">
+      <c r="M19" s="29">
         <v>8.0</v>
       </c>
-      <c r="N19" s="38">
+      <c r="N19" s="30">
         <v>0.5208333333333334</v>
       </c>
-      <c r="O19" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="P19" s="37" t="s">
+      <c r="O19" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="P19" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="Q19" s="37" t="s">
+      <c r="Q19" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="R19" s="39" t="s">
+      <c r="R19" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="S19" s="31">
+      <c r="S19" s="24">
         <v>8.0</v>
       </c>
-      <c r="T19" s="32">
+      <c r="T19" s="25">
         <v>0.5208333333333334</v>
       </c>
-      <c r="U19" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="V19" s="40" t="s">
+      <c r="U19" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="V19" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="W19" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="X19" s="40" t="s">
+      <c r="W19" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="X19" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="Y19" s="37">
+      <c r="Y19" s="29">
         <v>8.0</v>
       </c>
-      <c r="Z19" s="38">
+      <c r="Z19" s="30">
         <v>0.5208333333333334</v>
       </c>
-      <c r="AA19" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB19" s="42" t="s">
+      <c r="AA19" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB19" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="AC19" s="42" t="s">
+      <c r="AC19" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="AD19" s="37" t="s">
+      <c r="AD19" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="AE19" s="43"/>
-      <c r="AF19" s="43"/>
+      <c r="AE19" s="42"/>
+      <c r="AF19" s="42"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="31">
@@ -1915,39 +1926,39 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" s="33" t="s">
         <v>21</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F20" s="33"/>
       <c r="G20" s="36">
         <v>9.0</v>
       </c>
-      <c r="H20" s="44">
+      <c r="H20" s="43">
         <v>0.5416666666666666</v>
       </c>
-      <c r="I20" s="45"/>
-      <c r="J20" s="45"/>
-      <c r="K20" s="45"/>
-      <c r="L20" s="45"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="44"/>
       <c r="M20" s="31">
         <v>9.0</v>
       </c>
       <c r="N20" s="32">
         <v>0.5416666666666666</v>
       </c>
-      <c r="O20" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="P20" s="47" t="s">
+      <c r="O20" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="P20" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="Q20" s="47" t="s">
-        <v>23</v>
+      <c r="Q20" s="46" t="s">
+        <v>24</v>
       </c>
       <c r="R20" s="33" t="s">
         <v>19</v>
@@ -1959,55 +1970,49 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="U20" s="33" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V20" s="33" t="s">
         <v>21</v>
       </c>
       <c r="W20" s="33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X20" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="Y20" s="37">
+      <c r="Y20" s="29">
         <v>9.0</v>
       </c>
-      <c r="Z20" s="38">
+      <c r="Z20" s="30">
         <v>0.5416666666666666</v>
       </c>
-      <c r="AA20" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB20" s="42" t="s">
+      <c r="AA20" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB20" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="AC20" s="42" t="s">
+      <c r="AC20" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="AD20" s="48"/>
-      <c r="AE20" s="49"/>
-      <c r="AF20" s="49"/>
+      <c r="AD20" s="47"/>
+      <c r="AE20" s="48"/>
+      <c r="AF20" s="48"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="31">
+      <c r="A21" s="36">
         <v>10.0</v>
       </c>
-      <c r="B21" s="32">
+      <c r="B21" s="43">
         <v>0.5555555555555556</v>
       </c>
-      <c r="C21" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" s="33" t="s">
-        <v>19</v>
-      </c>
+      <c r="C21" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
       <c r="G21" s="31">
         <v>10.0</v>
       </c>
@@ -2015,13 +2020,13 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="I21" s="33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J21" s="33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K21" s="33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L21" s="33" t="s">
         <v>19</v>
@@ -2032,16 +2037,16 @@
       <c r="N21" s="32">
         <v>0.5555555555555556</v>
       </c>
-      <c r="O21" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="P21" s="51" t="s">
+      <c r="O21" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="P21" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="Q21" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="R21" s="37" t="s">
+      <c r="Q21" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="R21" s="38" t="s">
         <v>19</v>
       </c>
       <c r="S21" s="31">
@@ -2051,7 +2056,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="U21" s="33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V21" s="33" t="s">
         <v>21</v>
@@ -2067,13 +2072,13 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="AA21" s="33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AB21" s="33" t="s">
         <v>21</v>
       </c>
       <c r="AC21" s="33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AD21" s="31"/>
       <c r="AE21" s="27"/>
@@ -2087,13 +2092,13 @@
         <v>0.5694444444444444</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F22" s="33" t="s">
         <v>19</v>
@@ -2101,27 +2106,27 @@
       <c r="G22" s="36">
         <v>11.0</v>
       </c>
-      <c r="H22" s="44">
+      <c r="H22" s="43">
         <v>0.5694444444444444</v>
       </c>
       <c r="I22" s="36"/>
       <c r="J22" s="36"/>
       <c r="K22" s="36"/>
       <c r="L22" s="36"/>
-      <c r="M22" s="31">
+      <c r="M22" s="24">
         <v>11.0</v>
       </c>
-      <c r="N22" s="32">
+      <c r="N22" s="25">
         <v>0.5694444444444444</v>
       </c>
-      <c r="O22" s="46" t="s">
-        <v>40</v>
+      <c r="O22" s="45" t="s">
+        <v>41</v>
       </c>
       <c r="P22" s="33" t="s">
         <v>21</v>
       </c>
       <c r="Q22" s="33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R22" s="31"/>
       <c r="S22" s="31">
@@ -2131,13 +2136,13 @@
         <v>0.5694444444444444</v>
       </c>
       <c r="U22" s="33" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V22" s="33" t="s">
         <v>21</v>
       </c>
       <c r="W22" s="33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X22" s="33" t="s">
         <v>19</v>
@@ -2149,7 +2154,7 @@
         <v>0.5694444444444444</v>
       </c>
       <c r="AA22" s="33" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AB22" s="33" t="s">
         <v>21</v>
@@ -2160,36 +2165,36 @@
       <c r="AD22" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="AE22" s="52"/>
-      <c r="AF22" s="52"/>
+      <c r="AE22" s="51"/>
+      <c r="AF22" s="51"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="37">
+      <c r="A23" s="38">
         <v>13.0</v>
       </c>
       <c r="B23" s="32">
         <v>0.5833333333333334</v>
       </c>
-      <c r="C23" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="37" t="s">
+      <c r="C23" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="F23" s="37" t="s">
+      <c r="E23" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="F23" s="38" t="s">
         <v>19</v>
       </c>
       <c r="G23" s="36">
         <v>12.0</v>
       </c>
-      <c r="H23" s="44">
+      <c r="H23" s="43">
         <v>0.5833333333333334</v>
       </c>
       <c r="I23" s="36"/>
-      <c r="J23" s="53"/>
+      <c r="J23" s="52"/>
       <c r="K23" s="36"/>
       <c r="L23" s="36"/>
       <c r="M23" s="31">
@@ -2198,16 +2203,16 @@
       <c r="N23" s="32">
         <v>0.5833333333333334</v>
       </c>
-      <c r="O23" s="54" t="s">
-        <v>44</v>
-      </c>
-      <c r="P23" s="37" t="s">
+      <c r="O23" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="P23" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="Q23" s="37" t="s">
+      <c r="Q23" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="R23" s="37" t="s">
+      <c r="R23" s="38" t="s">
         <v>19</v>
       </c>
       <c r="S23" s="31">
@@ -2217,7 +2222,7 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="U23" s="33" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V23" s="33" t="s">
         <v>21</v>
@@ -2234,16 +2239,16 @@
       <c r="Z23" s="32">
         <v>0.5833333333333334</v>
       </c>
-      <c r="AA23" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB23" s="37" t="s">
+      <c r="AA23" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB23" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="AC23" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="AD23" s="50"/>
+      <c r="AC23" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD23" s="49"/>
       <c r="AE23" s="27"/>
       <c r="AF23" s="27"/>
     </row>
@@ -2255,13 +2260,13 @@
         <v>0.5972222222222222</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D24" s="33" t="s">
         <v>21</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F24" s="33" t="s">
         <v>19</v>
@@ -2273,13 +2278,13 @@
         <v>0.5972222222222222</v>
       </c>
       <c r="I24" s="33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J24" s="33" t="s">
         <v>21</v>
       </c>
       <c r="K24" s="33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L24" s="33" t="s">
         <v>19</v>
@@ -2290,16 +2295,16 @@
       <c r="N24" s="32">
         <v>0.5972222222222222</v>
       </c>
-      <c r="O24" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="P24" s="37" t="s">
+      <c r="O24" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="P24" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="Q24" s="37" t="s">
+      <c r="Q24" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="R24" s="37" t="s">
+      <c r="R24" s="38" t="s">
         <v>19</v>
       </c>
       <c r="S24" s="31">
@@ -2309,13 +2314,13 @@
         <v>0.5972222222222222</v>
       </c>
       <c r="U24" s="33" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="V24" s="33" t="s">
         <v>21</v>
       </c>
       <c r="W24" s="33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X24" s="33" t="s">
         <v>19</v>
@@ -2323,7 +2328,7 @@
       <c r="Y24" s="36">
         <v>13.0</v>
       </c>
-      <c r="Z24" s="44">
+      <c r="Z24" s="43">
         <v>0.5972222222222222</v>
       </c>
       <c r="AA24" s="36"/>
@@ -2337,7 +2342,7 @@
       <c r="A25" s="36">
         <v>14.0</v>
       </c>
-      <c r="B25" s="44">
+      <c r="B25" s="43">
         <v>0.6111111111111112</v>
       </c>
       <c r="C25" s="36"/>
@@ -2351,13 +2356,13 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="I25" s="33" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J25" s="33" t="s">
         <v>21</v>
       </c>
       <c r="K25" s="33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L25" s="33" t="s">
         <v>19</v>
@@ -2369,7 +2374,7 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="O25" s="33" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P25" s="33" t="s">
         <v>21</v>
@@ -2385,7 +2390,7 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="U25" s="33" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="V25" s="33" t="s">
         <v>21</v>
@@ -2403,13 +2408,13 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="AA25" s="33" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AB25" s="33" t="s">
         <v>21</v>
       </c>
       <c r="AC25" s="33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AD25" s="33" t="s">
         <v>19</v>
@@ -2421,12 +2426,12 @@
       <c r="A26" s="36">
         <v>15.0</v>
       </c>
-      <c r="B26" s="44">
+      <c r="B26" s="43">
         <v>0.625</v>
       </c>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
       <c r="F26" s="36"/>
       <c r="G26" s="31">
         <v>15.0</v>
@@ -2435,13 +2440,13 @@
         <v>0.625</v>
       </c>
       <c r="I26" s="33" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J26" s="33" t="s">
         <v>21</v>
       </c>
       <c r="K26" s="33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L26" s="33" t="s">
         <v>19</v>
@@ -2453,7 +2458,7 @@
         <v>0.625</v>
       </c>
       <c r="O26" s="33" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P26" s="33" t="s">
         <v>21</v>
@@ -2469,13 +2474,13 @@
         <v>0.625</v>
       </c>
       <c r="U26" s="33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V26" s="33" t="s">
         <v>21</v>
       </c>
       <c r="W26" s="33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X26" s="33" t="s">
         <v>19</v>
@@ -2487,7 +2492,7 @@
         <v>0.625</v>
       </c>
       <c r="AA26" s="33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AB26" s="33" t="s">
         <v>21</v>
@@ -2496,22 +2501,26 @@
         <v>15</v>
       </c>
       <c r="AD26" s="33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AE26" s="27"/>
       <c r="AF26" s="27"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="22">
+      <c r="A27" s="31">
         <v>16.0</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B27" s="32">
         <v>0.6388888888888888</v>
       </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
+      <c r="C27" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
       <c r="G27" s="31">
         <v>16.0</v>
       </c>
@@ -2519,13 +2528,13 @@
         <v>0.6388888888888888</v>
       </c>
       <c r="I27" s="33" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J27" s="33" t="s">
         <v>21</v>
       </c>
       <c r="K27" s="33" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L27" s="33" t="s">
         <v>19</v>
@@ -2537,7 +2546,7 @@
         <v>0.6388888888888888</v>
       </c>
       <c r="O27" s="33" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="P27" s="33" t="s">
         <v>21</v>
@@ -2551,7 +2560,7 @@
       <c r="S27" s="36">
         <v>16.0</v>
       </c>
-      <c r="T27" s="44">
+      <c r="T27" s="43">
         <v>0.6388888888888888</v>
       </c>
       <c r="U27" s="36"/>
@@ -2565,13 +2574,13 @@
         <v>0.6388888888888888</v>
       </c>
       <c r="AA27" s="33" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AB27" s="33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AC27" s="33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AD27" s="33" t="s">
         <v>19</v>
@@ -2587,13 +2596,13 @@
         <v>0.6527777777777778</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D28" s="33" t="s">
         <v>21</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F28" s="33" t="s">
         <v>19</v>
@@ -2605,13 +2614,13 @@
         <v>0.6527777777777778</v>
       </c>
       <c r="I28" s="33" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J28" s="33" t="s">
         <v>21</v>
       </c>
       <c r="K28" s="33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L28" s="33" t="s">
         <v>19</v>
@@ -2622,22 +2631,22 @@
       <c r="N28" s="32">
         <v>0.6527777777777778</v>
       </c>
-      <c r="O28" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="P28" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q28" s="37" t="s">
+      <c r="O28" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="P28" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q28" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="R28" s="55" t="s">
+      <c r="R28" s="54" t="s">
         <v>19</v>
       </c>
       <c r="S28" s="36">
         <v>17.0</v>
       </c>
-      <c r="T28" s="44">
+      <c r="T28" s="43">
         <v>0.6527777777777778</v>
       </c>
       <c r="U28" s="36"/>
@@ -2651,7 +2660,7 @@
         <v>0.6527777777777778</v>
       </c>
       <c r="AA28" s="33" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AB28" s="33" t="s">
         <v>21</v>
@@ -2673,13 +2682,13 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D29" s="33" t="s">
         <v>21</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F29" s="33" t="s">
         <v>19</v>
@@ -2687,7 +2696,7 @@
       <c r="G29" s="36">
         <v>18.0</v>
       </c>
-      <c r="H29" s="44">
+      <c r="H29" s="43">
         <v>0.6666666666666666</v>
       </c>
       <c r="I29" s="36"/>
@@ -2701,33 +2710,33 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="O29" s="33" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P29" s="33" t="s">
         <v>21</v>
       </c>
       <c r="Q29" s="33" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="R29" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="S29" s="37">
+      <c r="S29" s="38">
         <v>18.0</v>
       </c>
-      <c r="T29" s="38">
+      <c r="T29" s="55">
         <v>0.6666666666666666</v>
       </c>
-      <c r="U29" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="V29" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="W29" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="X29" s="55" t="s">
+      <c r="U29" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="V29" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="W29" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="X29" s="54" t="s">
         <v>19</v>
       </c>
       <c r="Y29" s="31">
@@ -2736,14 +2745,14 @@
       <c r="Z29" s="32">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AA29" s="47" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB29" s="47" t="s">
+      <c r="AA29" s="46" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB29" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="AC29" s="47" t="s">
-        <v>23</v>
+      <c r="AC29" s="46" t="s">
+        <v>24</v>
       </c>
       <c r="AD29" s="56" t="s">
         <v>19</v>
@@ -2759,7 +2768,7 @@
         <v>0.6805555555555556</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D30" s="33" t="s">
         <v>21</v>
@@ -2775,13 +2784,13 @@
         <v>0.6805555555555556</v>
       </c>
       <c r="I30" s="33" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J30" s="33" t="s">
         <v>21</v>
       </c>
       <c r="K30" s="33" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L30" s="33" t="s">
         <v>19</v>
@@ -2793,16 +2802,16 @@
         <v>0.6805555555555556</v>
       </c>
       <c r="O30" s="33" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P30" s="33" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Q30" s="33" t="s">
         <v>15</v>
       </c>
       <c r="R30" s="33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S30" s="22">
         <v>19.0</v>
@@ -2835,7 +2844,7 @@
         <v>0.6944444444444444</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D31" s="33" t="s">
         <v>21</v>
@@ -2863,7 +2872,7 @@
         <v>0.6944444444444444</v>
       </c>
       <c r="O31" s="61" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P31" s="62"/>
       <c r="Q31" s="62"/>
@@ -2919,7 +2928,7 @@
         <v>0.7083333333333334</v>
       </c>
       <c r="O32" s="61" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P32" s="62"/>
       <c r="Q32" s="62"/>
@@ -2975,7 +2984,7 @@
         <v>0.7222222222222222</v>
       </c>
       <c r="O33" s="61" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P33" s="62"/>
       <c r="Q33" s="62"/>
@@ -2997,7 +3006,7 @@
         <v>0.7222222222222222</v>
       </c>
       <c r="AA33" s="22" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="AB33" s="22"/>
       <c r="AC33" s="22"/>
@@ -3033,7 +3042,7 @@
         <v>0.7361111111111112</v>
       </c>
       <c r="O34" s="61" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P34" s="62"/>
       <c r="Q34" s="62"/>
@@ -3089,7 +3098,7 @@
         <v>0.75</v>
       </c>
       <c r="O35" s="61" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P35" s="62"/>
       <c r="Q35" s="62"/>
@@ -3145,7 +3154,7 @@
         <v>0.7638888888888888</v>
       </c>
       <c r="O36" s="61" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P36" s="62"/>
       <c r="Q36" s="62"/>
@@ -3201,7 +3210,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="O37" s="61" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P37" s="62"/>
       <c r="Q37" s="62"/>
@@ -3257,7 +3266,7 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="O38" s="61" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P38" s="62"/>
       <c r="Q38" s="62"/>
@@ -3313,7 +3322,7 @@
         <v>0.8055555555555556</v>
       </c>
       <c r="O39" s="61" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P39" s="62"/>
       <c r="Q39" s="62"/>
@@ -3369,7 +3378,7 @@
         <v>0.8194444444444444</v>
       </c>
       <c r="O40" s="61" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P40" s="62"/>
       <c r="Q40" s="62"/>
@@ -3425,7 +3434,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="O41" s="61" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P41" s="62"/>
       <c r="Q41" s="62"/>
@@ -3481,7 +3490,7 @@
         <v>0.8472222222222222</v>
       </c>
       <c r="O42" s="61" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P42" s="62"/>
       <c r="Q42" s="62"/>
@@ -3537,7 +3546,7 @@
         <v>0.8611111111111112</v>
       </c>
       <c r="O43" s="69" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P43" s="70"/>
       <c r="Q43" s="70"/>

--- a/file_wisuda_4okt.xlsx
+++ b/file_wisuda_4okt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="81">
   <si>
     <t xml:space="preserve">Graduation Schedule 
 </t>
@@ -406,14 +406,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-        <bgColor rgb="FF00FF00"/>
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF00FF00"/>
+        <bgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -563,7 +563,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="76">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -653,78 +653,87 @@
     <xf borderId="5" fillId="9" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="5" fillId="10" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="10" fontId="13" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="6" fillId="9" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="5" fillId="10" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="11" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="13" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf borderId="6" fillId="9" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="6" fillId="11" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="10" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="6" fillId="10" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf borderId="5" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="11" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="7" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="6" fillId="11" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="6" fillId="10" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="10" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="10" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="7" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="10" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="11" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="5" fillId="10" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="8" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="8" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -815,7 +824,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPr id="0" name="image5.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -843,7 +852,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -871,7 +880,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -899,7 +908,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -927,7 +936,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.jpg"/>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1771,22 +1780,22 @@
       <c r="AF17" s="27"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="31">
+      <c r="A18" s="24">
         <v>7.0</v>
       </c>
-      <c r="B18" s="32">
+      <c r="B18" s="25">
         <v>0.5</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="C18" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="33" t="s">
+      <c r="D18" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="33" t="s">
+      <c r="E18" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="33" t="s">
+      <c r="F18" s="26" t="s">
         <v>19</v>
       </c>
       <c r="G18" s="22">
@@ -1839,44 +1848,44 @@
       <c r="B19" s="25">
         <v>0.5208333333333334</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C19" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="D19" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="33" t="s">
+      <c r="E19" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="33" t="s">
+      <c r="F19" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="G19" s="34">
+      <c r="G19" s="31">
         <v>8.0</v>
       </c>
-      <c r="H19" s="35">
+      <c r="H19" s="32">
         <v>0.5208333333333334</v>
       </c>
-      <c r="I19" s="34"/>
-      <c r="J19" s="36"/>
-      <c r="K19" s="36"/>
-      <c r="L19" s="36"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="33"/>
       <c r="M19" s="29">
         <v>8.0</v>
       </c>
       <c r="N19" s="30">
         <v>0.5208333333333334</v>
       </c>
-      <c r="O19" s="37" t="s">
+      <c r="O19" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="P19" s="38" t="s">
+      <c r="P19" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="Q19" s="38" t="s">
+      <c r="Q19" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="R19" s="37" t="s">
+      <c r="R19" s="34" t="s">
         <v>19</v>
       </c>
       <c r="S19" s="24">
@@ -1885,16 +1894,16 @@
       <c r="T19" s="25">
         <v>0.5208333333333334</v>
       </c>
-      <c r="U19" s="39" t="s">
+      <c r="U19" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="V19" s="39" t="s">
+      <c r="V19" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="W19" s="39" t="s">
+      <c r="W19" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="X19" s="39" t="s">
+      <c r="X19" s="36" t="s">
         <v>19</v>
       </c>
       <c r="Y19" s="29">
@@ -1903,82 +1912,82 @@
       <c r="Z19" s="30">
         <v>0.5208333333333334</v>
       </c>
-      <c r="AA19" s="40" t="s">
+      <c r="AA19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="AB19" s="41" t="s">
+      <c r="AB19" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="AC19" s="41" t="s">
+      <c r="AC19" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="AD19" s="38" t="s">
+      <c r="AD19" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="AE19" s="42"/>
-      <c r="AF19" s="42"/>
+      <c r="AE19" s="40"/>
+      <c r="AF19" s="40"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="31">
+      <c r="A20" s="24">
         <v>9.0</v>
       </c>
-      <c r="B20" s="32">
+      <c r="B20" s="25">
         <v>0.5416666666666666</v>
       </c>
-      <c r="C20" s="33" t="s">
+      <c r="C20" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="33" t="s">
+      <c r="D20" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="33" t="s">
+      <c r="E20" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="33"/>
-      <c r="G20" s="36">
+      <c r="F20" s="41"/>
+      <c r="G20" s="33">
         <v>9.0</v>
       </c>
-      <c r="H20" s="43">
+      <c r="H20" s="42">
         <v>0.5416666666666666</v>
       </c>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="44"/>
-      <c r="L20" s="44"/>
-      <c r="M20" s="31">
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="43"/>
+      <c r="M20" s="24">
         <v>9.0</v>
       </c>
-      <c r="N20" s="32">
+      <c r="N20" s="25">
         <v>0.5416666666666666</v>
       </c>
-      <c r="O20" s="45" t="s">
+      <c r="O20" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="P20" s="46" t="s">
+      <c r="P20" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="Q20" s="46" t="s">
+      <c r="Q20" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="R20" s="33" t="s">
+      <c r="R20" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="S20" s="31">
+      <c r="S20" s="24">
         <v>9.0</v>
       </c>
-      <c r="T20" s="32">
+      <c r="T20" s="25">
         <v>0.5416666666666666</v>
       </c>
-      <c r="U20" s="33" t="s">
+      <c r="U20" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="V20" s="33" t="s">
+      <c r="V20" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="W20" s="33" t="s">
+      <c r="W20" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="X20" s="33" t="s">
+      <c r="X20" s="41" t="s">
         <v>19</v>
       </c>
       <c r="Y20" s="29">
@@ -1987,13 +1996,13 @@
       <c r="Z20" s="30">
         <v>0.5416666666666666</v>
       </c>
-      <c r="AA20" s="40" t="s">
+      <c r="AA20" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="AB20" s="41" t="s">
+      <c r="AB20" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="AC20" s="41" t="s">
+      <c r="AC20" s="38" t="s">
         <v>15</v>
       </c>
       <c r="AD20" s="47"/>
@@ -2001,816 +2010,814 @@
       <c r="AF20" s="48"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="36">
+      <c r="A21" s="33">
         <v>10.0</v>
       </c>
-      <c r="B21" s="43">
+      <c r="B21" s="42">
         <v>0.5555555555555556</v>
       </c>
-      <c r="C21" s="44" t="s">
+      <c r="C21" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="31">
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="49">
         <v>10.0</v>
       </c>
-      <c r="H21" s="32">
+      <c r="H21" s="50">
         <v>0.5555555555555556</v>
       </c>
-      <c r="I21" s="33" t="s">
+      <c r="I21" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="J21" s="33" t="s">
+      <c r="J21" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="K21" s="33" t="s">
+      <c r="K21" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="L21" s="33" t="s">
+      <c r="L21" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="M21" s="31">
+      <c r="M21" s="49">
         <v>10.0</v>
       </c>
-      <c r="N21" s="32">
+      <c r="N21" s="50">
         <v>0.5555555555555556</v>
       </c>
-      <c r="O21" s="49" t="s">
+      <c r="O21" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="P21" s="50" t="s">
+      <c r="P21" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="Q21" s="38" t="s">
+      <c r="Q21" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="R21" s="38" t="s">
+      <c r="R21" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="S21" s="31">
+      <c r="S21" s="49">
         <v>10.0</v>
       </c>
-      <c r="T21" s="32">
+      <c r="T21" s="50">
         <v>0.5555555555555556</v>
       </c>
-      <c r="U21" s="33" t="s">
+      <c r="U21" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="V21" s="33" t="s">
+      <c r="V21" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="W21" s="33" t="s">
+      <c r="W21" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="X21" s="31"/>
-      <c r="Y21" s="31">
+      <c r="X21" s="49"/>
+      <c r="Y21" s="24">
         <v>10.0</v>
       </c>
-      <c r="Z21" s="32">
+      <c r="Z21" s="25">
         <v>0.5555555555555556</v>
       </c>
-      <c r="AA21" s="33" t="s">
+      <c r="AA21" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="AB21" s="33" t="s">
+      <c r="AB21" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="AC21" s="33" t="s">
+      <c r="AC21" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="AD21" s="31"/>
+      <c r="AD21" s="49"/>
       <c r="AE21" s="27"/>
       <c r="AF21" s="27"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="31">
+      <c r="A22" s="49">
         <v>11.0</v>
       </c>
-      <c r="B22" s="32">
+      <c r="B22" s="50">
         <v>0.5694444444444444</v>
       </c>
-      <c r="C22" s="33" t="s">
+      <c r="C22" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="D22" s="33" t="s">
+      <c r="D22" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="33" t="s">
+      <c r="E22" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="F22" s="33" t="s">
+      <c r="F22" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="G22" s="36">
+      <c r="G22" s="33">
         <v>11.0</v>
       </c>
-      <c r="H22" s="43">
+      <c r="H22" s="42">
         <v>0.5694444444444444</v>
       </c>
-      <c r="I22" s="36"/>
-      <c r="J22" s="36"/>
-      <c r="K22" s="36"/>
-      <c r="L22" s="36"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
       <c r="M22" s="24">
         <v>11.0</v>
       </c>
       <c r="N22" s="25">
         <v>0.5694444444444444</v>
       </c>
-      <c r="O22" s="45" t="s">
+      <c r="O22" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="P22" s="33" t="s">
+      <c r="P22" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="Q22" s="33" t="s">
+      <c r="Q22" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="R22" s="31"/>
-      <c r="S22" s="31">
+      <c r="R22" s="49"/>
+      <c r="S22" s="49">
         <v>11.0</v>
       </c>
-      <c r="T22" s="32">
+      <c r="T22" s="50">
         <v>0.5694444444444444</v>
       </c>
-      <c r="U22" s="33" t="s">
+      <c r="U22" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="V22" s="33" t="s">
+      <c r="V22" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="W22" s="33" t="s">
+      <c r="W22" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="X22" s="33" t="s">
+      <c r="X22" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="Y22" s="31">
+      <c r="Y22" s="49">
         <v>11.0</v>
       </c>
-      <c r="Z22" s="32">
+      <c r="Z22" s="50">
         <v>0.5694444444444444</v>
       </c>
-      <c r="AA22" s="33" t="s">
+      <c r="AA22" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="AB22" s="33" t="s">
+      <c r="AB22" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="AC22" s="33" t="s">
+      <c r="AC22" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="AD22" s="33" t="s">
+      <c r="AD22" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="AE22" s="51"/>
-      <c r="AF22" s="51"/>
+      <c r="AE22" s="54"/>
+      <c r="AF22" s="54"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="38">
+      <c r="A23" s="39">
         <v>13.0</v>
       </c>
-      <c r="B23" s="32">
+      <c r="B23" s="50">
         <v>0.5833333333333334</v>
       </c>
-      <c r="C23" s="38" t="s">
+      <c r="C23" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="38" t="s">
+      <c r="D23" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="38" t="s">
+      <c r="E23" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="F23" s="38" t="s">
+      <c r="F23" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="G23" s="36">
+      <c r="G23" s="33">
         <v>12.0</v>
       </c>
-      <c r="H23" s="43">
+      <c r="H23" s="42">
         <v>0.5833333333333334</v>
       </c>
-      <c r="I23" s="36"/>
-      <c r="J23" s="52"/>
-      <c r="K23" s="36"/>
-      <c r="L23" s="36"/>
-      <c r="M23" s="31">
+      <c r="I23" s="33"/>
+      <c r="J23" s="55"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="49">
         <v>12.0</v>
       </c>
-      <c r="N23" s="32">
+      <c r="N23" s="50">
         <v>0.5833333333333334</v>
       </c>
-      <c r="O23" s="53" t="s">
+      <c r="O23" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="P23" s="38" t="s">
+      <c r="P23" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="Q23" s="38" t="s">
+      <c r="Q23" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="R23" s="38" t="s">
+      <c r="R23" s="39"/>
+      <c r="S23" s="49">
+        <v>12.0</v>
+      </c>
+      <c r="T23" s="50">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="U23" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="V23" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="W23" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="X23" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="S23" s="31">
+      <c r="Y23" s="49">
         <v>12.0</v>
       </c>
-      <c r="T23" s="32">
+      <c r="Z23" s="50">
         <v>0.5833333333333334</v>
       </c>
-      <c r="U23" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="V23" s="33" t="s">
+      <c r="AA23" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB23" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="W23" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="X23" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y23" s="31">
-        <v>12.0</v>
-      </c>
-      <c r="Z23" s="32">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="AA23" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB23" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC23" s="38" t="s">
+      <c r="AC23" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="AD23" s="49"/>
+      <c r="AD23" s="51"/>
       <c r="AE23" s="27"/>
       <c r="AF23" s="27"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="33">
+      <c r="A24" s="41">
         <v>14.0</v>
       </c>
-      <c r="B24" s="32">
+      <c r="B24" s="50">
         <v>0.5972222222222222</v>
       </c>
-      <c r="C24" s="33" t="s">
+      <c r="C24" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="D24" s="33" t="s">
+      <c r="D24" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="33" t="s">
+      <c r="E24" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="F24" s="33" t="s">
+      <c r="F24" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="G24" s="31">
+      <c r="G24" s="49">
         <v>13.0</v>
       </c>
-      <c r="H24" s="32">
+      <c r="H24" s="50">
         <v>0.5972222222222222</v>
       </c>
-      <c r="I24" s="33" t="s">
+      <c r="I24" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="J24" s="33" t="s">
+      <c r="J24" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="K24" s="33" t="s">
+      <c r="K24" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="L24" s="33" t="s">
+      <c r="L24" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="M24" s="31">
+      <c r="M24" s="49">
         <v>13.0</v>
       </c>
-      <c r="N24" s="32">
+      <c r="N24" s="50">
         <v>0.5972222222222222</v>
       </c>
-      <c r="O24" s="38" t="s">
+      <c r="O24" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="P24" s="38" t="s">
+      <c r="P24" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="Q24" s="38" t="s">
+      <c r="Q24" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="R24" s="38" t="s">
+      <c r="R24" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="S24" s="31">
+      <c r="S24" s="49">
         <v>13.0</v>
       </c>
-      <c r="T24" s="32">
+      <c r="T24" s="50">
         <v>0.5972222222222222</v>
       </c>
-      <c r="U24" s="33" t="s">
+      <c r="U24" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="V24" s="33" t="s">
+      <c r="V24" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="W24" s="33" t="s">
+      <c r="W24" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="X24" s="33" t="s">
+      <c r="X24" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="Y24" s="36">
+      <c r="Y24" s="33">
         <v>13.0</v>
       </c>
-      <c r="Z24" s="43">
+      <c r="Z24" s="42">
         <v>0.5972222222222222</v>
       </c>
-      <c r="AA24" s="36"/>
-      <c r="AB24" s="36"/>
-      <c r="AC24" s="36"/>
-      <c r="AD24" s="36"/>
+      <c r="AA24" s="33"/>
+      <c r="AB24" s="33"/>
+      <c r="AC24" s="33"/>
+      <c r="AD24" s="33"/>
       <c r="AE24" s="27"/>
       <c r="AF24" s="27"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="36">
+      <c r="A25" s="33">
         <v>14.0</v>
       </c>
-      <c r="B25" s="43">
+      <c r="B25" s="42">
         <v>0.6111111111111112</v>
       </c>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="31">
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="49">
         <v>14.0</v>
       </c>
-      <c r="H25" s="32">
+      <c r="H25" s="50">
         <v>0.6111111111111112</v>
       </c>
-      <c r="I25" s="33" t="s">
+      <c r="I25" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="J25" s="33" t="s">
+      <c r="J25" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="K25" s="33" t="s">
+      <c r="K25" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="L25" s="33" t="s">
+      <c r="L25" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="M25" s="31">
+      <c r="M25" s="49">
         <v>14.0</v>
       </c>
-      <c r="N25" s="32">
+      <c r="N25" s="50">
         <v>0.6111111111111112</v>
       </c>
-      <c r="O25" s="33" t="s">
+      <c r="O25" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="P25" s="33" t="s">
+      <c r="P25" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="Q25" s="33" t="s">
+      <c r="Q25" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="R25" s="31"/>
-      <c r="S25" s="31">
+      <c r="R25" s="49"/>
+      <c r="S25" s="49">
         <v>14.0</v>
       </c>
-      <c r="T25" s="32">
+      <c r="T25" s="50">
         <v>0.6111111111111112</v>
       </c>
-      <c r="U25" s="33" t="s">
+      <c r="U25" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="V25" s="33" t="s">
+      <c r="V25" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="W25" s="33" t="s">
+      <c r="W25" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="X25" s="33" t="s">
+      <c r="X25" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="Y25" s="31">
+      <c r="Y25" s="49">
         <v>14.0</v>
       </c>
-      <c r="Z25" s="32">
+      <c r="Z25" s="50">
         <v>0.6111111111111112</v>
       </c>
-      <c r="AA25" s="33" t="s">
+      <c r="AA25" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="AB25" s="33" t="s">
+      <c r="AB25" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="AC25" s="33" t="s">
+      <c r="AC25" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="AD25" s="33" t="s">
+      <c r="AD25" s="41" t="s">
         <v>19</v>
       </c>
       <c r="AE25" s="27"/>
       <c r="AF25" s="27"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="36">
+      <c r="A26" s="33">
         <v>15.0</v>
       </c>
-      <c r="B26" s="43">
+      <c r="B26" s="42">
         <v>0.625</v>
       </c>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="31">
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="49">
         <v>15.0</v>
       </c>
-      <c r="H26" s="32">
+      <c r="H26" s="50">
         <v>0.625</v>
       </c>
-      <c r="I26" s="33" t="s">
+      <c r="I26" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="J26" s="33" t="s">
+      <c r="J26" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="K26" s="33" t="s">
+      <c r="K26" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="L26" s="33" t="s">
+      <c r="L26" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="M26" s="31">
+      <c r="M26" s="49">
         <v>15.0</v>
       </c>
-      <c r="N26" s="32">
+      <c r="N26" s="50">
         <v>0.625</v>
       </c>
-      <c r="O26" s="33" t="s">
+      <c r="O26" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="P26" s="33" t="s">
+      <c r="P26" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="Q26" s="33" t="s">
+      <c r="Q26" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="R26" s="31"/>
-      <c r="S26" s="31">
+      <c r="R26" s="49"/>
+      <c r="S26" s="49">
         <v>15.0</v>
       </c>
-      <c r="T26" s="32">
+      <c r="T26" s="50">
         <v>0.625</v>
       </c>
-      <c r="U26" s="33" t="s">
+      <c r="U26" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="V26" s="33" t="s">
+      <c r="V26" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="W26" s="33" t="s">
+      <c r="W26" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="X26" s="33" t="s">
+      <c r="X26" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="Y26" s="31">
+      <c r="Y26" s="49">
         <v>15.0</v>
       </c>
-      <c r="Z26" s="32">
+      <c r="Z26" s="50">
         <v>0.625</v>
       </c>
-      <c r="AA26" s="33" t="s">
+      <c r="AA26" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="AB26" s="33" t="s">
+      <c r="AB26" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="AC26" s="33" t="s">
+      <c r="AC26" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="AD26" s="33" t="s">
+      <c r="AD26" s="41" t="s">
         <v>60</v>
       </c>
       <c r="AE26" s="27"/>
       <c r="AF26" s="27"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="31">
+      <c r="A27" s="49">
         <v>16.0</v>
       </c>
-      <c r="B27" s="32">
+      <c r="B27" s="50">
         <v>0.6388888888888888</v>
       </c>
-      <c r="C27" s="33" t="s">
+      <c r="C27" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="D27" s="33" t="s">
+      <c r="D27" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="31">
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="49">
         <v>16.0</v>
       </c>
-      <c r="H27" s="32">
+      <c r="H27" s="50">
         <v>0.6388888888888888</v>
       </c>
-      <c r="I27" s="33" t="s">
+      <c r="I27" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="J27" s="33" t="s">
+      <c r="J27" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="K27" s="33" t="s">
+      <c r="K27" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="L27" s="33" t="s">
+      <c r="L27" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="M27" s="31">
+      <c r="M27" s="49">
         <v>16.0</v>
       </c>
-      <c r="N27" s="32">
+      <c r="N27" s="50">
         <v>0.6388888888888888</v>
       </c>
-      <c r="O27" s="33" t="s">
+      <c r="O27" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="P27" s="33" t="s">
+      <c r="P27" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="Q27" s="33" t="s">
+      <c r="Q27" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="R27" s="33" t="s">
+      <c r="R27" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="S27" s="36">
+      <c r="S27" s="33">
         <v>16.0</v>
       </c>
-      <c r="T27" s="43">
+      <c r="T27" s="42">
         <v>0.6388888888888888</v>
       </c>
-      <c r="U27" s="36"/>
-      <c r="V27" s="36"/>
-      <c r="W27" s="36"/>
-      <c r="X27" s="36"/>
-      <c r="Y27" s="31">
+      <c r="U27" s="33"/>
+      <c r="V27" s="33"/>
+      <c r="W27" s="33"/>
+      <c r="X27" s="33"/>
+      <c r="Y27" s="49">
         <v>16.0</v>
       </c>
-      <c r="Z27" s="32">
+      <c r="Z27" s="50">
         <v>0.6388888888888888</v>
       </c>
-      <c r="AA27" s="33" t="s">
+      <c r="AA27" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="AB27" s="33" t="s">
+      <c r="AB27" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="AC27" s="33" t="s">
+      <c r="AC27" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="AD27" s="33" t="s">
+      <c r="AD27" s="41" t="s">
         <v>19</v>
       </c>
       <c r="AE27" s="27"/>
       <c r="AF27" s="27"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="31">
+      <c r="A28" s="49">
         <v>17.0</v>
       </c>
-      <c r="B28" s="32">
+      <c r="B28" s="50">
         <v>0.6527777777777778</v>
       </c>
-      <c r="C28" s="33" t="s">
+      <c r="C28" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="D28" s="33" t="s">
+      <c r="D28" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="E28" s="33" t="s">
+      <c r="E28" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="F28" s="33" t="s">
+      <c r="F28" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="G28" s="31">
+      <c r="G28" s="49">
         <v>17.0</v>
       </c>
-      <c r="H28" s="32">
+      <c r="H28" s="50">
         <v>0.6527777777777778</v>
       </c>
-      <c r="I28" s="33" t="s">
+      <c r="I28" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="J28" s="33" t="s">
+      <c r="J28" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="K28" s="33" t="s">
+      <c r="K28" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="L28" s="33" t="s">
+      <c r="L28" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="M28" s="31">
+      <c r="M28" s="49">
         <v>17.0</v>
       </c>
-      <c r="N28" s="32">
+      <c r="N28" s="50">
         <v>0.6527777777777778</v>
       </c>
-      <c r="O28" s="38" t="s">
+      <c r="O28" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="P28" s="38" t="s">
+      <c r="P28" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="Q28" s="38" t="s">
+      <c r="Q28" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="R28" s="54" t="s">
+      <c r="R28" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="S28" s="36">
+      <c r="S28" s="33">
         <v>17.0</v>
       </c>
-      <c r="T28" s="43">
+      <c r="T28" s="42">
         <v>0.6527777777777778</v>
       </c>
-      <c r="U28" s="36"/>
-      <c r="V28" s="36"/>
-      <c r="W28" s="36"/>
-      <c r="X28" s="36"/>
-      <c r="Y28" s="31">
+      <c r="U28" s="33"/>
+      <c r="V28" s="33"/>
+      <c r="W28" s="33"/>
+      <c r="X28" s="33"/>
+      <c r="Y28" s="49">
         <v>17.0</v>
       </c>
-      <c r="Z28" s="32">
+      <c r="Z28" s="50">
         <v>0.6527777777777778</v>
       </c>
-      <c r="AA28" s="33" t="s">
+      <c r="AA28" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="AB28" s="33" t="s">
+      <c r="AB28" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="AC28" s="33" t="s">
+      <c r="AC28" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="AD28" s="33" t="s">
+      <c r="AD28" s="41" t="s">
         <v>19</v>
       </c>
       <c r="AE28" s="27"/>
       <c r="AF28" s="27"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="31">
+      <c r="A29" s="49">
         <v>18.0</v>
       </c>
-      <c r="B29" s="32">
+      <c r="B29" s="50">
         <v>0.6666666666666666</v>
       </c>
-      <c r="C29" s="33" t="s">
+      <c r="C29" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="D29" s="33" t="s">
+      <c r="D29" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="E29" s="33" t="s">
+      <c r="E29" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="F29" s="33" t="s">
+      <c r="F29" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="G29" s="36">
+      <c r="G29" s="33">
         <v>18.0</v>
       </c>
-      <c r="H29" s="43">
+      <c r="H29" s="42">
         <v>0.6666666666666666</v>
       </c>
-      <c r="I29" s="36"/>
-      <c r="J29" s="36"/>
-      <c r="K29" s="36"/>
-      <c r="L29" s="36"/>
-      <c r="M29" s="31">
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="49">
         <v>18.0</v>
       </c>
-      <c r="N29" s="32">
+      <c r="N29" s="50">
         <v>0.6666666666666666</v>
       </c>
-      <c r="O29" s="33" t="s">
+      <c r="O29" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="P29" s="33" t="s">
+      <c r="P29" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="Q29" s="33" t="s">
+      <c r="Q29" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="R29" s="33" t="s">
+      <c r="R29" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="S29" s="38">
+      <c r="S29" s="39">
         <v>18.0</v>
       </c>
-      <c r="T29" s="55">
+      <c r="T29" s="58">
         <v>0.6666666666666666</v>
       </c>
-      <c r="U29" s="46" t="s">
+      <c r="U29" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="V29" s="46" t="s">
+      <c r="V29" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="W29" s="46" t="s">
+      <c r="W29" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="X29" s="54" t="s">
+      <c r="X29" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="Y29" s="31">
+      <c r="Y29" s="49">
         <v>18.0</v>
       </c>
-      <c r="Z29" s="32">
+      <c r="Z29" s="50">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AA29" s="46" t="s">
+      <c r="AA29" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="AB29" s="46" t="s">
+      <c r="AB29" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="AC29" s="46" t="s">
+      <c r="AC29" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="AD29" s="56" t="s">
+      <c r="AD29" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="AE29" s="57"/>
-      <c r="AF29" s="58"/>
+      <c r="AE29" s="60"/>
+      <c r="AF29" s="61"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="31">
+      <c r="A30" s="49">
         <v>19.0</v>
       </c>
-      <c r="B30" s="32">
+      <c r="B30" s="50">
         <v>0.6805555555555556</v>
       </c>
-      <c r="C30" s="33" t="s">
+      <c r="C30" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="33" t="s">
+      <c r="D30" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="E30" s="33" t="s">
+      <c r="E30" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31">
+      <c r="F30" s="49"/>
+      <c r="G30" s="49">
         <v>19.0</v>
       </c>
-      <c r="H30" s="32">
+      <c r="H30" s="50">
         <v>0.6805555555555556</v>
       </c>
-      <c r="I30" s="33" t="s">
+      <c r="I30" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="J30" s="33" t="s">
+      <c r="J30" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="K30" s="33" t="s">
+      <c r="K30" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="L30" s="33" t="s">
+      <c r="L30" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="M30" s="31">
+      <c r="M30" s="49">
         <v>19.0</v>
       </c>
-      <c r="N30" s="32">
+      <c r="N30" s="50">
         <v>0.6805555555555556</v>
       </c>
-      <c r="O30" s="33" t="s">
+      <c r="O30" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="P30" s="33" t="s">
+      <c r="P30" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="Q30" s="33" t="s">
+      <c r="Q30" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="R30" s="33" t="s">
+      <c r="R30" s="41" t="s">
         <v>60</v>
       </c>
       <c r="S30" s="22">
@@ -2837,22 +2844,22 @@
       <c r="AF30" s="27"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="31">
+      <c r="A31" s="49">
         <v>20.0</v>
       </c>
-      <c r="B31" s="32">
+      <c r="B31" s="50">
         <v>0.6944444444444444</v>
       </c>
-      <c r="C31" s="33" t="s">
+      <c r="C31" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="D31" s="33" t="s">
+      <c r="D31" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="E31" s="33" t="s">
+      <c r="E31" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="F31" s="33" t="s">
+      <c r="F31" s="41" t="s">
         <v>16</v>
       </c>
       <c r="G31" s="22">
@@ -2865,18 +2872,18 @@
       <c r="J31" s="22"/>
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
-      <c r="M31" s="59">
+      <c r="M31" s="62">
         <v>20.0</v>
       </c>
-      <c r="N31" s="60">
+      <c r="N31" s="63">
         <v>0.6944444444444444</v>
       </c>
-      <c r="O31" s="61" t="s">
+      <c r="O31" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="P31" s="62"/>
-      <c r="Q31" s="62"/>
-      <c r="R31" s="63"/>
+      <c r="P31" s="65"/>
+      <c r="Q31" s="65"/>
+      <c r="R31" s="66"/>
       <c r="S31" s="22">
         <v>20.0</v>
       </c>
@@ -2921,18 +2928,18 @@
       <c r="J32" s="22"/>
       <c r="K32" s="22"/>
       <c r="L32" s="22"/>
-      <c r="M32" s="59">
+      <c r="M32" s="62">
         <v>21.0</v>
       </c>
-      <c r="N32" s="60">
+      <c r="N32" s="63">
         <v>0.7083333333333334</v>
       </c>
-      <c r="O32" s="61" t="s">
+      <c r="O32" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="P32" s="62"/>
-      <c r="Q32" s="62"/>
-      <c r="R32" s="63"/>
+      <c r="P32" s="65"/>
+      <c r="Q32" s="65"/>
+      <c r="R32" s="66"/>
       <c r="S32" s="22">
         <v>21.0</v>
       </c>
@@ -2977,18 +2984,18 @@
       <c r="J33" s="22"/>
       <c r="K33" s="22"/>
       <c r="L33" s="22"/>
-      <c r="M33" s="59">
+      <c r="M33" s="62">
         <v>22.0</v>
       </c>
-      <c r="N33" s="60">
+      <c r="N33" s="63">
         <v>0.7222222222222222</v>
       </c>
-      <c r="O33" s="61" t="s">
+      <c r="O33" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="P33" s="62"/>
-      <c r="Q33" s="62"/>
-      <c r="R33" s="63"/>
+      <c r="P33" s="65"/>
+      <c r="Q33" s="65"/>
+      <c r="R33" s="66"/>
       <c r="S33" s="22">
         <v>22.0</v>
       </c>
@@ -3035,18 +3042,18 @@
       <c r="J34" s="22"/>
       <c r="K34" s="22"/>
       <c r="L34" s="22"/>
-      <c r="M34" s="59">
+      <c r="M34" s="62">
         <v>23.0</v>
       </c>
-      <c r="N34" s="60">
+      <c r="N34" s="63">
         <v>0.7361111111111112</v>
       </c>
-      <c r="O34" s="61" t="s">
+      <c r="O34" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="P34" s="62"/>
-      <c r="Q34" s="62"/>
-      <c r="R34" s="63"/>
+      <c r="P34" s="65"/>
+      <c r="Q34" s="65"/>
+      <c r="R34" s="66"/>
       <c r="S34" s="22">
         <v>23.0</v>
       </c>
@@ -3091,18 +3098,18 @@
       <c r="J35" s="22"/>
       <c r="K35" s="22"/>
       <c r="L35" s="22"/>
-      <c r="M35" s="59">
+      <c r="M35" s="62">
         <v>24.0</v>
       </c>
-      <c r="N35" s="60">
+      <c r="N35" s="63">
         <v>0.75</v>
       </c>
-      <c r="O35" s="61" t="s">
+      <c r="O35" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="P35" s="62"/>
-      <c r="Q35" s="62"/>
-      <c r="R35" s="63"/>
+      <c r="P35" s="65"/>
+      <c r="Q35" s="65"/>
+      <c r="R35" s="66"/>
       <c r="S35" s="22">
         <v>24.0</v>
       </c>
@@ -3147,18 +3154,18 @@
       <c r="J36" s="22"/>
       <c r="K36" s="22"/>
       <c r="L36" s="22"/>
-      <c r="M36" s="59">
+      <c r="M36" s="62">
         <v>25.0</v>
       </c>
-      <c r="N36" s="60">
+      <c r="N36" s="63">
         <v>0.7638888888888888</v>
       </c>
-      <c r="O36" s="61" t="s">
+      <c r="O36" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="P36" s="62"/>
-      <c r="Q36" s="62"/>
-      <c r="R36" s="63"/>
+      <c r="P36" s="65"/>
+      <c r="Q36" s="65"/>
+      <c r="R36" s="66"/>
       <c r="S36" s="22">
         <v>25.0</v>
       </c>
@@ -3203,18 +3210,18 @@
       <c r="J37" s="22"/>
       <c r="K37" s="22"/>
       <c r="L37" s="22"/>
-      <c r="M37" s="59">
+      <c r="M37" s="62">
         <v>26.0</v>
       </c>
-      <c r="N37" s="60">
+      <c r="N37" s="63">
         <v>0.7777777777777778</v>
       </c>
-      <c r="O37" s="61" t="s">
+      <c r="O37" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="P37" s="62"/>
-      <c r="Q37" s="62"/>
-      <c r="R37" s="63"/>
+      <c r="P37" s="65"/>
+      <c r="Q37" s="65"/>
+      <c r="R37" s="66"/>
       <c r="S37" s="22">
         <v>26.0</v>
       </c>
@@ -3259,18 +3266,18 @@
       <c r="J38" s="22"/>
       <c r="K38" s="22"/>
       <c r="L38" s="22"/>
-      <c r="M38" s="59">
+      <c r="M38" s="62">
         <v>27.0</v>
       </c>
-      <c r="N38" s="60">
+      <c r="N38" s="63">
         <v>0.7916666666666666</v>
       </c>
-      <c r="O38" s="61" t="s">
+      <c r="O38" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="P38" s="62"/>
-      <c r="Q38" s="62"/>
-      <c r="R38" s="63"/>
+      <c r="P38" s="65"/>
+      <c r="Q38" s="65"/>
+      <c r="R38" s="66"/>
       <c r="S38" s="22">
         <v>27.0</v>
       </c>
@@ -3315,18 +3322,18 @@
       <c r="J39" s="22"/>
       <c r="K39" s="22"/>
       <c r="L39" s="22"/>
-      <c r="M39" s="59">
+      <c r="M39" s="62">
         <v>28.0</v>
       </c>
-      <c r="N39" s="60">
+      <c r="N39" s="63">
         <v>0.8055555555555556</v>
       </c>
-      <c r="O39" s="61" t="s">
+      <c r="O39" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="P39" s="62"/>
-      <c r="Q39" s="62"/>
-      <c r="R39" s="63"/>
+      <c r="P39" s="65"/>
+      <c r="Q39" s="65"/>
+      <c r="R39" s="66"/>
       <c r="S39" s="22">
         <v>28.0</v>
       </c>
@@ -3346,7 +3353,7 @@
       <c r="AA39" s="22"/>
       <c r="AB39" s="22"/>
       <c r="AC39" s="22"/>
-      <c r="AD39" s="64"/>
+      <c r="AD39" s="67"/>
       <c r="AE39" s="1"/>
       <c r="AF39" s="1"/>
     </row>
@@ -3371,18 +3378,18 @@
       <c r="J40" s="22"/>
       <c r="K40" s="22"/>
       <c r="L40" s="22"/>
-      <c r="M40" s="59">
+      <c r="M40" s="62">
         <v>29.0</v>
       </c>
-      <c r="N40" s="60">
+      <c r="N40" s="63">
         <v>0.8194444444444444</v>
       </c>
-      <c r="O40" s="61" t="s">
+      <c r="O40" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="P40" s="62"/>
-      <c r="Q40" s="62"/>
-      <c r="R40" s="63"/>
+      <c r="P40" s="65"/>
+      <c r="Q40" s="65"/>
+      <c r="R40" s="66"/>
       <c r="S40" s="22">
         <v>29.0</v>
       </c>
@@ -3402,7 +3409,7 @@
       <c r="AA40" s="22"/>
       <c r="AB40" s="22"/>
       <c r="AC40" s="22"/>
-      <c r="AD40" s="64"/>
+      <c r="AD40" s="67"/>
       <c r="AE40" s="1"/>
       <c r="AF40" s="1"/>
     </row>
@@ -3427,18 +3434,18 @@
       <c r="J41" s="22"/>
       <c r="K41" s="22"/>
       <c r="L41" s="22"/>
-      <c r="M41" s="59">
+      <c r="M41" s="62">
         <v>30.0</v>
       </c>
-      <c r="N41" s="60">
+      <c r="N41" s="63">
         <v>0.8333333333333334</v>
       </c>
-      <c r="O41" s="61" t="s">
+      <c r="O41" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="P41" s="62"/>
-      <c r="Q41" s="62"/>
-      <c r="R41" s="63"/>
+      <c r="P41" s="65"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="66"/>
       <c r="S41" s="22">
         <v>30.0</v>
       </c>
@@ -3458,7 +3465,7 @@
       <c r="AA41" s="22"/>
       <c r="AB41" s="22"/>
       <c r="AC41" s="22"/>
-      <c r="AD41" s="64"/>
+      <c r="AD41" s="67"/>
       <c r="AE41" s="1"/>
       <c r="AF41" s="1"/>
     </row>
@@ -3483,18 +3490,18 @@
       <c r="J42" s="22"/>
       <c r="K42" s="22"/>
       <c r="L42" s="22"/>
-      <c r="M42" s="59">
+      <c r="M42" s="62">
         <v>31.0</v>
       </c>
-      <c r="N42" s="60">
+      <c r="N42" s="63">
         <v>0.8472222222222222</v>
       </c>
-      <c r="O42" s="61" t="s">
+      <c r="O42" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="P42" s="62"/>
-      <c r="Q42" s="62"/>
-      <c r="R42" s="63"/>
+      <c r="P42" s="65"/>
+      <c r="Q42" s="65"/>
+      <c r="R42" s="66"/>
       <c r="S42" s="22">
         <v>31.0</v>
       </c>
@@ -3514,63 +3521,63 @@
       <c r="AA42" s="22"/>
       <c r="AB42" s="22"/>
       <c r="AC42" s="22"/>
-      <c r="AD42" s="64"/>
+      <c r="AD42" s="67"/>
       <c r="AE42" s="1"/>
       <c r="AF42" s="1"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="65">
+      <c r="A43" s="68">
         <v>32.0</v>
       </c>
-      <c r="B43" s="66">
+      <c r="B43" s="69">
         <v>0.8611111111111112</v>
       </c>
-      <c r="C43" s="65"/>
-      <c r="D43" s="65"/>
-      <c r="E43" s="65"/>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65">
+      <c r="C43" s="68"/>
+      <c r="D43" s="68"/>
+      <c r="E43" s="68"/>
+      <c r="F43" s="68"/>
+      <c r="G43" s="68">
         <v>32.0</v>
       </c>
-      <c r="H43" s="66">
+      <c r="H43" s="69">
         <v>0.8611111111111112</v>
       </c>
-      <c r="I43" s="65"/>
-      <c r="J43" s="65"/>
-      <c r="K43" s="65"/>
-      <c r="L43" s="65"/>
-      <c r="M43" s="67">
+      <c r="I43" s="68"/>
+      <c r="J43" s="68"/>
+      <c r="K43" s="68"/>
+      <c r="L43" s="68"/>
+      <c r="M43" s="70">
         <v>32.0</v>
       </c>
-      <c r="N43" s="68">
+      <c r="N43" s="71">
         <v>0.8611111111111112</v>
       </c>
-      <c r="O43" s="69" t="s">
+      <c r="O43" s="72" t="s">
         <v>80</v>
       </c>
-      <c r="P43" s="70"/>
-      <c r="Q43" s="70"/>
-      <c r="R43" s="71"/>
-      <c r="S43" s="65">
+      <c r="P43" s="73"/>
+      <c r="Q43" s="73"/>
+      <c r="R43" s="74"/>
+      <c r="S43" s="68">
         <v>32.0</v>
       </c>
-      <c r="T43" s="66">
+      <c r="T43" s="69">
         <v>0.8611111111111112</v>
       </c>
-      <c r="U43" s="65"/>
-      <c r="V43" s="65"/>
-      <c r="W43" s="65"/>
-      <c r="X43" s="65"/>
-      <c r="Y43" s="65">
+      <c r="U43" s="68"/>
+      <c r="V43" s="68"/>
+      <c r="W43" s="68"/>
+      <c r="X43" s="68"/>
+      <c r="Y43" s="68">
         <v>32.0</v>
       </c>
-      <c r="Z43" s="66">
+      <c r="Z43" s="69">
         <v>0.8611111111111112</v>
       </c>
-      <c r="AA43" s="65"/>
-      <c r="AB43" s="65"/>
-      <c r="AC43" s="65"/>
-      <c r="AD43" s="72"/>
+      <c r="AA43" s="68"/>
+      <c r="AB43" s="68"/>
+      <c r="AC43" s="68"/>
+      <c r="AD43" s="75"/>
       <c r="AE43" s="1"/>
       <c r="AF43" s="1"/>
     </row>

--- a/file_wisuda_4okt.xlsx
+++ b/file_wisuda_4okt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="83">
   <si>
     <t xml:space="preserve">Graduation Schedule 
 </t>
@@ -109,6 +109,9 @@
     <t>Widika Aden Agatha</t>
   </si>
   <si>
+    <t>fna</t>
+  </si>
+  <si>
     <t>Desni</t>
   </si>
   <si>
@@ -169,97 +172,100 @@
     <t>Aghnia Amalia</t>
   </si>
   <si>
+    <t>ƒ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bela</t>
+  </si>
+  <si>
+    <t>Riski Mulyawan Pangestu</t>
+  </si>
+  <si>
+    <t>Restu Alfareizzy</t>
+  </si>
+  <si>
+    <t>Silvia</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Andin</t>
+  </si>
+  <si>
+    <t>Fahmy Bagas</t>
+  </si>
+  <si>
+    <t>Sema</t>
+  </si>
+  <si>
+    <t>Fadlah Faqih Mashobih</t>
+  </si>
+  <si>
+    <t>alif</t>
+  </si>
+  <si>
+    <t>dp 200</t>
+  </si>
+  <si>
+    <t>Ridho</t>
+  </si>
+  <si>
+    <t>Indriyani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IN </t>
+  </si>
+  <si>
+    <t>Fakhrian Yoga Permana</t>
+  </si>
+  <si>
+    <t>Asrul Adiyanto</t>
+  </si>
+  <si>
+    <t>Nafa Aswanda</t>
+  </si>
+  <si>
+    <t>Rio Furqon</t>
+  </si>
+  <si>
+    <t>Ezar Nadhif</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Allez galan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ILham Zambrota</t>
+  </si>
+  <si>
+    <t>Graduation Premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dhabi</t>
+  </si>
+  <si>
+    <t>Hanan Aldi R</t>
+  </si>
+  <si>
+    <t>Rendy Ilhamsyah</t>
+  </si>
+  <si>
+    <t>Alif Arhansyah</t>
+  </si>
+  <si>
+    <t>Cibita</t>
+  </si>
+  <si>
     <t>Viona Pramudista</t>
   </si>
   <si>
-    <t xml:space="preserve"> Bela</t>
-  </si>
-  <si>
-    <t>Riski Mulyawan Pangestu</t>
-  </si>
-  <si>
-    <t>Restu Alfareizzy</t>
-  </si>
-  <si>
-    <t>Silvia</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Andin</t>
-  </si>
-  <si>
-    <t>Fahmy Bagas</t>
-  </si>
-  <si>
-    <t>Sema</t>
-  </si>
-  <si>
-    <t>Fadlah Faqih Mashobih</t>
-  </si>
-  <si>
-    <t>alif</t>
-  </si>
-  <si>
-    <t>dp 200</t>
-  </si>
-  <si>
-    <t>Ridho</t>
-  </si>
-  <si>
-    <t>Indriyani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IN </t>
-  </si>
-  <si>
-    <t>Fakhrian Yoga Permana</t>
-  </si>
-  <si>
-    <t>Asrul Adiyanto</t>
-  </si>
-  <si>
-    <t>Nafa Aswanda</t>
-  </si>
-  <si>
-    <t>Rio Furqon</t>
+    <t>Renaldy</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
   </si>
   <si>
     <t>Febby</t>
-  </si>
-  <si>
-    <t>Graduation Premium</t>
-  </si>
-  <si>
-    <t>Renaldy</t>
-  </si>
-  <si>
-    <t>Ezar Nadhif</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Allez galan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ILham Zambrota</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Dhabi</t>
-  </si>
-  <si>
-    <t>Hanan Aldi R</t>
-  </si>
-  <si>
-    <t>Rendy Ilhamsyah</t>
-  </si>
-  <si>
-    <t>Alif Arhansyah</t>
-  </si>
-  <si>
-    <t>Cibita</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
   </si>
 </sst>
 </file>
@@ -349,7 +355,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -408,12 +414,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor rgb="FFFF0000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-        <bgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -563,7 +563,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="72">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -668,72 +668,63 @@
     <xf borderId="5" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="11" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="6" fillId="9" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="5" fillId="10" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="6" fillId="9" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="5" fillId="9" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="7" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="10" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="6" fillId="9" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="6" fillId="11" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="7" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="6" fillId="11" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="11" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="8" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="9" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="8" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -742,13 +733,10 @@
     <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="8" fillId="12" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="8" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="9" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -762,13 +750,13 @@
     <xf borderId="10" fillId="0" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="10" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="10" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="10" fillId="12" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="10" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="11" fillId="12" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="11" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="12" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -796,7 +784,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image2.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -824,7 +812,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.jpg"/>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -852,7 +840,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -880,7 +868,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image5.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -908,7 +896,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -936,7 +924,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1168,7 +1156,7 @@
     <col customWidth="1" min="6" max="6" width="11.63"/>
     <col customWidth="1" min="7" max="7" width="5.25"/>
     <col customWidth="1" min="8" max="8" width="9.88"/>
-    <col customWidth="1" min="9" max="9" width="19.13"/>
+    <col customWidth="1" min="9" max="9" width="22.75"/>
     <col customWidth="1" min="10" max="10" width="17.0"/>
     <col customWidth="1" min="11" max="11" width="9.25"/>
     <col customWidth="1" min="12" max="12" width="11.63"/>
@@ -1897,13 +1885,13 @@
       <c r="U19" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="V19" s="36" t="s">
+      <c r="V19" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="W19" s="36" t="s">
+      <c r="W19" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="X19" s="36" t="s">
+      <c r="X19" s="35" t="s">
         <v>19</v>
       </c>
       <c r="Y19" s="29">
@@ -1912,20 +1900,20 @@
       <c r="Z19" s="30">
         <v>0.5208333333333334</v>
       </c>
-      <c r="AA19" s="37" t="s">
+      <c r="AA19" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="AB19" s="38" t="s">
+      <c r="AB19" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="AC19" s="38" t="s">
+      <c r="AC19" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="AD19" s="39" t="s">
+      <c r="AD19" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="AE19" s="40"/>
-      <c r="AF19" s="40"/>
+      <c r="AE19" s="38"/>
+      <c r="AF19" s="38"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="24">
@@ -1934,42 +1922,44 @@
       <c r="B20" s="25">
         <v>0.5416666666666666</v>
       </c>
-      <c r="C20" s="41" t="s">
+      <c r="C20" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="41" t="s">
+      <c r="D20" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="F20" s="41"/>
+      <c r="E20" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>19</v>
+      </c>
       <c r="G20" s="33">
         <v>9.0</v>
       </c>
-      <c r="H20" s="42">
+      <c r="H20" s="39">
         <v>0.5416666666666666</v>
       </c>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="43"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="40"/>
       <c r="M20" s="24">
         <v>9.0</v>
       </c>
       <c r="N20" s="25">
         <v>0.5416666666666666</v>
       </c>
-      <c r="O20" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="P20" s="45" t="s">
+      <c r="O20" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="P20" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="Q20" s="45" t="s">
+      <c r="Q20" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="R20" s="41" t="s">
+      <c r="R20" s="26" t="s">
         <v>19</v>
       </c>
       <c r="S20" s="24">
@@ -1978,16 +1968,16 @@
       <c r="T20" s="25">
         <v>0.5416666666666666</v>
       </c>
-      <c r="U20" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="V20" s="41" t="s">
+      <c r="U20" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="V20" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="W20" s="41" t="s">
+      <c r="W20" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="X20" s="41" t="s">
+      <c r="X20" s="26" t="s">
         <v>19</v>
       </c>
       <c r="Y20" s="29">
@@ -1996,126 +1986,126 @@
       <c r="Z20" s="30">
         <v>0.5416666666666666</v>
       </c>
-      <c r="AA20" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB20" s="38" t="s">
+      <c r="AA20" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB20" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="AC20" s="38" t="s">
+      <c r="AC20" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="AD20" s="47"/>
-      <c r="AE20" s="48"/>
-      <c r="AF20" s="48"/>
+      <c r="AD20" s="43"/>
+      <c r="AE20" s="44"/>
+      <c r="AF20" s="44"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="33">
         <v>10.0</v>
       </c>
-      <c r="B21" s="42">
+      <c r="B21" s="39">
         <v>0.5555555555555556</v>
       </c>
-      <c r="C21" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="49">
+      <c r="C21" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="24">
         <v>10.0</v>
       </c>
-      <c r="H21" s="50">
+      <c r="H21" s="25">
         <v>0.5555555555555556</v>
       </c>
-      <c r="I21" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="J21" s="41" t="s">
+      <c r="I21" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="K21" s="41" t="s">
+      <c r="J21" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="K21" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="L21" s="41" t="s">
+      <c r="L21" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="M21" s="49">
+      <c r="M21" s="24">
         <v>10.0</v>
       </c>
-      <c r="N21" s="50">
+      <c r="N21" s="25">
         <v>0.5555555555555556</v>
       </c>
-      <c r="O21" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="P21" s="52" t="s">
+      <c r="O21" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="P21" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="Q21" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="R21" s="39" t="s">
+      <c r="Q21" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="R21" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="S21" s="49">
+      <c r="S21" s="24">
         <v>10.0</v>
       </c>
-      <c r="T21" s="50">
+      <c r="T21" s="25">
         <v>0.5555555555555556</v>
       </c>
-      <c r="U21" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="V21" s="41" t="s">
+      <c r="U21" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="V21" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="W21" s="41" t="s">
+      <c r="W21" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="X21" s="49"/>
+      <c r="X21" s="24"/>
       <c r="Y21" s="24">
         <v>10.0</v>
       </c>
       <c r="Z21" s="25">
         <v>0.5555555555555556</v>
       </c>
-      <c r="AA21" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB21" s="41" t="s">
+      <c r="AA21" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB21" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="AC21" s="41" t="s">
+      <c r="AC21" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="AD21" s="49"/>
+      <c r="AD21" s="24"/>
       <c r="AE21" s="27"/>
       <c r="AF21" s="27"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="49">
+      <c r="A22" s="24">
         <v>11.0</v>
       </c>
-      <c r="B22" s="50">
+      <c r="B22" s="25">
         <v>0.5694444444444444</v>
       </c>
-      <c r="C22" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="E22" s="41" t="s">
+      <c r="C22" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F22" s="41" t="s">
+      <c r="F22" s="26" t="s">
         <v>19</v>
       </c>
       <c r="G22" s="33">
         <v>11.0</v>
       </c>
-      <c r="H22" s="42">
+      <c r="H22" s="39">
         <v>0.5694444444444444</v>
       </c>
       <c r="I22" s="33"/>
@@ -2128,214 +2118,202 @@
       <c r="N22" s="25">
         <v>0.5694444444444444</v>
       </c>
-      <c r="O22" s="53" t="s">
-        <v>41</v>
-      </c>
-      <c r="P22" s="41" t="s">
+      <c r="O22" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="P22" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="Q22" s="41" t="s">
+      <c r="Q22" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="R22" s="49"/>
-      <c r="S22" s="49">
+      <c r="R22" s="24"/>
+      <c r="S22" s="47">
         <v>11.0</v>
       </c>
-      <c r="T22" s="50">
+      <c r="T22" s="48">
         <v>0.5694444444444444</v>
       </c>
-      <c r="U22" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="V22" s="41" t="s">
+      <c r="U22" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="V22" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="W22" s="41" t="s">
+      <c r="W22" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="X22" s="41" t="s">
+      <c r="X22" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="Y22" s="49">
+      <c r="Y22" s="24">
         <v>11.0</v>
       </c>
-      <c r="Z22" s="50">
+      <c r="Z22" s="25">
         <v>0.5694444444444444</v>
       </c>
-      <c r="AA22" s="41" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB22" s="41" t="s">
+      <c r="AA22" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB22" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="AC22" s="41" t="s">
+      <c r="AC22" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="AD22" s="41" t="s">
+      <c r="AD22" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="AE22" s="54"/>
-      <c r="AF22" s="54"/>
+      <c r="AE22" s="50"/>
+      <c r="AF22" s="50"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="39">
+      <c r="A23" s="29">
         <v>13.0</v>
       </c>
-      <c r="B23" s="50">
+      <c r="B23" s="25">
         <v>0.5833333333333334</v>
       </c>
-      <c r="C23" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" s="39" t="s">
+      <c r="C23" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="39" t="s">
+      <c r="E23" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="F23" s="39" t="s">
+      <c r="F23" s="29" t="s">
         <v>19</v>
       </c>
       <c r="G23" s="33">
         <v>12.0</v>
       </c>
-      <c r="H23" s="42">
+      <c r="H23" s="39">
         <v>0.5833333333333334</v>
       </c>
       <c r="I23" s="33"/>
-      <c r="J23" s="55"/>
+      <c r="J23" s="51"/>
       <c r="K23" s="33"/>
       <c r="L23" s="33"/>
-      <c r="M23" s="49">
+      <c r="M23" s="24">
         <v>12.0</v>
       </c>
-      <c r="N23" s="50">
+      <c r="N23" s="25">
         <v>0.5833333333333334</v>
       </c>
-      <c r="O23" s="56" t="s">
-        <v>45</v>
-      </c>
-      <c r="P23" s="39" t="s">
+      <c r="O23" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="P23" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="Q23" s="39" t="s">
+      <c r="Q23" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="R23" s="39"/>
-      <c r="S23" s="49">
+      <c r="R23" s="29"/>
+      <c r="S23" s="24">
         <v>12.0</v>
       </c>
-      <c r="T23" s="50">
+      <c r="T23" s="25">
         <v>0.5833333333333334</v>
       </c>
-      <c r="U23" s="41" t="s">
-        <v>46</v>
-      </c>
-      <c r="V23" s="41" t="s">
+      <c r="U23" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="V23" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="W23" s="41" t="s">
+      <c r="W23" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="X23" s="41" t="s">
+      <c r="X23" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="Y23" s="49">
+      <c r="Y23" s="24">
         <v>12.0</v>
       </c>
-      <c r="Z23" s="50">
+      <c r="Z23" s="25">
         <v>0.5833333333333334</v>
       </c>
-      <c r="AA23" s="39" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB23" s="39" t="s">
+      <c r="AA23" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB23" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="AC23" s="39" t="s">
+      <c r="AC23" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="AD23" s="51"/>
+      <c r="AD23" s="45"/>
       <c r="AE23" s="27"/>
       <c r="AF23" s="27"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="41">
+      <c r="A24" s="26">
         <v>14.0</v>
       </c>
-      <c r="B24" s="50">
+      <c r="B24" s="25">
         <v>0.5972222222222222</v>
       </c>
-      <c r="C24" s="41" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24" s="41" t="s">
+      <c r="C24" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="41" t="s">
+      <c r="E24" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F24" s="41" t="s">
+      <c r="F24" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="G24" s="49">
+      <c r="G24" s="24">
         <v>13.0</v>
       </c>
-      <c r="H24" s="50">
+      <c r="H24" s="25">
         <v>0.5972222222222222</v>
       </c>
-      <c r="I24" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="J24" s="41" t="s">
+      <c r="I24" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="J24" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="K24" s="41" t="s">
+      <c r="K24" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="L24" s="41" t="s">
+      <c r="L24" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="M24" s="49">
+      <c r="M24" s="22">
         <v>13.0</v>
       </c>
-      <c r="N24" s="50">
+      <c r="N24" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="S24" s="24">
+        <v>13.0</v>
+      </c>
+      <c r="T24" s="25">
         <v>0.5972222222222222</v>
       </c>
-      <c r="O24" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="P24" s="39" t="s">
+      <c r="U24" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="V24" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="Q24" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="R24" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="S24" s="49">
-        <v>13.0</v>
-      </c>
-      <c r="T24" s="50">
-        <v>0.5972222222222222</v>
-      </c>
-      <c r="U24" s="41" t="s">
-        <v>51</v>
-      </c>
-      <c r="V24" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="W24" s="41" t="s">
+      <c r="W24" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="X24" s="41" t="s">
+      <c r="X24" s="26" t="s">
         <v>19</v>
       </c>
       <c r="Y24" s="33">
         <v>13.0</v>
       </c>
-      <c r="Z24" s="42">
+      <c r="Z24" s="39">
         <v>0.5972222222222222</v>
       </c>
       <c r="AA24" s="33"/>
@@ -2349,81 +2327,81 @@
       <c r="A25" s="33">
         <v>14.0</v>
       </c>
-      <c r="B25" s="42">
+      <c r="B25" s="39">
         <v>0.6111111111111112</v>
       </c>
       <c r="C25" s="33"/>
       <c r="D25" s="33"/>
       <c r="E25" s="33"/>
       <c r="F25" s="33"/>
-      <c r="G25" s="49">
+      <c r="G25" s="24">
         <v>14.0</v>
       </c>
-      <c r="H25" s="50">
+      <c r="H25" s="25">
         <v>0.6111111111111112</v>
       </c>
-      <c r="I25" s="41" t="s">
-        <v>52</v>
-      </c>
-      <c r="J25" s="41" t="s">
+      <c r="I25" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="J25" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="K25" s="41" t="s">
+      <c r="K25" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="L25" s="41" t="s">
+      <c r="L25" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="M25" s="49">
+      <c r="M25" s="24">
         <v>14.0</v>
       </c>
-      <c r="N25" s="50">
+      <c r="N25" s="25">
         <v>0.6111111111111112</v>
       </c>
-      <c r="O25" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="P25" s="41" t="s">
+      <c r="O25" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="P25" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="Q25" s="41" t="s">
+      <c r="Q25" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="R25" s="49"/>
-      <c r="S25" s="49">
+      <c r="R25" s="24"/>
+      <c r="S25" s="24">
         <v>14.0</v>
       </c>
-      <c r="T25" s="50">
+      <c r="T25" s="25">
         <v>0.6111111111111112</v>
       </c>
-      <c r="U25" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="V25" s="41" t="s">
+      <c r="U25" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="V25" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="W25" s="41" t="s">
+      <c r="W25" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="X25" s="41" t="s">
+      <c r="X25" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="Y25" s="49">
+      <c r="Y25" s="24">
         <v>14.0</v>
       </c>
-      <c r="Z25" s="50">
+      <c r="Z25" s="25">
         <v>0.6111111111111112</v>
       </c>
-      <c r="AA25" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB25" s="41" t="s">
+      <c r="AA25" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB25" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="AC25" s="41" t="s">
+      <c r="AC25" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="AD25" s="41" t="s">
+      <c r="AD25" s="26" t="s">
         <v>19</v>
       </c>
       <c r="AE25" s="27"/>
@@ -2433,392 +2411,376 @@
       <c r="A26" s="33">
         <v>15.0</v>
       </c>
-      <c r="B26" s="42">
+      <c r="B26" s="39">
         <v>0.625</v>
       </c>
-      <c r="C26" s="43"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
       <c r="F26" s="33"/>
-      <c r="G26" s="49">
+      <c r="G26" s="24">
         <v>15.0</v>
       </c>
-      <c r="H26" s="50">
+      <c r="H26" s="25">
         <v>0.625</v>
       </c>
-      <c r="I26" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="J26" s="41" t="s">
+      <c r="I26" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="J26" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="K26" s="41" t="s">
+      <c r="K26" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="L26" s="41" t="s">
+      <c r="L26" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="M26" s="49">
+      <c r="M26" s="24">
         <v>15.0</v>
       </c>
-      <c r="N26" s="50">
+      <c r="N26" s="25">
         <v>0.625</v>
       </c>
-      <c r="O26" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="P26" s="41" t="s">
+      <c r="O26" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="P26" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="Q26" s="41" t="s">
+      <c r="Q26" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="R26" s="49"/>
-      <c r="S26" s="49">
+      <c r="R26" s="24"/>
+      <c r="S26" s="24">
         <v>15.0</v>
       </c>
-      <c r="T26" s="50">
+      <c r="T26" s="25">
         <v>0.625</v>
       </c>
-      <c r="U26" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="V26" s="41" t="s">
+      <c r="U26" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="V26" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="W26" s="41" t="s">
+      <c r="W26" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="X26" s="41" t="s">
+      <c r="X26" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="Y26" s="49">
+      <c r="Y26" s="24">
         <v>15.0</v>
       </c>
-      <c r="Z26" s="50">
+      <c r="Z26" s="25">
         <v>0.625</v>
       </c>
-      <c r="AA26" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="AB26" s="41" t="s">
+      <c r="AA26" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB26" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="AC26" s="41" t="s">
+      <c r="AC26" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="AD26" s="41" t="s">
-        <v>60</v>
+      <c r="AD26" s="26" t="s">
+        <v>61</v>
       </c>
       <c r="AE26" s="27"/>
       <c r="AF26" s="27"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="49">
+      <c r="A27" s="24">
         <v>16.0</v>
       </c>
-      <c r="B27" s="50">
+      <c r="B27" s="25">
         <v>0.6388888888888888</v>
       </c>
-      <c r="C27" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="D27" s="41" t="s">
+      <c r="C27" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="49">
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="47">
         <v>16.0</v>
       </c>
-      <c r="H27" s="50">
+      <c r="H27" s="48">
         <v>0.6388888888888888</v>
       </c>
-      <c r="I27" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="J27" s="41" t="s">
+      <c r="I27" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="J27" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="K27" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="L27" s="41" t="s">
+      <c r="K27" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="L27" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="M27" s="49">
+      <c r="M27" s="24">
         <v>16.0</v>
       </c>
-      <c r="N27" s="50">
+      <c r="N27" s="25">
         <v>0.6388888888888888</v>
       </c>
-      <c r="O27" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="P27" s="41" t="s">
+      <c r="O27" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="P27" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="Q27" s="41" t="s">
+      <c r="Q27" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="R27" s="41" t="s">
+      <c r="R27" s="26" t="s">
         <v>19</v>
       </c>
       <c r="S27" s="33">
         <v>16.0</v>
       </c>
-      <c r="T27" s="42">
+      <c r="T27" s="39">
         <v>0.6388888888888888</v>
       </c>
       <c r="U27" s="33"/>
       <c r="V27" s="33"/>
       <c r="W27" s="33"/>
       <c r="X27" s="33"/>
-      <c r="Y27" s="49">
+      <c r="Y27" s="24">
         <v>16.0</v>
       </c>
-      <c r="Z27" s="50">
+      <c r="Z27" s="25">
         <v>0.6388888888888888</v>
       </c>
-      <c r="AA27" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB27" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC27" s="41" t="s">
+      <c r="AA27" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB27" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC27" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="AD27" s="41" t="s">
+      <c r="AD27" s="26" t="s">
         <v>19</v>
       </c>
       <c r="AE27" s="27"/>
       <c r="AF27" s="27"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="49">
+      <c r="A28" s="47">
         <v>17.0</v>
       </c>
-      <c r="B28" s="50">
+      <c r="B28" s="48">
         <v>0.6527777777777778</v>
       </c>
-      <c r="C28" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="D28" s="41" t="s">
+      <c r="C28" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="E28" s="41" t="s">
+      <c r="E28" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="F28" s="41" t="s">
+      <c r="F28" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="G28" s="49">
+      <c r="G28" s="24">
         <v>17.0</v>
       </c>
-      <c r="H28" s="50">
+      <c r="H28" s="25">
         <v>0.6527777777777778</v>
       </c>
-      <c r="I28" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="J28" s="41" t="s">
+      <c r="I28" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="J28" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="K28" s="41" t="s">
+      <c r="K28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="L28" s="41" t="s">
+      <c r="L28" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="M28" s="49">
+      <c r="M28" s="22">
         <v>17.0</v>
       </c>
-      <c r="N28" s="50">
+      <c r="N28" s="23">
         <v>0.6527777777777778</v>
       </c>
-      <c r="O28" s="39" t="s">
-        <v>68</v>
-      </c>
-      <c r="P28" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q28" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="R28" s="57" t="s">
-        <v>19</v>
-      </c>
+      <c r="O28" s="53"/>
+      <c r="P28" s="53"/>
+      <c r="Q28" s="53"/>
+      <c r="R28" s="54"/>
       <c r="S28" s="33">
         <v>17.0</v>
       </c>
-      <c r="T28" s="42">
+      <c r="T28" s="39">
         <v>0.6527777777777778</v>
       </c>
       <c r="U28" s="33"/>
       <c r="V28" s="33"/>
       <c r="W28" s="33"/>
       <c r="X28" s="33"/>
-      <c r="Y28" s="49">
+      <c r="Y28" s="22">
         <v>17.0</v>
       </c>
-      <c r="Z28" s="50">
+      <c r="Z28" s="23">
         <v>0.6527777777777778</v>
       </c>
-      <c r="AA28" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB28" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC28" s="41" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD28" s="41" t="s">
-        <v>19</v>
-      </c>
+      <c r="AA28" s="28"/>
+      <c r="AB28" s="28"/>
+      <c r="AC28" s="28"/>
+      <c r="AD28" s="28"/>
       <c r="AE28" s="27"/>
       <c r="AF28" s="27"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="49">
+      <c r="A29" s="24">
         <v>18.0</v>
       </c>
-      <c r="B29" s="50">
+      <c r="B29" s="25">
         <v>0.6666666666666666</v>
       </c>
-      <c r="C29" s="41" t="s">
-        <v>71</v>
-      </c>
-      <c r="D29" s="41" t="s">
+      <c r="C29" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E29" s="41" t="s">
+      <c r="E29" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F29" s="41" t="s">
+      <c r="F29" s="26" t="s">
         <v>19</v>
       </c>
       <c r="G29" s="33">
         <v>18.0</v>
       </c>
-      <c r="H29" s="42">
+      <c r="H29" s="39">
         <v>0.6666666666666666</v>
       </c>
       <c r="I29" s="33"/>
       <c r="J29" s="33"/>
       <c r="K29" s="33"/>
       <c r="L29" s="33"/>
-      <c r="M29" s="49">
+      <c r="M29" s="24">
         <v>18.0</v>
       </c>
-      <c r="N29" s="50">
+      <c r="N29" s="25">
         <v>0.6666666666666666</v>
       </c>
-      <c r="O29" s="41" t="s">
+      <c r="O29" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="P29" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q29" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="R29" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="S29" s="29">
+        <v>18.0</v>
+      </c>
+      <c r="T29" s="30">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="U29" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="P29" s="41" t="s">
+      <c r="V29" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="W29" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="X29" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y29" s="24">
+        <v>18.0</v>
+      </c>
+      <c r="Z29" s="25">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AA29" s="42" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB29" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="Q29" s="41" t="s">
-        <v>73</v>
-      </c>
-      <c r="R29" s="41" t="s">
+      <c r="AC29" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD29" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="S29" s="39">
-        <v>18.0</v>
-      </c>
-      <c r="T29" s="58">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="U29" s="45" t="s">
-        <v>74</v>
-      </c>
-      <c r="V29" s="45" t="s">
-        <v>69</v>
-      </c>
-      <c r="W29" s="45" t="s">
-        <v>24</v>
-      </c>
-      <c r="X29" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y29" s="49">
-        <v>18.0</v>
-      </c>
-      <c r="Z29" s="50">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AA29" s="45" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB29" s="45" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC29" s="45" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD29" s="59" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE29" s="60"/>
-      <c r="AF29" s="61"/>
+      <c r="AE29" s="57"/>
+      <c r="AF29" s="58"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="49">
+      <c r="A30" s="24">
         <v>19.0</v>
       </c>
-      <c r="B30" s="50">
+      <c r="B30" s="25">
         <v>0.6805555555555556</v>
       </c>
-      <c r="C30" s="41" t="s">
+      <c r="C30" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24">
+        <v>19.0</v>
+      </c>
+      <c r="H30" s="25">
+        <v>0.6805555555555556</v>
+      </c>
+      <c r="I30" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="41" t="s">
+      <c r="J30" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E30" s="41" t="s">
+      <c r="K30" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="L30" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M30" s="47">
+        <v>19.0</v>
+      </c>
+      <c r="N30" s="48">
+        <v>0.6805555555555556</v>
+      </c>
+      <c r="O30" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="P30" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q30" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="F30" s="49"/>
-      <c r="G30" s="49">
-        <v>19.0</v>
-      </c>
-      <c r="H30" s="50">
-        <v>0.6805555555555556</v>
-      </c>
-      <c r="I30" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="J30" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="K30" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="L30" s="41" t="s">
-        <v>19</v>
-      </c>
-      <c r="M30" s="49">
-        <v>19.0</v>
-      </c>
-      <c r="N30" s="50">
-        <v>0.6805555555555556</v>
-      </c>
-      <c r="O30" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="P30" s="41" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q30" s="41" t="s">
-        <v>15</v>
-      </c>
-      <c r="R30" s="41" t="s">
-        <v>60</v>
+      <c r="R30" s="49" t="s">
+        <v>61</v>
       </c>
       <c r="S30" s="22">
         <v>19.0</v>
@@ -2826,40 +2788,40 @@
       <c r="T30" s="23">
         <v>0.6805555555555556</v>
       </c>
-      <c r="U30" s="22"/>
-      <c r="V30" s="22"/>
-      <c r="W30" s="22"/>
-      <c r="X30" s="22"/>
-      <c r="Y30" s="22">
+      <c r="U30" s="28"/>
+      <c r="V30" s="28"/>
+      <c r="W30" s="28"/>
+      <c r="X30" s="28"/>
+      <c r="Y30" s="33">
         <v>19.0</v>
       </c>
-      <c r="Z30" s="23">
+      <c r="Z30" s="39">
         <v>0.6805555555555556</v>
       </c>
-      <c r="AA30" s="22"/>
-      <c r="AB30" s="22"/>
-      <c r="AC30" s="22"/>
-      <c r="AD30" s="22"/>
+      <c r="AA30" s="33"/>
+      <c r="AB30" s="33"/>
+      <c r="AC30" s="33"/>
+      <c r="AD30" s="33"/>
       <c r="AE30" s="27"/>
       <c r="AF30" s="27"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="49">
+      <c r="A31" s="24">
         <v>20.0</v>
       </c>
-      <c r="B31" s="50">
+      <c r="B31" s="25">
         <v>0.6944444444444444</v>
       </c>
-      <c r="C31" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="D31" s="41" t="s">
+      <c r="C31" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="D31" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E31" s="41" t="s">
+      <c r="E31" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="F31" s="41" t="s">
+      <c r="F31" s="26" t="s">
         <v>16</v>
       </c>
       <c r="G31" s="22">
@@ -2872,18 +2834,24 @@
       <c r="J31" s="22"/>
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
-      <c r="M31" s="62">
+      <c r="M31" s="24">
         <v>20.0</v>
       </c>
-      <c r="N31" s="63">
+      <c r="N31" s="25">
         <v>0.6944444444444444</v>
       </c>
-      <c r="O31" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="P31" s="65"/>
-      <c r="Q31" s="65"/>
-      <c r="R31" s="66"/>
+      <c r="O31" s="59" t="s">
+        <v>79</v>
+      </c>
+      <c r="P31" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q31" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="R31" s="29" t="s">
+        <v>19</v>
+      </c>
       <c r="S31" s="22">
         <v>20.0</v>
       </c>
@@ -2894,16 +2862,24 @@
       <c r="V31" s="22"/>
       <c r="W31" s="22"/>
       <c r="X31" s="22"/>
-      <c r="Y31" s="22">
+      <c r="Y31" s="24">
         <v>20.0</v>
       </c>
-      <c r="Z31" s="23">
+      <c r="Z31" s="25">
         <v>0.6944444444444444</v>
       </c>
-      <c r="AA31" s="22"/>
-      <c r="AB31" s="22"/>
-      <c r="AC31" s="22"/>
-      <c r="AD31" s="22"/>
+      <c r="AA31" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB31" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC31" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD31" s="29" t="s">
+        <v>19</v>
+      </c>
       <c r="AE31" s="27"/>
       <c r="AF31" s="27"/>
     </row>
@@ -2928,28 +2904,36 @@
       <c r="J32" s="22"/>
       <c r="K32" s="22"/>
       <c r="L32" s="22"/>
-      <c r="M32" s="62">
+      <c r="M32" s="47">
         <v>21.0</v>
       </c>
-      <c r="N32" s="63">
+      <c r="N32" s="48">
         <v>0.7083333333333334</v>
       </c>
-      <c r="O32" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="P32" s="65"/>
-      <c r="Q32" s="65"/>
-      <c r="R32" s="66"/>
-      <c r="S32" s="22">
+      <c r="O32" s="60" t="s">
+        <v>81</v>
+      </c>
+      <c r="P32" s="61"/>
+      <c r="Q32" s="61"/>
+      <c r="R32" s="62"/>
+      <c r="S32" s="24">
         <v>21.0</v>
       </c>
-      <c r="T32" s="23">
+      <c r="T32" s="25">
         <v>0.7083333333333334</v>
       </c>
-      <c r="U32" s="22"/>
-      <c r="V32" s="22"/>
-      <c r="W32" s="22"/>
-      <c r="X32" s="22"/>
+      <c r="U32" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="V32" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="W32" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="X32" s="55" t="s">
+        <v>19</v>
+      </c>
       <c r="Y32" s="22">
         <v>21.0</v>
       </c>
@@ -2984,18 +2968,18 @@
       <c r="J33" s="22"/>
       <c r="K33" s="22"/>
       <c r="L33" s="22"/>
-      <c r="M33" s="62">
+      <c r="M33" s="47">
         <v>22.0</v>
       </c>
-      <c r="N33" s="63">
+      <c r="N33" s="48">
         <v>0.7222222222222222</v>
       </c>
-      <c r="O33" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="P33" s="65"/>
-      <c r="Q33" s="65"/>
-      <c r="R33" s="66"/>
+      <c r="O33" s="60" t="s">
+        <v>81</v>
+      </c>
+      <c r="P33" s="61"/>
+      <c r="Q33" s="61"/>
+      <c r="R33" s="62"/>
       <c r="S33" s="22">
         <v>22.0</v>
       </c>
@@ -3013,7 +2997,7 @@
         <v>0.7222222222222222</v>
       </c>
       <c r="AA33" s="22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AB33" s="22"/>
       <c r="AC33" s="22"/>
@@ -3042,18 +3026,18 @@
       <c r="J34" s="22"/>
       <c r="K34" s="22"/>
       <c r="L34" s="22"/>
-      <c r="M34" s="62">
+      <c r="M34" s="47">
         <v>23.0</v>
       </c>
-      <c r="N34" s="63">
+      <c r="N34" s="48">
         <v>0.7361111111111112</v>
       </c>
-      <c r="O34" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="P34" s="65"/>
-      <c r="Q34" s="65"/>
-      <c r="R34" s="66"/>
+      <c r="O34" s="60" t="s">
+        <v>81</v>
+      </c>
+      <c r="P34" s="61"/>
+      <c r="Q34" s="61"/>
+      <c r="R34" s="62"/>
       <c r="S34" s="22">
         <v>23.0</v>
       </c>
@@ -3098,18 +3082,18 @@
       <c r="J35" s="22"/>
       <c r="K35" s="22"/>
       <c r="L35" s="22"/>
-      <c r="M35" s="62">
+      <c r="M35" s="47">
         <v>24.0</v>
       </c>
-      <c r="N35" s="63">
+      <c r="N35" s="48">
         <v>0.75</v>
       </c>
-      <c r="O35" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="P35" s="65"/>
-      <c r="Q35" s="65"/>
-      <c r="R35" s="66"/>
+      <c r="O35" s="60" t="s">
+        <v>81</v>
+      </c>
+      <c r="P35" s="61"/>
+      <c r="Q35" s="61"/>
+      <c r="R35" s="62"/>
       <c r="S35" s="22">
         <v>24.0</v>
       </c>
@@ -3154,18 +3138,18 @@
       <c r="J36" s="22"/>
       <c r="K36" s="22"/>
       <c r="L36" s="22"/>
-      <c r="M36" s="62">
+      <c r="M36" s="47">
         <v>25.0</v>
       </c>
-      <c r="N36" s="63">
+      <c r="N36" s="48">
         <v>0.7638888888888888</v>
       </c>
-      <c r="O36" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="P36" s="65"/>
-      <c r="Q36" s="65"/>
-      <c r="R36" s="66"/>
+      <c r="O36" s="60" t="s">
+        <v>81</v>
+      </c>
+      <c r="P36" s="61"/>
+      <c r="Q36" s="61"/>
+      <c r="R36" s="62"/>
       <c r="S36" s="22">
         <v>25.0</v>
       </c>
@@ -3210,18 +3194,18 @@
       <c r="J37" s="22"/>
       <c r="K37" s="22"/>
       <c r="L37" s="22"/>
-      <c r="M37" s="62">
+      <c r="M37" s="47">
         <v>26.0</v>
       </c>
-      <c r="N37" s="63">
+      <c r="N37" s="48">
         <v>0.7777777777777778</v>
       </c>
-      <c r="O37" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="P37" s="65"/>
-      <c r="Q37" s="65"/>
-      <c r="R37" s="66"/>
+      <c r="O37" s="60" t="s">
+        <v>81</v>
+      </c>
+      <c r="P37" s="61"/>
+      <c r="Q37" s="61"/>
+      <c r="R37" s="62"/>
       <c r="S37" s="22">
         <v>26.0</v>
       </c>
@@ -3266,18 +3250,18 @@
       <c r="J38" s="22"/>
       <c r="K38" s="22"/>
       <c r="L38" s="22"/>
-      <c r="M38" s="62">
+      <c r="M38" s="47">
         <v>27.0</v>
       </c>
-      <c r="N38" s="63">
+      <c r="N38" s="48">
         <v>0.7916666666666666</v>
       </c>
-      <c r="O38" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="P38" s="65"/>
-      <c r="Q38" s="65"/>
-      <c r="R38" s="66"/>
+      <c r="O38" s="60" t="s">
+        <v>81</v>
+      </c>
+      <c r="P38" s="61"/>
+      <c r="Q38" s="61"/>
+      <c r="R38" s="62"/>
       <c r="S38" s="22">
         <v>27.0</v>
       </c>
@@ -3322,18 +3306,18 @@
       <c r="J39" s="22"/>
       <c r="K39" s="22"/>
       <c r="L39" s="22"/>
-      <c r="M39" s="62">
+      <c r="M39" s="47">
         <v>28.0</v>
       </c>
-      <c r="N39" s="63">
+      <c r="N39" s="48">
         <v>0.8055555555555556</v>
       </c>
-      <c r="O39" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="P39" s="65"/>
-      <c r="Q39" s="65"/>
-      <c r="R39" s="66"/>
+      <c r="O39" s="60" t="s">
+        <v>81</v>
+      </c>
+      <c r="P39" s="61"/>
+      <c r="Q39" s="61"/>
+      <c r="R39" s="62"/>
       <c r="S39" s="22">
         <v>28.0</v>
       </c>
@@ -3353,7 +3337,7 @@
       <c r="AA39" s="22"/>
       <c r="AB39" s="22"/>
       <c r="AC39" s="22"/>
-      <c r="AD39" s="67"/>
+      <c r="AD39" s="63"/>
       <c r="AE39" s="1"/>
       <c r="AF39" s="1"/>
     </row>
@@ -3378,18 +3362,18 @@
       <c r="J40" s="22"/>
       <c r="K40" s="22"/>
       <c r="L40" s="22"/>
-      <c r="M40" s="62">
+      <c r="M40" s="47">
         <v>29.0</v>
       </c>
-      <c r="N40" s="63">
+      <c r="N40" s="48">
         <v>0.8194444444444444</v>
       </c>
-      <c r="O40" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="P40" s="65"/>
-      <c r="Q40" s="65"/>
-      <c r="R40" s="66"/>
+      <c r="O40" s="60" t="s">
+        <v>81</v>
+      </c>
+      <c r="P40" s="61"/>
+      <c r="Q40" s="61"/>
+      <c r="R40" s="62"/>
       <c r="S40" s="22">
         <v>29.0</v>
       </c>
@@ -3409,7 +3393,7 @@
       <c r="AA40" s="22"/>
       <c r="AB40" s="22"/>
       <c r="AC40" s="22"/>
-      <c r="AD40" s="67"/>
+      <c r="AD40" s="63"/>
       <c r="AE40" s="1"/>
       <c r="AF40" s="1"/>
     </row>
@@ -3434,18 +3418,18 @@
       <c r="J41" s="22"/>
       <c r="K41" s="22"/>
       <c r="L41" s="22"/>
-      <c r="M41" s="62">
+      <c r="M41" s="47">
         <v>30.0</v>
       </c>
-      <c r="N41" s="63">
+      <c r="N41" s="48">
         <v>0.8333333333333334</v>
       </c>
-      <c r="O41" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="P41" s="65"/>
-      <c r="Q41" s="65"/>
-      <c r="R41" s="66"/>
+      <c r="O41" s="60" t="s">
+        <v>81</v>
+      </c>
+      <c r="P41" s="61"/>
+      <c r="Q41" s="61"/>
+      <c r="R41" s="62"/>
       <c r="S41" s="22">
         <v>30.0</v>
       </c>
@@ -3465,7 +3449,7 @@
       <c r="AA41" s="22"/>
       <c r="AB41" s="22"/>
       <c r="AC41" s="22"/>
-      <c r="AD41" s="67"/>
+      <c r="AD41" s="63"/>
       <c r="AE41" s="1"/>
       <c r="AF41" s="1"/>
     </row>
@@ -3490,18 +3474,18 @@
       <c r="J42" s="22"/>
       <c r="K42" s="22"/>
       <c r="L42" s="22"/>
-      <c r="M42" s="62">
+      <c r="M42" s="47">
         <v>31.0</v>
       </c>
-      <c r="N42" s="63">
+      <c r="N42" s="48">
         <v>0.8472222222222222</v>
       </c>
-      <c r="O42" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="P42" s="65"/>
-      <c r="Q42" s="65"/>
-      <c r="R42" s="66"/>
+      <c r="O42" s="60" t="s">
+        <v>81</v>
+      </c>
+      <c r="P42" s="61"/>
+      <c r="Q42" s="61"/>
+      <c r="R42" s="62"/>
       <c r="S42" s="22">
         <v>31.0</v>
       </c>
@@ -3521,63 +3505,63 @@
       <c r="AA42" s="22"/>
       <c r="AB42" s="22"/>
       <c r="AC42" s="22"/>
-      <c r="AD42" s="67"/>
+      <c r="AD42" s="63"/>
       <c r="AE42" s="1"/>
       <c r="AF42" s="1"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="68">
+      <c r="A43" s="64">
         <v>32.0</v>
       </c>
-      <c r="B43" s="69">
+      <c r="B43" s="65">
         <v>0.8611111111111112</v>
       </c>
-      <c r="C43" s="68"/>
-      <c r="D43" s="68"/>
-      <c r="E43" s="68"/>
-      <c r="F43" s="68"/>
-      <c r="G43" s="68">
+      <c r="C43" s="64"/>
+      <c r="D43" s="64"/>
+      <c r="E43" s="64"/>
+      <c r="F43" s="64"/>
+      <c r="G43" s="64">
         <v>32.0</v>
       </c>
-      <c r="H43" s="69">
+      <c r="H43" s="65">
         <v>0.8611111111111112</v>
       </c>
-      <c r="I43" s="68"/>
-      <c r="J43" s="68"/>
-      <c r="K43" s="68"/>
-      <c r="L43" s="68"/>
-      <c r="M43" s="70">
+      <c r="I43" s="64"/>
+      <c r="J43" s="64"/>
+      <c r="K43" s="64"/>
+      <c r="L43" s="64"/>
+      <c r="M43" s="66">
         <v>32.0</v>
       </c>
-      <c r="N43" s="71">
+      <c r="N43" s="67">
         <v>0.8611111111111112</v>
       </c>
-      <c r="O43" s="72" t="s">
-        <v>80</v>
-      </c>
-      <c r="P43" s="73"/>
-      <c r="Q43" s="73"/>
-      <c r="R43" s="74"/>
-      <c r="S43" s="68">
+      <c r="O43" s="68" t="s">
+        <v>81</v>
+      </c>
+      <c r="P43" s="69"/>
+      <c r="Q43" s="69"/>
+      <c r="R43" s="70"/>
+      <c r="S43" s="64">
         <v>32.0</v>
       </c>
-      <c r="T43" s="69">
+      <c r="T43" s="65">
         <v>0.8611111111111112</v>
       </c>
-      <c r="U43" s="68"/>
-      <c r="V43" s="68"/>
-      <c r="W43" s="68"/>
-      <c r="X43" s="68"/>
-      <c r="Y43" s="68">
+      <c r="U43" s="64"/>
+      <c r="V43" s="64"/>
+      <c r="W43" s="64"/>
+      <c r="X43" s="64"/>
+      <c r="Y43" s="64">
         <v>32.0</v>
       </c>
-      <c r="Z43" s="69">
+      <c r="Z43" s="65">
         <v>0.8611111111111112</v>
       </c>
-      <c r="AA43" s="68"/>
-      <c r="AB43" s="68"/>
-      <c r="AC43" s="68"/>
-      <c r="AD43" s="75"/>
+      <c r="AA43" s="64"/>
+      <c r="AB43" s="64"/>
+      <c r="AC43" s="64"/>
+      <c r="AD43" s="71"/>
       <c r="AE43" s="1"/>
       <c r="AF43" s="1"/>
     </row>
@@ -4539,7 +4523,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="54">
+  <mergeCells count="53">
     <mergeCell ref="V10:V11"/>
     <mergeCell ref="W10:W11"/>
     <mergeCell ref="X10:X11"/>
@@ -4581,19 +4565,18 @@
     <mergeCell ref="N10:N11"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="AD10:AD11"/>
-    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
-    <mergeCell ref="O31:R31"/>
     <mergeCell ref="O32:R32"/>
     <mergeCell ref="O33:R33"/>
     <mergeCell ref="O34:R34"/>
     <mergeCell ref="O35:R35"/>
     <mergeCell ref="O36:R36"/>
     <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/file_wisuda_4okt.xlsx
+++ b/file_wisuda_4okt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="82">
   <si>
     <t xml:space="preserve">Graduation Schedule 
 </t>
@@ -151,9 +151,6 @@
     <t>Nabilla Epiztiany</t>
   </si>
   <si>
-    <t>Fitri Diana</t>
-  </si>
-  <si>
     <t>Wildan Ramdani</t>
   </si>
   <si>
@@ -196,7 +193,7 @@
     <t>Sema</t>
   </si>
   <si>
-    <t>Fadlah Faqih Mashobih</t>
+    <t>Fadlan Faqih</t>
   </si>
   <si>
     <t>alif</t>
@@ -784,7 +781,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -812,7 +809,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2152,9 +2149,7 @@
       <c r="Z22" s="25">
         <v>0.5694444444444444</v>
       </c>
-      <c r="AA22" s="26" t="s">
-        <v>44</v>
-      </c>
+      <c r="AA22" s="26"/>
       <c r="AB22" s="26" t="s">
         <v>21</v>
       </c>
@@ -2175,7 +2170,7 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D23" s="29" t="s">
         <v>21</v>
@@ -2203,7 +2198,7 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="O23" s="52" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P23" s="29" t="s">
         <v>21</v>
@@ -2219,7 +2214,7 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="U23" s="26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="V23" s="26" t="s">
         <v>21</v>
@@ -2237,7 +2232,7 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="AA23" s="29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AB23" s="29" t="s">
         <v>21</v>
@@ -2257,7 +2252,7 @@
         <v>0.5972222222222222</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D24" s="26" t="s">
         <v>21</v>
@@ -2275,7 +2270,7 @@
         <v>0.5972222222222222</v>
       </c>
       <c r="I24" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J24" s="26" t="s">
         <v>21</v>
@@ -2290,7 +2285,7 @@
         <v>13.0</v>
       </c>
       <c r="N24" s="28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S24" s="24">
         <v>13.0</v>
@@ -2299,7 +2294,7 @@
         <v>0.5972222222222222</v>
       </c>
       <c r="U24" s="26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V24" s="26" t="s">
         <v>21</v>
@@ -2341,7 +2336,7 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="I25" s="26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J25" s="26" t="s">
         <v>21</v>
@@ -2359,7 +2354,7 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="O25" s="26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P25" s="26" t="s">
         <v>21</v>
@@ -2375,7 +2370,7 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="U25" s="26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V25" s="26" t="s">
         <v>21</v>
@@ -2393,7 +2388,7 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="AA25" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AB25" s="26" t="s">
         <v>21</v>
@@ -2425,7 +2420,7 @@
         <v>0.625</v>
       </c>
       <c r="I26" s="26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J26" s="26" t="s">
         <v>21</v>
@@ -2443,7 +2438,7 @@
         <v>0.625</v>
       </c>
       <c r="O26" s="26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P26" s="26" t="s">
         <v>21</v>
@@ -2459,7 +2454,7 @@
         <v>0.625</v>
       </c>
       <c r="U26" s="26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V26" s="26" t="s">
         <v>21</v>
@@ -2477,7 +2472,7 @@
         <v>0.625</v>
       </c>
       <c r="AA26" s="26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AB26" s="26" t="s">
         <v>21</v>
@@ -2486,7 +2481,7 @@
         <v>15</v>
       </c>
       <c r="AD26" s="26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AE26" s="27"/>
       <c r="AF26" s="27"/>
@@ -2499,7 +2494,7 @@
         <v>0.6388888888888888</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D27" s="26" t="s">
         <v>21</v>
@@ -2513,13 +2508,13 @@
         <v>0.6388888888888888</v>
       </c>
       <c r="I27" s="49" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J27" s="49" t="s">
         <v>21</v>
       </c>
       <c r="K27" s="49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L27" s="49" t="s">
         <v>19</v>
@@ -2531,7 +2526,7 @@
         <v>0.6388888888888888</v>
       </c>
       <c r="O27" s="26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P27" s="26" t="s">
         <v>21</v>
@@ -2559,7 +2554,7 @@
         <v>0.6388888888888888</v>
       </c>
       <c r="AA27" s="26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AB27" s="26" t="s">
         <v>36</v>
@@ -2581,7 +2576,7 @@
         <v>0.6527777777777778</v>
       </c>
       <c r="C28" s="49" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D28" s="49" t="s">
         <v>21</v>
@@ -2599,7 +2594,7 @@
         <v>0.6527777777777778</v>
       </c>
       <c r="I28" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J28" s="26" t="s">
         <v>21</v>
@@ -2651,7 +2646,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D29" s="26" t="s">
         <v>21</v>
@@ -2679,13 +2674,13 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="O29" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P29" s="26" t="s">
         <v>21</v>
       </c>
       <c r="Q29" s="26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R29" s="26" t="s">
         <v>19</v>
@@ -2697,10 +2692,10 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="U29" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="V29" s="42" t="s">
         <v>72</v>
-      </c>
-      <c r="V29" s="42" t="s">
-        <v>73</v>
       </c>
       <c r="W29" s="42" t="s">
         <v>24</v>
@@ -2715,7 +2710,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="AA29" s="42" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AB29" s="42" t="s">
         <v>21</v>
@@ -2737,7 +2732,7 @@
         <v>0.6805555555555556</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D30" s="26" t="s">
         <v>21</v>
@@ -2753,13 +2748,13 @@
         <v>0.6805555555555556</v>
       </c>
       <c r="I30" s="26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J30" s="26" t="s">
         <v>21</v>
       </c>
       <c r="K30" s="26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L30" s="26" t="s">
         <v>19</v>
@@ -2771,16 +2766,16 @@
         <v>0.6805555555555556</v>
       </c>
       <c r="O30" s="49" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P30" s="49" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q30" s="49" t="s">
         <v>15</v>
       </c>
       <c r="R30" s="49" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S30" s="22">
         <v>19.0</v>
@@ -2813,7 +2808,7 @@
         <v>0.6944444444444444</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D31" s="26" t="s">
         <v>21</v>
@@ -2841,7 +2836,7 @@
         <v>0.6944444444444444</v>
       </c>
       <c r="O31" s="59" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P31" s="29" t="s">
         <v>21</v>
@@ -2869,7 +2864,7 @@
         <v>0.6944444444444444</v>
       </c>
       <c r="AA31" s="29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB31" s="29" t="s">
         <v>21</v>
@@ -2911,7 +2906,7 @@
         <v>0.7083333333333334</v>
       </c>
       <c r="O32" s="60" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P32" s="61"/>
       <c r="Q32" s="61"/>
@@ -2923,10 +2918,10 @@
         <v>0.7083333333333334</v>
       </c>
       <c r="U32" s="29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="V32" s="29" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W32" s="29" t="s">
         <v>15</v>
@@ -2975,7 +2970,7 @@
         <v>0.7222222222222222</v>
       </c>
       <c r="O33" s="60" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
@@ -3033,7 +3028,7 @@
         <v>0.7361111111111112</v>
       </c>
       <c r="O34" s="60" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P34" s="61"/>
       <c r="Q34" s="61"/>
@@ -3089,7 +3084,7 @@
         <v>0.75</v>
       </c>
       <c r="O35" s="60" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
@@ -3145,7 +3140,7 @@
         <v>0.7638888888888888</v>
       </c>
       <c r="O36" s="60" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P36" s="61"/>
       <c r="Q36" s="61"/>
@@ -3201,7 +3196,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="O37" s="60" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
@@ -3257,7 +3252,7 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="O38" s="60" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P38" s="61"/>
       <c r="Q38" s="61"/>
@@ -3313,7 +3308,7 @@
         <v>0.8055555555555556</v>
       </c>
       <c r="O39" s="60" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
@@ -3369,7 +3364,7 @@
         <v>0.8194444444444444</v>
       </c>
       <c r="O40" s="60" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P40" s="61"/>
       <c r="Q40" s="61"/>
@@ -3425,7 +3420,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="O41" s="60" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
@@ -3481,7 +3476,7 @@
         <v>0.8472222222222222</v>
       </c>
       <c r="O42" s="60" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P42" s="61"/>
       <c r="Q42" s="61"/>
@@ -3537,7 +3532,7 @@
         <v>0.8611111111111112</v>
       </c>
       <c r="O43" s="68" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P43" s="69"/>
       <c r="Q43" s="69"/>

--- a/file_wisuda_4okt.xlsx
+++ b/file_wisuda_4okt.xlsx
@@ -781,7 +781,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image3.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -809,7 +809,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -837,7 +837,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -893,7 +893,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
